--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -712,7 +712,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>joe root</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -783,7 +783,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>nathan sowter</t>
+          <t>jamie smith</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1067,23 +1067,27 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>thomas rew</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thomas Rew</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1098,7 +1102,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1107,13 +1111,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -1142,7 +1146,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>daniel worrall</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1209,23 +1213,27 @@
       <c r="E11" t="b">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>james vince</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jamie smith</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1237,25 +1245,25 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -1280,23 +1288,27 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>james vince</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>asa tribe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1311,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1320,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -1355,7 +1367,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>adil rashid</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1501,7 +1513,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1643,7 +1655,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>daniel worrall</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1710,29 +1722,33 @@
       <c r="E18" t="b">
         <v>0</v>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>jason roy</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>joe root</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Joe Root</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1741,22 +1757,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
@@ -1860,7 +1876,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>ben mckinney</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1927,29 +1943,33 @@
       <c r="E21" t="b">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>matthew potts</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>matthew short</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Matthew Short</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>possible_mismatch:76.92307692307692</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1958,22 +1978,22 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22">
@@ -2077,7 +2097,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2799,23 +2819,27 @@
       <c r="E33" t="b">
         <v>0</v>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>nicholas pooran</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>luke wood</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2830,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2839,13 +2863,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -2945,23 +2969,27 @@
       <c r="E35" t="b">
         <v>0</v>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>jofra archer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2976,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -2985,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -3016,20 +3044,24 @@
       <c r="E36" t="b">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>richard gleeson</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>lockie ferguson</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3056,13 +3088,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -3091,7 +3123,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3158,26 +3190,30 @@
       <c r="E38" t="b">
         <v>0</v>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>brydon carse</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>marco jansen</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Marco Jansen</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3186,25 +3222,25 @@
         <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39">
@@ -3304,7 +3340,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3371,20 +3407,24 @@
       <c r="E41" t="b">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>rashid khan</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>adil rashid</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3411,13 +3451,13 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -3446,7 +3486,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>dan lawrence</t>
+          <t>asa tribe</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3588,20 +3628,24 @@
       <c r="E44" t="b">
         <v>0</v>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>will jacks</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>phil salt</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3616,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3625,16 +3669,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45">
@@ -3663,7 +3707,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4018,23 +4062,27 @@
       <c r="E50" t="b">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>jason roy</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>jordan cox</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -4049,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4058,13 +4106,13 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -4164,7 +4212,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>nikhil chaudhary</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4306,7 +4354,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4373,29 +4421,33 @@
       <c r="E55" t="b">
         <v>0</v>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>dan lawrence</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>david miller</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4404,22 +4456,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56">
@@ -4594,7 +4646,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>joe root</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4661,23 +4713,27 @@
       <c r="E59" t="b">
         <v>0</v>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>nathan sowter</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>tristan stubbs</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4692,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4701,13 +4757,13 @@
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -4736,7 +4792,7 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4878,29 +4934,33 @@
       <c r="E62" t="b">
         <v>0</v>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>zak crawley</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>david miller</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>David Miller</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>fuzzy_margin:83.33333333333334</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -4909,22 +4969,22 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63">
@@ -4949,26 +5009,30 @@
       <c r="E63" t="b">
         <v>0</v>
       </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>nikhil chaudhary</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nikhil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -4980,22 +5044,22 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="64">
@@ -5020,53 +5084,57 @@
       <c r="E64" t="b">
         <v>0</v>
       </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>rashid khan</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>rachin ravindra</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rachin Ravindra</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65">
@@ -5241,7 +5309,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5308,26 +5376,30 @@
       <c r="E68" t="b">
         <v>0</v>
       </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>will jacks</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>chris woakes</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Chris Woakes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5336,25 +5408,25 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69">
@@ -5600,7 +5672,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>chris woakes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5671,7 +5743,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>nathan sowter</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5809,29 +5881,33 @@
       <c r="E75" t="b">
         <v>0</v>
       </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>nicholas pooran</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>chris jordan</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -5840,22 +5916,22 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
@@ -6247,7 +6323,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>matthew potts</t>
+          <t>matthew short</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6333,7 +6409,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>584</v>
+        <v>763</v>
       </c>
     </row>
     <row r="3">
@@ -6346,7 +6422,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>323</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -6355,11 +6431,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
@@ -6368,11 +6444,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6">
@@ -6385,7 +6461,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -6399,7 +6475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6663,32 +6739,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -6697,19 +6773,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -6717,32 +6793,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -6751,19 +6827,19 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
@@ -6771,23 +6847,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -6796,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -6805,19 +6881,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -6825,7 +6901,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6844,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6862,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N8" t="n">
         <v>6</v>
@@ -6871,7 +6947,7 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -6879,17 +6955,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -6898,13 +6974,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -6913,19 +6989,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -6933,53 +7009,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
+        <v>20</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24</v>
+      </c>
+      <c r="M10" t="n">
         <v>25</v>
       </c>
-      <c r="D10" t="n">
-        <v>16</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>32</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -6987,26 +7063,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -7021,10 +7097,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-2</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -7033,36 +7109,34 @@
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -7077,10 +7151,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -7089,7 +7163,7 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -7097,23 +7171,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
         <v>18</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7131,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -7143,7 +7217,7 @@
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -7151,20 +7225,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7176,28 +7250,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -7205,26 +7279,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -7236,22 +7310,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7259,26 +7333,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -7293,10 +7367,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -7305,7 +7379,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7313,32 +7387,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -7347,19 +7421,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7367,24 +7441,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
+        <v>16</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
@@ -7401,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -7413,7 +7487,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -7421,7 +7495,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -7431,7 +7505,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -7440,13 +7514,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -7455,27 +7529,29 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -7485,7 +7561,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -7494,54 +7570,52 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -7550,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -7562,22 +7636,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7585,21 +7659,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15</v>
+      </c>
+      <c r="E22" t="n">
         <v>2</v>
       </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
@@ -7610,7 +7684,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7619,19 +7693,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -7639,7 +7713,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7649,7 +7723,7 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -7658,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -7673,10 +7747,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -7685,10 +7759,1254 @@
         <v>4</v>
       </c>
       <c r="P23" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>James Vince</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>17</v>
+      </c>
+      <c r="D24" t="n">
+        <v>18</v>
+      </c>
+      <c r="E24" t="n">
         <v>2</v>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Nathan Sowter</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>16</v>
+      </c>
+      <c r="O25" t="n">
+        <v>4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Zak Crawley</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="n">
+        <v>11</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>14</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Asa Tribe</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D27" t="n">
+        <v>12</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>12</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Matthew Potts</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Harry Brook</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>9</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>4</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>8</v>
+      </c>
+      <c r="O37" t="n">
+        <v>4</v>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>4</v>
+      </c>
+      <c r="P39" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" t="n">
+        <v>7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>2</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7703,7 +9021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U62"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7910,7 +9228,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>joe root</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -7981,7 +9299,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>nathan sowter</t>
+          <t>jamie smith</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -8123,7 +9441,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>jofra archer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8171,12 +9489,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>thomas rew</t>
+          <t>donavan ferreria</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8194,7 +9512,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>daniel worrall</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -8242,12 +9560,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>donavan ferreria</t>
+          <t>dewald bevis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -8265,7 +9583,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>adil rashid</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -8313,12 +9631,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>jamie smith</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -8336,7 +9654,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>rachin ravindra</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8384,12 +9702,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>asa tribe</t>
+          <t>tawanda muyeye</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8407,7 +9725,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -8455,12 +9773,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dewald bevis</t>
+          <t>adien markram</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8478,7 +9796,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>daniel worrall</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8526,12 +9844,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>ben duckett</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8549,7 +9867,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>ben mckinney</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8597,12 +9915,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tawanda muyeye</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -8620,7 +9938,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -8668,12 +9986,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>adien markram</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -8691,7 +10009,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>james vince</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -8739,12 +10057,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>joe root</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -8762,7 +10080,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>james vince</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -8810,12 +10128,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ben duckett</t>
+          <t>rehan ahmed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -8833,7 +10151,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -8881,7 +10199,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>noor ahmed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8904,7 +10222,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>ryan rickelton</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8952,7 +10270,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>josh tougue</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9023,12 +10341,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9037,7 +10355,7 @@
         </is>
       </c>
       <c r="D19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -9046,7 +10364,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9085,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -9094,12 +10412,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rehan ahmed</t>
+          <t>adam zampa</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9165,12 +10483,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>noor ahmed</t>
+          <t>tymal mills</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9188,7 +10506,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9236,12 +10554,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>josh tougue</t>
+          <t>usman tariq</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9259,7 +10577,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>asa tribe</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9307,12 +10625,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>luke wood</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9330,7 +10648,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>nicholas pooran</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9378,12 +10696,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>tom banton</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9401,7 +10719,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -9449,12 +10767,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lockie fergunson</t>
+          <t>lhuan dra p</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9472,7 +10790,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>richard gleeson</t>
+          <t>nathan ellis</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -9520,7 +10838,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>jonny bairstow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9543,7 +10861,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>jason roy</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -9591,12 +10909,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>marco jasen</t>
+          <t>james rew</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9614,7 +10932,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>james vince</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -9662,7 +10980,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adam zampa</t>
+          <t>tom kohler</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9685,7 +11003,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>nikhil chaudhary</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -9733,12 +11051,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tymal mills</t>
+          <t>tom abell</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9756,7 +11074,7 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -9804,12 +11122,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adil rashid</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9827,7 +11145,7 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>rashid khan</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -9875,12 +11193,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>usman tariq</t>
+          <t>will smeed</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9898,7 +11216,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>dan lawrence</t>
+          <t>will jacks</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -9946,12 +11264,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>phil salt</t>
+          <t>joe clarke</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9969,7 +11287,7 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>joe root</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -10017,7 +11335,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>laurie evans</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -10040,7 +11358,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -10088,12 +11406,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>tom banton</t>
+          <t>mitchell owen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -10111,7 +11429,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -10159,12 +11477,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lhuan dra p</t>
+          <t>craig overton</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10182,7 +11500,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10230,12 +11548,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>jonny bairstow</t>
+          <t>liam dawson</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10253,7 +11571,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -10301,7 +11619,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jordan cox</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -10324,7 +11642,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -10372,12 +11690,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>james rew</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10395,7 +11713,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>chris woakes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -10443,12 +11761,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tom kohler</t>
+          <t>gus atkinson</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10466,7 +11784,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -10514,12 +11832,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>tom abell</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10537,7 +11855,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -10585,7 +11903,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>josh fillpi</t>
+          <t>saqib mahmood</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -10608,7 +11926,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -10656,12 +11974,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -10679,7 +11997,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>dan lawrence</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -10727,12 +12045,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>will smeed</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10750,7 +12068,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -10798,12 +12116,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>joe clarke</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10821,7 +12139,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>matthew short</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -10863,1284 +12181,6 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>tristan stubbs</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D45" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>nathan sowter</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>laurie evans</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>sam curran</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>david willey</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D47" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>zak crawley</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>nikhil chaudhary</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D48" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>rachin ravindra</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D49" t="b">
-        <v>0</v>
-      </c>
-      <c r="E49" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>rashid khan</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>mitchell owen</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D50" t="b">
-        <v>0</v>
-      </c>
-      <c r="E50" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>craig overton</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D51" t="b">
-        <v>0</v>
-      </c>
-      <c r="E51" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>ryan rickelton</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>chris woakes</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D52" t="b">
-        <v>0</v>
-      </c>
-      <c r="E52" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>will jacks</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>liam dawson</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D53" t="b">
-        <v>0</v>
-      </c>
-      <c r="E53" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>mitchell santner</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D54" t="b">
-        <v>0</v>
-      </c>
-      <c r="E54" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>chris wood</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D55" t="b">
-        <v>0</v>
-      </c>
-      <c r="E55" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>nicholas pooran</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>gus atkinson</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D56" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>nathan sowter</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>mustafizur rahman</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D57" t="b">
-        <v>0</v>
-      </c>
-      <c r="E57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>sam curran</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>chris jordan</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E58" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>nicholas pooran</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>saqib mahmood</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D59" t="b">
-        <v>0</v>
-      </c>
-      <c r="E59" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" t="n">
-        <v>0</v>
-      </c>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>reece topley</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D60" t="b">
-        <v>0</v>
-      </c>
-      <c r="E60" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>trent boult</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D61" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>brydon carse</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D62" t="b">
-        <v>0</v>
-      </c>
-      <c r="E62" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>matthew potts</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12155,7 +12195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12263,77 +12303,6 @@
         <is>
           <t>Points</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>matthew short</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>matthew potts</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>possible_mismatch:76.92307692307692</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -13,6 +13,7 @@
     <sheet name="No_Stats_Yet" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Possible_Mismatch" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="AI_Matches" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Match_Team_Points" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4934,33 +4935,29 @@
       <c r="E62" t="b">
         <v>0</v>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
         <is>
           <t>david miller</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>David Miller</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>fuzzy_margin:83.33333333333334</t>
+          <t>no_stats_yet</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
@@ -4969,22 +4966,22 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -6448,7 +6445,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>222</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
@@ -9021,7 +9018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11406,12 +11403,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mitchell owen</t>
+          <t>david willey</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -11429,7 +11426,7 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>david miller</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -11477,12 +11474,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>craig overton</t>
+          <t>mitchell owen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -11500,7 +11497,7 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>chris jordan</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -11548,12 +11545,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>liam dawson</t>
+          <t>craig overton</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -11571,7 +11568,7 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -11619,12 +11616,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mitchell santner</t>
+          <t>liam dawson</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -11642,7 +11639,7 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>mitchell marsh</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -11690,12 +11687,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>chris wood</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -11713,7 +11710,7 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>chris woakes</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -11761,12 +11758,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gus atkinson</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -11784,7 +11781,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>chris woakes</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -11832,12 +11829,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>mustafizur rahman</t>
+          <t>gus atkinson</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -11855,7 +11852,7 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -11903,12 +11900,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>saqib mahmood</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -11926,7 +11923,7 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -11974,7 +11971,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>reece topley</t>
+          <t>saqib mahmood</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11997,7 +11994,7 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -12045,7 +12042,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>bradley currie</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12068,7 +12065,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>trent boult</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -12116,12 +12113,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>matt henry</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -12139,48 +12136,119 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
+          <t>brydon carse</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>no_stats_yet</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>matt henry</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NAN</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>matthew short</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>no_stats_yet</t>
         </is>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12429,4 +12497,220 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MatchNo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M1: MI London v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M2: Southern Brave v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -23,16 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -43,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,21 +48,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,107 +423,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Captain</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ViceCaptain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Matched_Player</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>API_Name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Suggested_Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Match_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>RunOuts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Batting_Points</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Bowling_Points</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Fielding_Points</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Base_Points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Multiplier</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -552,11 +540,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="b">
         <v>1</v>
       </c>
@@ -627,34 +611,34 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="b">
         <v>0</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>richard gleeson</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>heinrich klaasen</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Heinrich Klaasen</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -669,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -678,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -698,11 +682,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="b">
         <v>0</v>
       </c>
@@ -769,34 +749,34 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="b">
         <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>jamie smith</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tim seifert</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tim Seifert</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -811,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -820,13 +800,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -840,11 +820,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="b">
         <v>0</v>
       </c>
@@ -855,7 +831,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -911,11 +887,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="b">
         <v>0</v>
       </c>
@@ -986,34 +958,34 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>jofra archer</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>jos buttler</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Jos Buttler</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1028,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1037,13 +1009,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9">
@@ -1057,11 +1029,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="b">
         <v>0</v>
       </c>
@@ -1132,11 +1100,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="b">
         <v>0</v>
       </c>
@@ -1203,11 +1167,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="b">
         <v>0</v>
       </c>
@@ -1278,11 +1238,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="b">
         <v>0</v>
       </c>
@@ -1353,34 +1309,34 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="b">
         <v>0</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>adil rashid</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>dewald brevis</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dewald Brevis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1395,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1404,13 +1360,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -1424,11 +1380,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="b">
         <v>0</v>
       </c>
@@ -1499,11 +1451,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="b">
         <v>0</v>
       </c>
@@ -1514,7 +1462,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1570,11 +1518,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="b">
         <v>0</v>
       </c>
@@ -1585,7 +1529,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1641,34 +1585,34 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>daniel worrall</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>aiden markram</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1683,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1692,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1712,11 +1656,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="b">
         <v>1</v>
       </c>
@@ -1787,11 +1727,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="b">
         <v>0</v>
       </c>
@@ -1862,11 +1798,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="b">
         <v>0</v>
       </c>
@@ -1933,11 +1865,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="b">
         <v>0</v>
       </c>
@@ -2008,11 +1936,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="b">
         <v>0</v>
       </c>
@@ -2083,11 +2007,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="b">
         <v>0</v>
       </c>
@@ -2098,7 +2018,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>gus atkinson</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2154,11 +2074,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="b">
         <v>1</v>
       </c>
@@ -2229,64 +2145,64 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="b">
         <v>0</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>james vince</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>liam livingstone</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Liam Livingstone</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26">
@@ -2300,11 +2216,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="b">
         <v>0</v>
       </c>
@@ -2375,40 +2287,40 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="b">
         <v>1</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>james vince</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>jamie overton</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Jamie Overton</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2417,22 +2329,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -2446,11 +2358,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="b">
         <v>0</v>
       </c>
@@ -2517,34 +2425,34 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="b">
         <v>0</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>noor ahmad</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>fuzzy:90.0</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2559,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2568,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -2588,11 +2496,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="b">
         <v>0</v>
       </c>
@@ -2663,11 +2567,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="b">
         <v>0</v>
       </c>
@@ -2738,37 +2638,37 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="b">
         <v>0</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>james vince</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>josh tongue</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Josh Tongue</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2780,22 +2680,22 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -2809,11 +2709,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="b">
         <v>0</v>
       </c>
@@ -2884,11 +2780,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="b">
         <v>0</v>
       </c>
@@ -2959,11 +2851,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="b">
         <v>0</v>
       </c>
@@ -3034,11 +2922,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="b">
         <v>0</v>
       </c>
@@ -3109,37 +2993,37 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="b">
         <v>0</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>david miller</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>adam milne</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Adam Milne</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3154,19 +3038,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
@@ -3180,11 +3064,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="b">
         <v>0</v>
       </c>
@@ -3255,37 +3135,37 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="b">
         <v>0</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>adam zampa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Adam Zampa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3300,19 +3180,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
@@ -3326,31 +3206,31 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="b">
         <v>0</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>david miller</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>tymal mills</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3377,13 +3257,13 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T40" t="n">
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -3397,11 +3277,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="b">
         <v>0</v>
       </c>
@@ -3472,11 +3348,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="b">
         <v>0</v>
       </c>
@@ -3543,11 +3415,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="b">
         <v>0</v>
       </c>
@@ -3618,11 +3486,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="b">
         <v>0</v>
       </c>
@@ -3693,11 +3557,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="b">
         <v>0</v>
       </c>
@@ -3708,7 +3568,7 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>kiran carlson</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3764,11 +3624,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="b">
         <v>0</v>
       </c>
@@ -3835,34 +3691,34 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="b">
         <v>0</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>nathan ellis</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>lhuan dre pretorius</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Lhuan-dre Pretorius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>fuzzy_margin:81.08108108108108</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3877,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3886,13 +3742,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48">
@@ -3906,11 +3762,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="b">
         <v>0</v>
       </c>
@@ -3981,11 +3833,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="b">
         <v>0</v>
       </c>
@@ -3996,7 +3844,7 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>sonny baker</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4052,11 +3900,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="b">
         <v>0</v>
       </c>
@@ -4127,31 +3971,31 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="b">
         <v>0</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>james vince</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>james rew</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -4166,25 +4010,25 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -4198,11 +4042,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="b">
         <v>0</v>
       </c>
@@ -4213,7 +4053,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>nikhil chaudhary</t>
+          <t>tom moores</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4269,11 +4109,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="b">
         <v>0</v>
       </c>
@@ -4340,11 +4176,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="b">
         <v>0</v>
       </c>
@@ -4411,11 +4243,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="b">
         <v>0</v>
       </c>
@@ -4486,11 +4314,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="b">
         <v>0</v>
       </c>
@@ -4561,11 +4385,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="b">
         <v>0</v>
       </c>
@@ -4576,7 +4396,7 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>will jacks</t>
+          <t>willey</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -4632,11 +4452,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="b">
         <v>0</v>
       </c>
@@ -4647,7 +4463,7 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>joe root</t>
+          <t>james coles</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4703,11 +4519,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="b">
         <v>0</v>
       </c>
@@ -4778,11 +4590,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="b">
         <v>0</v>
       </c>
@@ -4849,11 +4657,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="b">
         <v>0</v>
       </c>
@@ -4924,37 +4728,37 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="b">
         <v>0</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>david miller</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>david willey</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>David Willey</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4969,19 +4773,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="63">
@@ -4995,11 +4799,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="b">
         <v>0</v>
       </c>
@@ -5070,11 +4870,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="b">
         <v>0</v>
       </c>
@@ -5145,11 +4941,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="b">
         <v>0</v>
       </c>
@@ -5220,11 +5012,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="b">
         <v>0</v>
       </c>
@@ -5291,11 +5079,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="b">
         <v>0</v>
       </c>
@@ -5306,12 +5090,12 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>chris jordan</t>
+          <t>jamie overton</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>possible_mismatch:76.92307692307692</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -5362,11 +5146,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C68" t="inlineStr"/>
       <c r="D68" t="b">
         <v>0</v>
       </c>
@@ -5437,11 +5217,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="b">
         <v>0</v>
       </c>
@@ -5512,37 +5288,37 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C70" t="inlineStr"/>
       <c r="D70" t="b">
         <v>0</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>liam dawson</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Liam Dawson</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5554,22 +5330,22 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71">
@@ -5583,11 +5359,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="b">
         <v>0</v>
       </c>
@@ -5654,11 +5426,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="b">
         <v>0</v>
       </c>
@@ -5725,40 +5493,40 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C73" t="inlineStr"/>
       <c r="D73" t="b">
         <v>0</v>
       </c>
       <c r="E73" t="b">
         <v>0</v>
       </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>gus atkinson</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Gus Atkinson</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -5767,22 +5535,22 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -5796,11 +5564,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="b">
         <v>0</v>
       </c>
@@ -5867,11 +5631,7 @@
           <t>ssw</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="b">
         <v>0</v>
       </c>
@@ -5942,11 +5702,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="b">
         <v>0</v>
       </c>
@@ -6013,11 +5769,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="b">
         <v>0</v>
       </c>
@@ -6028,7 +5780,7 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>trent boult</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6084,11 +5836,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="b">
         <v>0</v>
       </c>
@@ -6155,11 +5903,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="b">
         <v>0</v>
       </c>
@@ -6230,11 +5974,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="b">
         <v>0</v>
       </c>
@@ -6305,11 +6045,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="b">
         <v>0</v>
       </c>
@@ -6380,17 +6116,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -6406,7 +6142,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>763</v>
+        <v>861</v>
       </c>
     </row>
     <row r="3">
@@ -6419,7 +6155,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>394</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4">
@@ -6432,7 +6168,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>231</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5">
@@ -6445,7 +6181,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>156</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6">
@@ -6458,7 +6194,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>115</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -6472,96 +6208,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Balls</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Fours</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sixes</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Maidens</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RunOuts</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Batting_Points</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Bowling_Points</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Fielding_Points</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Lineup_Points</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Base_Points</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Fifties</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Ducks</t>
         </is>
@@ -6570,23 +6306,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="n">
         <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
@@ -6601,22 +6337,22 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="M2" t="n">
         <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -6626,32 +6362,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6660,150 +6396,152 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M3" t="n">
-        <v>118</v>
+        <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
       <c r="P4" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
+        <v>88</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>22</v>
-      </c>
-      <c r="M5" t="n">
-        <v>61</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>114</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>3</v>
@@ -6815,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -6824,52 +6562,54 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -6878,19 +6618,19 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -6898,20 +6638,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -6923,28 +6663,28 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>53</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -6952,17 +6692,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -6986,10 +6726,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -6998,7 +6738,7 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -7006,26 +6746,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -7040,10 +6780,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -7052,7 +6792,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -7060,20 +6800,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -7085,7 +6825,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -7094,19 +6834,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -7114,26 +6854,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -7148,10 +6888,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -7160,7 +6900,7 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -7168,26 +6908,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7199,22 +6939,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -7222,53 +6962,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -7276,20 +7016,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7301,28 +7041,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7330,26 +7070,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -7364,10 +7104,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M16" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -7376,7 +7116,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7384,32 +7124,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -7418,19 +7158,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7438,26 +7178,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -7472,10 +7212,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -7484,7 +7224,7 @@
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -7492,26 +7232,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -7526,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-2</v>
+        <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -7538,42 +7278,40 @@
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -7582,19 +7320,19 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M20" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -7602,7 +7340,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7639,7 +7377,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N21" t="n">
         <v>6</v>
@@ -7648,7 +7386,7 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7656,32 +7394,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7690,19 +7428,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -7710,7 +7448,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -7735,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -7750,13 +7488,13 @@
         <v>25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -7764,26 +7502,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -7798,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -7810,7 +7548,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -7818,23 +7556,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -7843,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7852,19 +7590,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7872,26 +7610,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -7903,22 +7641,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -7926,26 +7664,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -7960,10 +7698,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -7972,61 +7710,63 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>25</v>
+      </c>
+      <c r="N28" t="n">
         <v>6</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>10</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -8034,26 +7774,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -8065,22 +7805,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -8088,17 +7828,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -8107,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -8119,22 +7859,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -8142,26 +7882,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -8176,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -8188,7 +7928,7 @@
         <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8196,17 +7936,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -8215,13 +7955,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8230,19 +7970,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -8250,20 +7990,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -8284,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -8296,7 +8036,7 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8304,20 +8044,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -8329,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -8338,19 +8078,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8358,23 +8098,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -8389,22 +8129,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -8412,23 +8152,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -8446,7 +8186,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -8458,7 +8198,7 @@
         <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -8466,21 +8206,21 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D37" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
@@ -8491,7 +8231,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8500,45 +8240,43 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>-2</v>
+        <v>19</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="n">
-        <v>1</v>
-      </c>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -8556,7 +8294,7 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -8568,7 +8306,7 @@
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8576,17 +8314,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -8601,7 +8339,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8610,19 +8348,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O39" t="n">
         <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8630,53 +8368,53 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" t="n">
         <v>4</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>7</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>4</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
         <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -8684,23 +8422,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D41" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -8718,7 +8456,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -8730,7 +8468,7 @@
         <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -8738,20 +8476,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -8772,7 +8510,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -8784,7 +8522,7 @@
         <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8792,20 +8530,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -8826,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -8838,7 +8576,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8846,23 +8584,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -8880,7 +8618,7 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -8892,7 +8630,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8900,20 +8638,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -8934,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -8946,7 +8684,7 @@
         <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8954,14 +8692,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
@@ -8979,7 +8717,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -8988,22 +8726,1324 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O46" t="n">
         <v>4</v>
       </c>
       <c r="P46" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chris Jordan</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Jamie Smith</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>6</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Abrar Ahmed</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>8</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ben Kellaway</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>8</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P51" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Peter Willey</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
         <v>2</v>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>8</v>
+      </c>
+      <c r="O53" t="n">
+        <v>4</v>
+      </c>
+      <c r="P53" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6</v>
+      </c>
+      <c r="O54" t="n">
+        <v>4</v>
+      </c>
+      <c r="P54" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Willey</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
+        <v>6</v>
+      </c>
+      <c r="O55" t="n">
+        <v>4</v>
+      </c>
+      <c r="P55" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>8</v>
+      </c>
+      <c r="O56" t="n">
+        <v>4</v>
+      </c>
+      <c r="P56" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>6</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>6</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="n">
+        <v>9</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>4</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>4</v>
+      </c>
+      <c r="P59" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>4</v>
+      </c>
+      <c r="D60" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>4</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>4</v>
+      </c>
+      <c r="P60" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>4</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>4</v>
+      </c>
+      <c r="P61" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>2</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>2</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4</v>
+      </c>
+      <c r="P64" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>4</v>
+      </c>
+      <c r="P66" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
+        <v>4</v>
+      </c>
+      <c r="P67" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>4</v>
+      </c>
+      <c r="P68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
+        <v>4</v>
+      </c>
+      <c r="P69" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9018,111 +10058,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U45"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Captain</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ViceCaptain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Matched_Player</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>API_Name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Suggested_Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Match_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>RunOuts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Batting_Points</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Bowling_Points</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Fielding_Points</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Base_Points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Multiplier</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -9131,19 +10171,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>heinrich klaseen</t>
+          <t>ollie pope</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="b">
         <v>0</v>
       </c>
@@ -9154,7 +10190,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>richard gleeson</t>
+          <t>joe root</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -9202,19 +10238,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ollie pope</t>
+          <t>sam billings</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +10257,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>joe root</t>
+          <t>liam livingstone</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -9273,19 +10305,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>donavan ferreria</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="b">
         <v>0</v>
       </c>
@@ -9296,7 +10324,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>jamie smith</t>
+          <t>daniel worrall</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -9344,19 +10372,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sam billings</t>
+          <t>tim david</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="b">
         <v>0</v>
       </c>
@@ -9367,7 +10391,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>tim seifert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -9415,21 +10439,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>tawanda muyeye</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -9438,7 +10458,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>jofra archer</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -9477,7 +10497,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -9486,7 +10506,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>donavan ferreria</t>
+          <t>ben duckett</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -9494,11 +10514,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="b">
         <v>0</v>
       </c>
@@ -9509,7 +10525,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>daniel worrall</t>
+          <t>ben mckinney</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -9557,19 +10573,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dewald bevis</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="b">
         <v>0</v>
       </c>
@@ -9580,7 +10592,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>adil rashid</t>
+          <t>gus atkinson</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -9628,19 +10640,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>rehan ahmed</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="b">
         <v>0</v>
       </c>
@@ -9651,7 +10659,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>rachin ravindra</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -9699,19 +10707,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tawanda muyeye</t>
+          <t>usman tariq</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="b">
         <v>0</v>
       </c>
@@ -9722,7 +10726,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>asa tribe</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -9770,19 +10774,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>adien markram</t>
+          <t>finn allen</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="b">
         <v>0</v>
       </c>
@@ -9793,7 +10793,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>daniel worrall</t>
+          <t>kiran carlson</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -9841,19 +10841,15 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ben duckett</t>
+          <t>tom banton</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="b">
         <v>0</v>
       </c>
@@ -9864,7 +10860,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>ben mckinney</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -9912,7 +10908,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>jonny bairstow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -9920,11 +10916,7 @@
           <t>f9</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="b">
         <v>0</v>
       </c>
@@ -9935,7 +10927,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>sonny baker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9983,19 +10975,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>tom kohler</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="b">
         <v>0</v>
       </c>
@@ -10006,7 +10994,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>tom moores</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -10054,21 +11042,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>jamie overton</t>
+          <t>tom abell</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -10077,7 +11061,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -10116,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -10125,19 +11109,15 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rehan ahmed</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="b">
         <v>0</v>
       </c>
@@ -10148,7 +11128,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10196,19 +11176,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>noor ahmed</t>
+          <t>will smeed</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="b">
         <v>0</v>
       </c>
@@ -10219,7 +11195,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>willey</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10267,7 +11243,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>josh tougue</t>
+          <t>joe clarke</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10275,11 +11251,7 @@
           <t>sd</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="b">
         <v>0</v>
       </c>
@@ -10290,7 +11262,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>james coles</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10338,19 +11310,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>laurie evans</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="b">
         <v>0</v>
       </c>
@@ -10361,7 +11329,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10409,19 +11377,15 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>adam zampa</t>
+          <t>mitchell owen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="b">
         <v>0</v>
       </c>
@@ -10432,7 +11396,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -10480,7 +11444,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tymal mills</t>
+          <t>mitchell santner</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -10488,11 +11452,7 @@
           <t>cc</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="b">
         <v>0</v>
       </c>
@@ -10503,7 +11463,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>mitchell marsh</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10551,7 +11511,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>usman tariq</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10559,11 +11519,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="b">
         <v>0</v>
       </c>
@@ -10574,7 +11530,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>asa tribe</t>
+          <t>chris woakes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10622,19 +11578,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="b">
         <v>0</v>
       </c>
@@ -10645,7 +11597,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>david miller</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -10693,7 +11645,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tom banton</t>
+          <t>saqib mahmood</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10701,11 +11653,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="b">
         <v>0</v>
       </c>
@@ -10716,7 +11664,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>abrar ahmed</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -10764,7 +11712,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>lhuan dra p</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10772,11 +11720,7 @@
           <t>lg</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="b">
         <v>0</v>
       </c>
@@ -10787,7 +11731,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>nathan ellis</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10835,19 +11779,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>jonny bairstow</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="b">
         <v>0</v>
       </c>
@@ -10858,7 +11798,7 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>jason roy</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -10906,19 +11846,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>james rew</t>
+          <t>matt henry</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="b">
         <v>0</v>
       </c>
@@ -10929,7 +11865,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>james vince</t>
+          <t>matthew short</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -10971,1284 +11907,6 @@
         <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>tom kohler</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>nikhil chaudhary</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>tom abell</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>josh fillpi</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>philip salt</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>will smeed</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>will jacks</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>joe clarke</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>joe root</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>laurie evans</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>david willey</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D34" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>david miller</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>mitchell owen</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" t="b">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>craig overton</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" t="b">
-        <v>0</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>chris jordan</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>liam dawson</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>mitchell santner</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>chris wood</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>chris woakes</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>gus atkinson</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>f9</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>mustafizur rahman</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D41" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>sam curran</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>saqib mahmood</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>reece topley</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>trent boult</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D44" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>brydon carse</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>NAN</t>
-        </is>
-      </c>
-      <c r="D45" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" t="b">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>matthew short</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12263,114 +11921,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Captain</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ViceCaptain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Matched_Player</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>API_Name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Suggested_Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Match_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>RunOuts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Batting_Points</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Bowling_Points</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Fielding_Points</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Base_Points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Multiplier</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>craig overton</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>jamie overton</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>possible_mismatch:76.92307692307692</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12388,107 +12113,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Player</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Captain</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ViceCaptain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Matched_Player</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>API_Name</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Suggested_Match</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Match_Type</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Matches</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Wickets</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Catches</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Stumpings</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>RunOuts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Batting_Points</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Bowling_Points</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Fielding_Points</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Base_Points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Multiplier</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -12505,26 +12230,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MatchNo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Match</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
@@ -12708,6 +12433,96 @@
       </c>
       <c r="D11" t="n">
         <v>179</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M3: London Spirit v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -827,23 +827,27 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>liam livingstone</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sam billings</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sam Billings</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -858,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -867,13 +871,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -1107,23 +1111,27 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>daniel worrall</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>donovan ferreira</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Donovan Ferreira</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1135,25 +1143,25 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -1458,23 +1466,27 @@
       <c r="E15" t="b">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>tim seifert</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>tim david</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1489,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1498,13 +1510,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -1805,23 +1817,27 @@
       <c r="E20" t="b">
         <v>0</v>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ben mckinney</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ben duckett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ben Duckett</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1836,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1845,13 +1861,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="21">
@@ -2365,23 +2381,27 @@
       <c r="E28" t="b">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>rehan ahmed</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rehan Ahmed</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2396,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2405,13 +2425,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -3355,26 +3375,30 @@
       <c r="E42" t="b">
         <v>0</v>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>asa tribe</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>usman tariq</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Usman Tariq</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3389,19 +3413,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -3564,29 +3588,33 @@
       <c r="E45" t="b">
         <v>0</v>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>kiran carlson</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>finn allen</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Finn Allen</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -3595,22 +3623,22 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46">
@@ -3631,29 +3659,33 @@
       <c r="E46" t="b">
         <v>0</v>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>tom banton</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tom Banton</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -3662,22 +3694,22 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47">
@@ -4392,23 +4424,27 @@
       <c r="E57" t="b">
         <v>0</v>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>willey</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>will smeed</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Will Smeed</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4423,7 +4459,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4432,13 +4468,13 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58">
@@ -4459,29 +4495,33 @@
       <c r="E58" t="b">
         <v>0</v>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>james coles</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>joe clarke</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Joe Clarke</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -4490,22 +4530,22 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
     </row>
     <row r="59">
@@ -5019,29 +5059,33 @@
       <c r="E66" t="b">
         <v>0</v>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>mitchell owen</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mitchell Owen</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -5050,22 +5094,22 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67">
@@ -5086,29 +5130,33 @@
       <c r="E67" t="b">
         <v>0</v>
       </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>jamie overton</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>craig overton</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Craig Overton</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>possible_mismatch:76.92307692307692</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -5117,22 +5165,22 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68">
@@ -5366,23 +5414,27 @@
       <c r="E71" t="b">
         <v>0</v>
       </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>mitchell santner</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -5397,7 +5449,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
@@ -5406,13 +5458,13 @@
         <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72">
@@ -5709,20 +5761,24 @@
       <c r="E76" t="b">
         <v>0</v>
       </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>saqib mahmood</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -5749,13 +5805,13 @@
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
@@ -5847,7 +5903,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6052,20 +6108,24 @@
       <c r="E81" t="b">
         <v>0</v>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>matthew short</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>matt henry</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6092,13 +6152,13 @@
         <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6142,7 +6202,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>861</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="3">
@@ -6155,7 +6215,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>629</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4">
@@ -6164,11 +6224,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>386</v>
+        <v>471</v>
       </c>
     </row>
     <row r="5">
@@ -6177,11 +6237,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>302</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6">
@@ -6194,7 +6254,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>218</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>
@@ -6208,7 +6268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R70"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6472,23 +6532,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -6503,22 +6563,22 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
         <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -6528,23 +6588,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6553,28 +6613,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O6" t="n">
         <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -6584,32 +6644,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -6618,52 +6678,54 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
+        <v>67</v>
+      </c>
+      <c r="D8" t="n">
+        <v>45</v>
+      </c>
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -6672,40 +6734,42 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>94</v>
       </c>
       <c r="M8" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6726,10 +6790,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M9" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -6738,7 +6802,7 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
@@ -6746,26 +6810,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -6780,10 +6844,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -6792,7 +6856,7 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -6800,32 +6864,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6834,19 +6898,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -6854,26 +6918,26 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6888,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -6900,15 +6964,17 @@
         <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -6933,13 +6999,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -6948,13 +7014,13 @@
         <v>53</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -6962,17 +7028,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6996,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -7008,7 +7074,7 @@
         <v>4</v>
       </c>
       <c r="P14" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -7016,26 +7082,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -7050,10 +7116,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>8</v>
@@ -7062,7 +7128,7 @@
         <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7070,23 +7136,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -7104,7 +7170,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -7116,7 +7182,7 @@
         <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7124,23 +7190,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -7158,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -7170,7 +7236,7 @@
         <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7178,32 +7244,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -7212,19 +7278,19 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -7232,23 +7298,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D19" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -7257,7 +7323,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -7266,19 +7332,19 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7286,53 +7352,53 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -7340,7 +7406,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -7359,7 +7425,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -7377,7 +7443,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N21" t="n">
         <v>6</v>
@@ -7386,7 +7452,7 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7394,17 +7460,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -7413,7 +7479,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -7428,10 +7494,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -7440,7 +7506,7 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -7448,20 +7514,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -7482,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M23" t="n">
         <v>25</v>
@@ -7494,7 +7560,7 @@
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -7502,26 +7568,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -7536,10 +7602,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M24" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -7548,7 +7614,7 @@
         <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -7556,23 +7622,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -7590,7 +7656,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -7602,7 +7668,7 @@
         <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7610,17 +7676,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -7629,7 +7695,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -7641,22 +7707,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -7664,20 +7730,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -7698,7 +7764,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
         <v>33</v>
@@ -7710,36 +7776,34 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -7751,22 +7815,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7774,23 +7838,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -7799,28 +7863,28 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
         <v>25</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7828,53 +7892,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="M30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O30" t="n">
         <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -7882,7 +7946,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -7913,22 +7977,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
         <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -7936,26 +8000,26 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -7967,22 +8031,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O32" t="n">
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -7990,26 +8054,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -8024,10 +8088,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>8</v>
@@ -8036,7 +8100,7 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8044,26 +8108,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -8078,10 +8142,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -8090,7 +8154,7 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8098,26 +8162,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -8132,10 +8196,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -8144,7 +8208,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -8152,26 +8216,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -8183,22 +8247,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>4</v>
       </c>
       <c r="P36" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -8206,23 +8270,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -8240,7 +8304,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -8252,7 +8316,7 @@
         <v>4</v>
       </c>
       <c r="P37" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8260,26 +8324,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -8291,22 +8355,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8314,7 +8378,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -8333,34 +8397,34 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>4</v>
       </c>
       <c r="P39" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8368,32 +8432,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8402,46 +8466,48 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>7</v>
+        <v>-2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>4</v>
       </c>
       <c r="P40" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -8453,22 +8519,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O41" t="n">
         <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -8476,26 +8542,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -8510,10 +8576,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -8522,7 +8588,7 @@
         <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8530,26 +8596,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -8564,10 +8630,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -8576,7 +8642,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8584,26 +8650,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -8618,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -8630,7 +8696,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8638,26 +8704,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -8672,10 +8738,10 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -8684,7 +8750,7 @@
         <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8692,20 +8758,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -8726,7 +8792,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -8738,7 +8804,7 @@
         <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -8746,17 +8812,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -8765,13 +8831,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8780,19 +8846,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8800,20 +8866,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -8831,22 +8897,22 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8854,20 +8920,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
@@ -8888,7 +8954,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -8900,7 +8966,7 @@
         <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -8908,23 +8974,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -8933,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -8942,19 +9008,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -8962,23 +9028,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -8987,7 +9053,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -8996,19 +9062,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>4</v>
       </c>
       <c r="P51" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9016,20 +9082,20 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -9041,7 +9107,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -9050,19 +9116,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -9070,14 +9136,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
         <v>2</v>
@@ -9086,7 +9152,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -9104,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>-2</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -9116,17 +9182,15 @@
         <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -9151,13 +9215,13 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -9166,13 +9230,13 @@
         <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O54" t="n">
         <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -9180,20 +9244,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -9205,28 +9269,28 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9234,23 +9298,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -9259,7 +9323,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -9268,42 +9332,40 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D57" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -9324,7 +9386,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -9336,7 +9398,7 @@
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9344,20 +9406,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -9375,45 +9437,43 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -9434,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -9446,7 +9506,7 @@
         <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -9454,7 +9514,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -9464,7 +9524,7 @@
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -9479,7 +9539,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -9494,13 +9554,13 @@
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
         <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9508,20 +9568,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -9542,7 +9602,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -9554,7 +9614,7 @@
         <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9562,23 +9622,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -9596,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -9608,7 +9668,7 @@
         <v>4</v>
       </c>
       <c r="P62" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9616,17 +9676,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -9641,7 +9701,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9650,19 +9710,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
         <v>4</v>
       </c>
       <c r="P63" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9670,17 +9730,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -9695,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -9704,19 +9764,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
         <v>4</v>
       </c>
       <c r="P64" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9724,23 +9784,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -9758,7 +9818,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -9770,7 +9830,7 @@
         <v>4</v>
       </c>
       <c r="P65" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9778,17 +9838,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -9809,22 +9869,22 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
         <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9832,7 +9892,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -9857,7 +9917,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -9872,13 +9932,13 @@
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O67" t="n">
         <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -9886,7 +9946,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -9911,7 +9971,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -9926,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O68" t="n">
         <v>4</v>
       </c>
       <c r="P68" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -9940,7 +10000,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -9965,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -9980,13 +10040,13 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -9994,56 +10054,1196 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>Mitchell Santner</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>8</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>7</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Jordan Cox</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>6</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" t="n">
+        <v>4</v>
+      </c>
+      <c r="P71" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Jason Roy</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>8</v>
+      </c>
+      <c r="O72" t="n">
+        <v>4</v>
+      </c>
+      <c r="P72" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Phil Salt</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="n">
+        <v>6</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4</v>
+      </c>
+      <c r="P73" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Willey</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="n">
+        <v>6</v>
+      </c>
+      <c r="O74" t="n">
+        <v>4</v>
+      </c>
+      <c r="P74" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Tom Moores</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Tristan Stubbs</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>7</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>4</v>
+      </c>
+      <c r="P76" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Jofra Archer</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>4</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>4</v>
+      </c>
+      <c r="P77" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>James Rew</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>6</v>
+      </c>
+      <c r="O78" t="n">
+        <v>4</v>
+      </c>
+      <c r="P78" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Ben McKinney</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="n">
+        <v>9</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>4</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4</v>
+      </c>
+      <c r="P79" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Tim David</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" t="n">
+        <v>4</v>
+      </c>
+      <c r="P80" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Will Jacks</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>4</v>
+      </c>
+      <c r="P81" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Dan Lawrence</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>2</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" t="n">
+        <v>4</v>
+      </c>
+      <c r="P82" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>2</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>4</v>
+      </c>
+      <c r="P83" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Noor Ahmad</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" t="n">
+        <v>4</v>
+      </c>
+      <c r="P84" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Aiden Markram</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" t="n">
+        <v>4</v>
+      </c>
+      <c r="P85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Adil Rashid</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" t="n">
+        <v>4</v>
+      </c>
+      <c r="P86" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Lockie Ferguson</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>4</v>
+      </c>
+      <c r="P87" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Matt Henry</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4</v>
+      </c>
+      <c r="P88" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>4</v>
+      </c>
+      <c r="P89" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
+        <v>4</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
         <v>-2</v>
       </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" t="n">
-        <v>4</v>
-      </c>
-      <c r="P70" t="n">
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
+        <v>4</v>
+      </c>
+      <c r="P91" t="n">
         <v>2</v>
       </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10058,7 +11258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10238,12 +11438,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sam billings</t>
+          <t>tawanda muyeye</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -10257,7 +11457,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>liam livingstone</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -10305,12 +11505,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>donavan ferreria</t>
+          <t>marcus stoinis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -10324,7 +11524,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>daniel worrall</t>
+          <t>gus atkinson</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -10372,7 +11572,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tim david</t>
+          <t>jonny bairstow</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10391,7 +11591,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tim seifert</t>
+          <t>sonny baker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -10439,12 +11639,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tawanda muyeye</t>
+          <t>tom kohler</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -10458,7 +11658,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>tom moores</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -10506,12 +11706,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ben duckett</t>
+          <t>tom abell</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -10525,7 +11725,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ben mckinney</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -10573,12 +11773,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -10592,7 +11792,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>gus atkinson</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -10640,12 +11840,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>rehan ahmed</t>
+          <t>laurie evans</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -10659,7 +11859,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>abrar ahmed</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -10707,7 +11907,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>usman tariq</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10726,7 +11926,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>asa tribe</t>
+          <t>chris woakes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -10774,12 +11974,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>finn allen</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -10793,7 +11993,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>kiran carlson</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -10841,7 +12041,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tom banton</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10860,7 +12060,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -10908,12 +12108,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jonny bairstow</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
@@ -10927,7 +12127,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>sonny baker</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -10969,944 +12169,6 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tom kohler</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>tom moores</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>tom abell</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>josh fillpi</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>philip salt</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>will smeed</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>willey</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>joe clarke</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>james coles</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>laurie evans</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>sd</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>mitchell owen</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>mitchell santner</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>mitchell marsh</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>chris wood</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>chris woakes</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>mustafizur rahman</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ssw</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>sam curran</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>saqib mahmood</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>abrar ahmed</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>reece topley</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>peter willey</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>brydon carse</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>matt henry</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>matthew short</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1</v>
-      </c>
-      <c r="U27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11921,7 +12183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:U1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12029,73 +12291,6 @@
         <is>
           <t>Points</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>craig overton</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>cc</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>jamie overton</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>possible_mismatch:76.92307692307692</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12230,7 +12425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12525,6 +12720,96 @@
         <v>98</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M4: Birmingham Phoenix v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -576,28 +576,28 @@
         <v>2</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="S2" t="n">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>228</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -933,22 +933,22 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1226,13 +1226,13 @@
         <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -1412,40 +1412,40 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
+        <v>11</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>8</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15">
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1719,13 +1719,13 @@
         <v>8</v>
       </c>
       <c r="S18" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>58</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
@@ -1763,10 +1763,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1790,13 +1790,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>23</v>
+        <v>123</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>23</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q21" t="n">
         <v>25</v>
@@ -1932,13 +1932,13 @@
         <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2003,13 +2003,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -2030,26 +2030,30 @@
       <c r="E23" t="b">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>gus atkinson</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>marcus stoinis</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Marcus Stoinis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2061,22 +2065,22 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
@@ -2114,7 +2118,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
         <v>60</v>
@@ -2132,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q24" t="n">
         <v>61</v>
@@ -2141,13 +2145,13 @@
         <v>8</v>
       </c>
       <c r="S24" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="25">
@@ -2256,10 +2260,10 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2274,7 +2278,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2283,13 +2287,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -2540,7 +2544,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
@@ -2567,13 +2571,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31">
@@ -2611,13 +2615,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2632,19 +2636,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>122</v>
+        <v>159</v>
       </c>
     </row>
     <row r="32">
@@ -2753,7 +2757,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
@@ -2780,13 +2784,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -2895,7 +2899,7 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
         <v>4</v>
@@ -2922,13 +2926,13 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -2966,13 +2970,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2987,19 +2991,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37">
@@ -3108,10 +3112,10 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
         <v>2</v>
@@ -3126,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
         <v>53</v>
@@ -3135,13 +3139,13 @@
         <v>6</v>
       </c>
       <c r="S38" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
@@ -3321,13 +3325,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3342,19 +3346,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42">
@@ -3463,13 +3467,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3484,19 +3488,19 @@
         <v>-2</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44">
@@ -3818,10 +3822,10 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3836,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3845,13 +3849,13 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>36</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49">
@@ -3956,16 +3960,16 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -3974,22 +3978,22 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51">
@@ -4299,16 +4303,16 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4317,22 +4321,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S55" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="56">
@@ -4370,16 +4374,16 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -4388,22 +4392,22 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="57">
@@ -4583,16 +4587,16 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4601,22 +4605,22 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60">
@@ -4721,16 +4725,16 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -4739,22 +4743,22 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
     </row>
     <row r="62">
@@ -4863,10 +4867,10 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -4881,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="Q63" t="n">
         <v>61</v>
@@ -4890,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64">
@@ -4934,16 +4938,16 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -4952,22 +4956,22 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R64" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S64" t="n">
-        <v>44</v>
+        <v>215</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>44</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65">
@@ -5005,10 +5009,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" t="n">
-        <v>41</v>
+        <v>110</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5023,7 +5027,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5032,13 +5036,13 @@
         <v>8</v>
       </c>
       <c r="S65" t="n">
-        <v>67</v>
+        <v>171</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>67</v>
+        <v>171</v>
       </c>
     </row>
     <row r="66">
@@ -5218,7 +5222,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5245,13 +5249,13 @@
         <v>6</v>
       </c>
       <c r="S68" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69">
@@ -5289,13 +5293,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -5307,22 +5311,22 @@
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q69" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70">
@@ -5489,7 +5493,7 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
-          <t>chris woakes</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5707,16 +5711,16 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -5725,22 +5729,22 @@
         <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R75" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S75" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
     </row>
     <row r="76">
@@ -5983,13 +5987,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K79" t="n">
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -5998,25 +6002,25 @@
         <v>0</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P79" t="n">
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="R79" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="S79" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80">
@@ -6054,13 +6058,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K80" t="n">
         <v>9</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -6075,19 +6079,19 @@
         <v>10</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81">
@@ -6202,7 +6206,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1053</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="3">
@@ -6215,7 +6219,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>819</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="4">
@@ -6224,11 +6228,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>471</v>
+        <v>701</v>
       </c>
     </row>
     <row r="5">
@@ -6241,7 +6245,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>392</v>
+        <v>625</v>
       </c>
     </row>
     <row r="6">
@@ -6250,11 +6254,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>373</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>
@@ -6268,7 +6272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6366,32 +6370,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -6400,19 +6404,19 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -6422,24 +6426,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
@@ -6453,22 +6457,22 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="M3" t="n">
         <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -6478,32 +6482,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -6512,52 +6516,54 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M4" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>122</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -6566,98 +6572,98 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
@@ -6669,28 +6675,28 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
+        <v>34</v>
+      </c>
+      <c r="O7" t="n">
         <v>8</v>
       </c>
-      <c r="O7" t="n">
-        <v>4</v>
-      </c>
       <c r="P7" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -6700,26 +6706,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6734,48 +6740,46 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6790,52 +6794,54 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>22</v>
+        <v>115</v>
       </c>
       <c r="M9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>87</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -6844,52 +6850,54 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>98</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>16</v>
-      </c>
-      <c r="M10" t="n">
-        <v>53</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E11" t="n">
         <v>4</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6898,46 +6906,48 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
         <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>80</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+        <v>108</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6952,54 +6962,52 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -7008,52 +7016,54 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M13" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -7062,52 +7072,54 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M14" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7116,19 +7128,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>8</v>
       </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
       <c r="P15" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7136,23 +7148,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -7161,7 +7173,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -7170,19 +7182,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7190,23 +7202,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -7224,7 +7236,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -7233,10 +7245,10 @@
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7244,53 +7256,53 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N18" t="n">
+        <v>18</v>
+      </c>
+      <c r="O18" t="n">
         <v>8</v>
       </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
       <c r="P18" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -7298,23 +7310,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -7332,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -7341,10 +7353,10 @@
         <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7352,23 +7364,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -7377,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -7386,19 +7398,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M20" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -7406,20 +7418,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -7431,28 +7443,28 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
         <v>53</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7460,26 +7472,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>1</v>
       </c>
       <c r="C22" t="n">
+        <v>31</v>
+      </c>
+      <c r="D22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E22" t="n">
         <v>4</v>
       </c>
-      <c r="D22" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -7494,10 +7506,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="M22" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -7506,7 +7518,7 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -7514,32 +7526,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -7548,43 +7560,45 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="M23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>4</v>
       </c>
       <c r="P23" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>47</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7593,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7602,19 +7616,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -7622,32 +7636,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7656,19 +7670,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7676,7 +7690,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -7701,7 +7715,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -7716,13 +7730,13 @@
         <v>53</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O26" t="n">
         <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -7730,26 +7744,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -7764,10 +7778,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -7776,7 +7790,7 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -7784,26 +7798,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -7815,22 +7829,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7838,26 +7852,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
+        <v>43</v>
+      </c>
+      <c r="D29" t="n">
+        <v>17</v>
+      </c>
+      <c r="E29" t="n">
         <v>6</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -7872,10 +7886,10 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>8</v>
@@ -7884,7 +7898,7 @@
         <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7892,23 +7906,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="D30" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7917,28 +7931,28 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -7946,26 +7960,26 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -7977,22 +7991,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M31" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8000,53 +8014,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>9</v>
       </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>28</v>
-      </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -8054,32 +8068,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8088,19 +8102,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M33" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>8</v>
       </c>
-      <c r="O33" t="n">
-        <v>4</v>
-      </c>
       <c r="P33" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8108,26 +8122,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -8142,10 +8156,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="M34" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -8154,7 +8168,7 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8162,26 +8176,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -8196,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M35" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -8208,7 +8222,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -8216,17 +8230,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -8235,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -8247,22 +8261,22 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -8270,32 +8284,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8304,19 +8318,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8324,7 +8338,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -8343,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -8355,22 +8369,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>4</v>
       </c>
       <c r="P38" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8378,17 +8392,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -8397,7 +8411,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -8409,22 +8423,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8432,32 +8446,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8466,39 +8480,37 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>-2</v>
+        <v>48</v>
       </c>
       <c r="M40" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -8507,7 +8519,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -8519,49 +8531,51 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -8573,22 +8587,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="M42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8596,26 +8610,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -8630,10 +8644,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="M43" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -8642,7 +8656,7 @@
         <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8650,7 +8664,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -8669,7 +8683,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -8687,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -8696,7 +8710,7 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8704,20 +8718,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -8729,7 +8743,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -8738,19 +8752,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M45" t="n">
         <v>25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8758,26 +8772,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -8789,22 +8803,22 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N46" t="n">
+        <v>14</v>
+      </c>
+      <c r="O46" t="n">
         <v>8</v>
       </c>
-      <c r="O46" t="n">
-        <v>4</v>
-      </c>
       <c r="P46" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -8812,20 +8826,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -8846,10 +8860,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -8858,7 +8872,7 @@
         <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8866,32 +8880,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -8900,19 +8914,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O48" t="n">
         <v>4</v>
       </c>
       <c r="P48" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8920,32 +8934,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -8954,19 +8968,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
         <v>4</v>
       </c>
       <c r="P49" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -8974,26 +8988,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -9008,19 +9022,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9028,17 +9042,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -9053,7 +9067,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -9062,19 +9076,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9082,14 +9096,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D52" t="n">
         <v>18</v>
@@ -9098,7 +9112,7 @@
         <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -9107,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -9116,19 +9130,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O52" t="n">
         <v>4</v>
       </c>
       <c r="P52" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -9136,53 +9150,53 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>6</v>
+      </c>
+      <c r="O53" t="n">
         <v>8</v>
       </c>
-      <c r="D53" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>10</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>8</v>
-      </c>
-      <c r="O53" t="n">
-        <v>4</v>
-      </c>
       <c r="P53" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -9190,20 +9204,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -9224,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -9233,64 +9247,66 @@
         <v>16</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>1</v>
       </c>
       <c r="C55" t="n">
+        <v>22</v>
+      </c>
+      <c r="D55" t="n">
+        <v>9</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>28</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="n">
         <v>6</v>
-      </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>7</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="n">
-        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9298,26 +9314,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -9332,10 +9348,10 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -9344,7 +9360,7 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9352,26 +9368,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -9383,22 +9399,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O57" t="n">
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9406,26 +9422,26 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -9437,22 +9453,22 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O58" t="n">
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9460,26 +9476,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -9494,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -9506,7 +9522,7 @@
         <v>4</v>
       </c>
       <c r="P59" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -9514,17 +9530,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -9533,13 +9549,13 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -9548,19 +9564,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>4</v>
       </c>
       <c r="P60" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9568,26 +9584,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -9602,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -9614,7 +9630,7 @@
         <v>4</v>
       </c>
       <c r="P61" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9626,49 +9642,49 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
+        <v>11</v>
+      </c>
+      <c r="D62" t="n">
+        <v>13</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>13</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
         <v>8</v>
       </c>
-      <c r="D62" t="n">
-        <v>7</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>10</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9676,17 +9692,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -9695,13 +9711,13 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9710,19 +9726,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>4</v>
       </c>
       <c r="P63" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9730,20 +9746,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -9755,7 +9771,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -9764,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="M64" t="n">
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>4</v>
       </c>
       <c r="P64" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9784,23 +9800,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -9809,7 +9825,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -9818,19 +9834,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9838,23 +9854,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D66" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -9869,22 +9885,22 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9892,20 +9908,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -9917,7 +9933,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -9926,19 +9942,19 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" t="n">
         <v>8</v>
       </c>
-      <c r="O67" t="n">
-        <v>4</v>
-      </c>
       <c r="P67" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -9950,7 +9966,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="n">
         <v>0</v>
@@ -9971,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -9986,13 +10002,13 @@
         <v>0</v>
       </c>
       <c r="N68" t="n">
+        <v>16</v>
+      </c>
+      <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="O68" t="n">
-        <v>4</v>
-      </c>
       <c r="P68" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -10000,23 +10016,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -10025,7 +10041,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10034,19 +10050,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10054,23 +10070,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -10088,7 +10104,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -10100,7 +10116,7 @@
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -10108,23 +10124,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D71" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -10133,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10142,19 +10158,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>4</v>
       </c>
       <c r="P71" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10162,7 +10178,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -10172,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -10187,7 +10203,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -10196,42 +10212,40 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
         <v>4</v>
       </c>
       <c r="P72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -10249,43 +10263,45 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -10297,28 +10313,28 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O74" t="n">
         <v>4</v>
       </c>
       <c r="P74" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -10326,23 +10342,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -10351,7 +10367,7 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -10360,42 +10376,40 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>4</v>
       </c>
       <c r="P75" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -10416,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -10428,7 +10442,7 @@
         <v>4</v>
       </c>
       <c r="P76" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -10436,7 +10450,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -10446,7 +10460,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -10461,7 +10475,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -10476,13 +10490,13 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
         <v>4</v>
       </c>
       <c r="P77" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -10490,17 +10504,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -10515,48 +10529,46 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O78" t="n">
         <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -10571,7 +10583,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -10580,19 +10592,19 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
         <v>4</v>
       </c>
       <c r="P79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -10600,17 +10612,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -10625,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -10634,19 +10646,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10654,17 +10666,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -10688,7 +10700,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -10697,10 +10709,10 @@
         <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -10708,17 +10720,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -10742,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10754,7 +10766,7 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10762,17 +10774,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -10793,22 +10805,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O83" t="n">
         <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10816,17 +10828,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -10859,10 +10871,10 @@
         <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -10870,17 +10882,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -10901,22 +10913,22 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
         <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10924,7 +10936,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -10934,7 +10946,7 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -10949,7 +10961,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -10958,27 +10970,29 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
         <v>4</v>
       </c>
       <c r="P86" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -10988,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -11009,40 +11023,42 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O87" t="n">
         <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -11066,7 +11082,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -11078,7 +11094,7 @@
         <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11086,17 +11102,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -11120,7 +11136,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -11132,7 +11148,7 @@
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11140,17 +11156,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11174,7 +11190,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -11186,7 +11202,7 @@
         <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11194,7 +11210,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -11204,7 +11220,7 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -11228,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -11240,10 +11256,172 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="n">
+      <c r="R91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Saqib Mahmood</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4</v>
+      </c>
+      <c r="P94" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11258,7 +11436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11505,7 +11683,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>marcus stoinis</t>
+          <t>jonny bairstow</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11524,7 +11702,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>gus atkinson</t>
+          <t>sonny baker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -11572,12 +11750,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>jonny bairstow</t>
+          <t>tom kohler</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -11591,7 +11769,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>sonny baker</t>
+          <t>tom moores</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -11639,12 +11817,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tom kohler</t>
+          <t>tom abell</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -11658,7 +11836,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>tom moores</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -11706,12 +11884,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tom abell</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -11725,7 +11903,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>philip salt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -11773,12 +11951,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>josh fillpi</t>
+          <t>laurie evans</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -11792,7 +11970,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>marco jansen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -11840,12 +12018,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>laurie evans</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -11859,7 +12037,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -11907,12 +12085,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chris wood</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -11926,7 +12104,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>chris woakes</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -11974,12 +12152,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mustafizur rahman</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -11993,7 +12171,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -12041,7 +12219,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reece topley</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -12060,7 +12238,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>peter willey</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -12102,73 +12280,6 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>scott currie</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12425,7 +12536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12810,6 +12921,186 @@
         <v>192</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M5: Sunrisers Leeds v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M6: Welsh Fire v MI London</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -662,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4">
@@ -693,7 +693,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>joe root</t>
+          <t>laurie evans</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -773,16 +773,16 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -791,22 +791,22 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6">
@@ -844,40 +844,40 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>14</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -986,10 +986,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -998,28 +998,28 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S8" t="n">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>46</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1128,40 +1128,40 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="S10" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1359,22 +1359,22 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1510,13 +1510,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1648,13 +1648,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1834,16 +1834,16 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>49</v>
+        <v>124</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1852,22 +1852,22 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>68</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -2207,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="Q25" t="n">
         <v>61</v>
@@ -2216,13 +2216,13 @@
         <v>14</v>
       </c>
       <c r="S25" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>177</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26">
@@ -2331,13 +2331,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -2349,22 +2349,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R27" t="n">
         <v>8</v>
       </c>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28">
@@ -2402,16 +2402,16 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
         <v>48</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2420,22 +2420,22 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>69</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2494,19 +2494,19 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30">
@@ -2686,13 +2686,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2707,19 +2707,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>30</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33">
@@ -3041,16 +3041,16 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -3059,22 +3059,22 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S37" t="n">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>37</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3210,13 +3210,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
@@ -3396,10 +3396,10 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
         <v>53</v>
@@ -3423,13 +3423,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>43</v>
@@ -3624,25 +3624,25 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S45" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3707,13 +3707,13 @@
         <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47">
@@ -3751,10 +3751,10 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3769,7 +3769,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3778,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>19</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -3876,20 +3876,24 @@
       <c r="E49" t="b">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>sonny baker</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>jonny bairstow</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Jonny Bairstow</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3898,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3907,22 +3911,22 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -4031,16 +4035,16 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -4049,22 +4053,22 @@
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>-2</v>
+        <v>29</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52">
@@ -4223,7 +4227,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4445,10 +4449,10 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4463,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4472,13 +4476,13 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="58">
@@ -4516,16 +4520,16 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K58" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
@@ -4534,22 +4538,22 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="S58" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59">
@@ -4641,23 +4645,27 @@
       <c r="E60" t="b">
         <v>0</v>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>marco jansen</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>laurie evans</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Laurie Evans</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4672,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4681,13 +4689,13 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
@@ -4796,13 +4804,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4814,22 +4822,22 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="63">
@@ -5080,10 +5088,10 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L66" t="n">
         <v>1</v>
@@ -5095,25 +5103,25 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="Q66" t="n">
         <v>25</v>
       </c>
       <c r="R66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="S66" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67">
@@ -5151,16 +5159,16 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K67" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -5169,22 +5177,22 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R67" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S67" t="n">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>16</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68">
@@ -5364,13 +5372,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5382,22 +5390,22 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q70" t="n">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>47</v>
+        <v>141</v>
       </c>
     </row>
     <row r="71">
@@ -5435,16 +5443,16 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
@@ -5453,22 +5461,22 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S71" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72">
@@ -5573,16 +5581,16 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K73" t="n">
         <v>6</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -5594,19 +5602,19 @@
         <v>7</v>
       </c>
       <c r="Q73" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="R73" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S73" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="74">
@@ -5782,13 +5790,13 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -5800,22 +5808,22 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
@@ -6129,16 +6137,16 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N81" t="n">
         <v>0</v>
@@ -6150,19 +6158,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S81" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -6206,7 +6214,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1424</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="3">
@@ -6219,7 +6227,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1292</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="4">
@@ -6232,7 +6240,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>701</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="5">
@@ -6241,11 +6249,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>625</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="6">
@@ -6254,11 +6262,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>590</v>
+        <v>894</v>
       </c>
     </row>
   </sheetData>
@@ -6272,7 +6280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6370,32 +6378,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -6404,19 +6412,19 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="M2" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
         <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -6426,32 +6434,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6460,19 +6468,19 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -6482,23 +6490,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -6516,7 +6524,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -6528,7 +6536,7 @@
         <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -6538,26 +6546,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -6572,10 +6580,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>8</v>
@@ -6584,44 +6592,42 @@
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -6630,43 +6636,47 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>151</v>
+        <v>61</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
+        <v>161</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E7" t="n">
         <v>8</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -6675,28 +6685,28 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -6706,7 +6716,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -6725,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6743,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -6752,7 +6762,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -6760,20 +6770,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
         <v>4</v>
@@ -6785,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -6794,19 +6804,19 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -6816,23 +6826,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -6844,25 +6854,25 @@
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P10" t="n">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
@@ -6872,32 +6882,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>4</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6906,49 +6916,47 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>16</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P11" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>4</v>
       </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -6962,10 +6970,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>61</v>
+        <v>134</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -6974,7 +6982,7 @@
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -6982,26 +6990,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7016,45 +7024,43 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -7072,7 +7078,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -7084,7 +7090,7 @@
         <v>8</v>
       </c>
       <c r="P14" t="n">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -7094,7 +7100,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7113,13 +7119,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7131,16 +7137,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>91</v>
+        <v>138</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7148,87 +7154,89 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
+        <v>48</v>
+      </c>
+      <c r="D16" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>63</v>
+      </c>
+      <c r="M16" t="n">
         <v>53</v>
       </c>
-      <c r="D16" t="n">
-        <v>42</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>64</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>4</v>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -7236,19 +7244,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O17" t="n">
         <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7256,26 +7264,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -7287,46 +7295,48 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="M18" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -7344,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -7356,31 +7366,33 @@
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>111</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -7389,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -7398,19 +7410,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -7418,23 +7430,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
@@ -7452,7 +7464,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M21" t="n">
         <v>53</v>
@@ -7461,10 +7473,10 @@
         <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7472,32 +7484,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7506,19 +7518,19 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -7526,27 +7538,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
@@ -7560,42 +7572,40 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>78</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D24" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>3</v>
@@ -7616,7 +7626,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -7628,34 +7638,36 @@
         <v>8</v>
       </c>
       <c r="P24" t="n">
-        <v>77</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -7670,10 +7682,10 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>8</v>
@@ -7682,7 +7694,7 @@
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7694,16 +7706,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -7724,7 +7736,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M26" t="n">
         <v>53</v>
@@ -7733,10 +7745,10 @@
         <v>16</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P26" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -7744,26 +7756,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -7778,46 +7790,48 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -7829,22 +7843,22 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="N28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7852,23 +7866,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
+        <v>62</v>
+      </c>
+      <c r="D29" t="n">
         <v>43</v>
       </c>
-      <c r="D29" t="n">
-        <v>17</v>
-      </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -7877,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -7886,19 +7900,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7906,23 +7920,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7931,7 +7945,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -7940,19 +7954,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
         <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -7960,23 +7974,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -7985,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -7994,19 +8008,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8014,23 +8028,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
@@ -8045,22 +8059,22 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O32" t="n">
         <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -8068,53 +8082,53 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="M33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O33" t="n">
         <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8122,23 +8136,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D34" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -8147,55 +8161,57 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -8210,10 +8226,10 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -8222,7 +8238,7 @@
         <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -8230,32 +8246,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8264,19 +8280,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M36" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
         <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -8284,7 +8300,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -8294,7 +8310,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -8309,7 +8325,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8321,16 +8337,16 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8338,32 +8354,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -8372,19 +8388,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="M38" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8392,7 +8408,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -8402,43 +8418,43 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
         <v>5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>4</v>
       </c>
       <c r="M39" t="n">
         <v>53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8446,23 +8462,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D40" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -8471,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8480,19 +8496,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -8500,20 +8516,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -8534,10 +8550,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>-2</v>
+        <v>13</v>
       </c>
       <c r="M41" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -8546,33 +8562,31 @@
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="n">
-        <v>1</v>
-      </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -8587,22 +8601,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8610,26 +8624,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -8644,19 +8658,19 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8664,53 +8678,53 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M44" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8718,7 +8732,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -8728,22 +8742,22 @@
         <v>7</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -8752,19 +8766,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M45" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8772,7 +8786,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -8782,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -8791,7 +8805,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -8806,10 +8820,10 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M46" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N46" t="n">
         <v>14</v>
@@ -8818,25 +8832,27 @@
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -8845,7 +8861,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -8860,19 +8876,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M47" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8880,32 +8896,32 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -8914,52 +8930,54 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -8968,19 +8986,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -8988,53 +9006,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
+        <v>7</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
         <v>9</v>
       </c>
-      <c r="D50" t="n">
-        <v>6</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>10</v>
-      </c>
       <c r="M50" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9042,26 +9060,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -9076,10 +9094,10 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N51" t="n">
         <v>8</v>
@@ -9088,7 +9106,7 @@
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9096,32 +9114,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -9130,19 +9148,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P52" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -9150,17 +9168,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -9169,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -9181,22 +9199,22 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M53" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -9204,32 +9222,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -9238,19 +9256,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N54" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
@@ -9260,53 +9278,53 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N55" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9314,32 +9332,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -9348,19 +9366,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M56" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9368,17 +9386,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -9387,7 +9405,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -9399,22 +9417,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N57" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9422,32 +9440,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -9456,19 +9474,19 @@
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="M58" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9476,26 +9494,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -9507,22 +9525,22 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="M59" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O59" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -9530,17 +9548,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -9555,28 +9573,28 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M60" t="n">
         <v>25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9584,11 +9602,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -9603,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -9621,16 +9639,16 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9638,20 +9656,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D62" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
@@ -9663,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -9672,19 +9690,19 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P62" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9692,20 +9710,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -9717,7 +9735,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9726,19 +9744,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M63" t="n">
         <v>25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9746,32 +9764,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D64" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -9780,19 +9798,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9800,23 +9818,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D65" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -9825,7 +9843,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -9834,19 +9852,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9854,20 +9872,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
         <v>1</v>
@@ -9888,7 +9906,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -9897,10 +9915,10 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9908,61 +9926,63 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
+        <v>26</v>
+      </c>
+      <c r="D67" t="n">
+        <v>17</v>
+      </c>
+      <c r="E67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>29</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="n">
         <v>14</v>
       </c>
-      <c r="D67" t="n">
-        <v>10</v>
-      </c>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>16</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" t="n">
         <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -9981,34 +10001,34 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N68" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -10016,23 +10036,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -10041,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10050,19 +10070,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10070,53 +10090,53 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>1</v>
       </c>
       <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>25</v>
+      </c>
+      <c r="N70" t="n">
         <v>16</v>
-      </c>
-      <c r="D70" t="n">
-        <v>11</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>19</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -10124,32 +10144,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10161,16 +10181,16 @@
         <v>10</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10178,23 +10198,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -10203,7 +10223,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -10212,19 +10232,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -10232,32 +10252,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -10266,45 +10286,43 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="n">
-        <v>1</v>
-      </c>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -10322,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -10334,7 +10352,7 @@
         <v>4</v>
       </c>
       <c r="P74" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -10342,26 +10360,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -10373,22 +10391,22 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -10396,17 +10414,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D76" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E76" t="n">
         <v>2</v>
@@ -10421,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10436,31 +10454,33 @@
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O76" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -10469,13 +10489,13 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -10484,43 +10504,45 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -10538,7 +10560,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -10547,10 +10569,10 @@
         <v>8</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -10558,23 +10580,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -10592,7 +10614,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -10601,10 +10623,10 @@
         <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -10612,20 +10634,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -10646,7 +10668,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -10655,10 +10677,10 @@
         <v>8</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P80" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10666,53 +10688,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
+        <v>19</v>
+      </c>
+      <c r="D81" t="n">
+        <v>19</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>22</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
         <v>4</v>
       </c>
-      <c r="D81" t="n">
-        <v>4</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>4</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>8</v>
-      </c>
       <c r="P81" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -10720,17 +10742,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -10745,7 +10767,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -10754,19 +10776,19 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10774,20 +10796,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -10805,22 +10827,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10828,20 +10850,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -10862,7 +10884,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
@@ -10874,15 +10896,17 @@
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -10907,13 +10931,13 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -10922,13 +10946,13 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
         <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10936,17 +10960,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -10961,7 +10985,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -10970,42 +10994,40 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B87" t="n">
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -11023,42 +11045,40 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>-2</v>
+        <v>15</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>4</v>
       </c>
       <c r="P87" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="n">
-        <v>1</v>
-      </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -11082,7 +11102,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -11091,10 +11111,10 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11102,17 +11122,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -11127,7 +11147,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -11136,19 +11156,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11156,17 +11176,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11190,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -11199,10 +11219,10 @@
         <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11210,7 +11230,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -11235,7 +11255,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -11250,13 +11270,13 @@
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O91" t="n">
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -11264,7 +11284,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -11295,7 +11315,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -11304,13 +11324,13 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O92" t="n">
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -11318,7 +11338,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -11349,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -11358,13 +11378,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O93" t="n">
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11372,7 +11392,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -11382,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -11397,7 +11417,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11412,16 +11432,180 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O94" t="n">
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Luke Wood</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="n">
+        <v>2</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
+        <v>8</v>
+      </c>
+      <c r="P95" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
+        <v>4</v>
+      </c>
+      <c r="P96" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
+        <v>4</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11436,7 +11620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11568,7 +11752,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>joe root</t>
+          <t>laurie evans</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -11683,12 +11867,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>jonny bairstow</t>
+          <t>tom kohler</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -11702,7 +11886,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>sonny baker</t>
+          <t>tom moores</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -11750,12 +11934,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tom kohler</t>
+          <t>tom abell</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -11769,7 +11953,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tom moores</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -11817,12 +12001,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tom abell</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -11836,7 +12020,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>jos buttler</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -11884,7 +12068,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>josh fillpi</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11903,7 +12087,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>philip salt</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -11951,12 +12135,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>laurie evans</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -11970,7 +12154,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>marco jansen</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -12018,7 +12202,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>chris wood</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12037,7 +12221,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>chris jordan</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12085,12 +12269,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mustafizur rahman</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -12104,7 +12288,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -12146,140 +12330,6 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>reece topley</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>peter willey</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>scott currie</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12536,7 +12586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13101,6 +13151,186 @@
         <v>169</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>7</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>M7: Manchester Super Giants v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>8</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>8</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>8</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>8</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M8: Trent Rockets v London Spirit</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>75</v>
@@ -579,25 +579,25 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="S2" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
@@ -689,29 +689,33 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>laurie evans</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ollie pope</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ollie Pope</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -720,22 +724,22 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1199,40 +1203,40 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>45</v>
+        <v>109</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="S11" t="n">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>59</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -1763,7 +1767,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>83</v>
@@ -1772,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -1781,22 +1785,22 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2051,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2065,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>79</v>
+        <v>180</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>79</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24">
@@ -2118,13 +2122,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
         <v>1</v>
@@ -2136,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="Q24" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="R24" t="n">
         <v>8</v>
       </c>
       <c r="S24" t="n">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>322</v>
+        <v>512</v>
       </c>
     </row>
     <row r="25">
@@ -2260,16 +2264,16 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2278,22 +2282,22 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
+        <v>92</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>16</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27">
@@ -2615,13 +2619,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2636,19 +2640,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>151</v>
+        <v>204</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>159</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32">
@@ -2757,7 +2761,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
@@ -2775,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2784,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -2828,7 +2832,7 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2837,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2852,16 +2856,16 @@
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -2899,10 +2903,10 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2914,25 +2918,25 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S35" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
@@ -3325,13 +3329,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3346,19 +3350,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42">
@@ -4227,7 +4231,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>ollie pope</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4307,10 +4311,10 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4325,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4334,13 +4338,13 @@
         <v>16</v>
       </c>
       <c r="S55" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
@@ -4591,16 +4595,16 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K59" t="n">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4609,22 +4613,22 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S59" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60">
@@ -4875,13 +4879,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -4893,22 +4897,22 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="Q63" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>106</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64">
@@ -5301,13 +5305,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -5316,25 +5320,25 @@
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q69" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S69" t="n">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>69</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70">
@@ -5719,10 +5723,10 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L75" t="n">
         <v>1</v>
@@ -5734,25 +5738,25 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q75" t="n">
         <v>25</v>
       </c>
       <c r="R75" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="S75" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76">
@@ -5995,13 +5999,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -6013,22 +6017,22 @@
         <v>2</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="R79" t="n">
         <v>18</v>
       </c>
       <c r="S79" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
     </row>
     <row r="80">
@@ -6214,7 +6218,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1540</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="3">
@@ -6227,7 +6231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1539</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="4">
@@ -6240,7 +6244,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1172</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="5">
@@ -6249,11 +6253,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1109</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="6">
@@ -6262,11 +6266,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>894</v>
+        <v>1109</v>
       </c>
     </row>
   </sheetData>
@@ -6280,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6378,26 +6382,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6409,57 +6413,59 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -6468,19 +6474,19 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="M3" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
         <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -6490,32 +6496,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -6524,75 +6530,73 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -6602,26 +6606,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>60</v>
+        <v>124</v>
       </c>
       <c r="D6" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6636,10 +6640,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="M6" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>8</v>
@@ -6648,38 +6652,36 @@
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6688,60 +6690,58 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>161</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -6750,43 +6750,45 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="M8" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -6795,28 +6797,28 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -6830,13 +6832,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
         <v>75</v>
       </c>
       <c r="D10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>8</v>
@@ -6857,78 +6859,80 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
+        <v>46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>34</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>94</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>12</v>
       </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>16</v>
-      </c>
-      <c r="M11" t="n">
-        <v>106</v>
-      </c>
-      <c r="N11" t="n">
-        <v>16</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
       <c r="P11" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -6936,32 +6940,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -6970,43 +6974,45 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="M12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
@@ -7015,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -7024,19 +7030,19 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M13" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -7044,63 +7050,61 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -7125,7 +7129,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7137,16 +7141,16 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7154,32 +7158,32 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -7188,75 +7192,73 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="M16" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>8</v>
       </c>
       <c r="P16" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="M17" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7264,27 +7266,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>83</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>4</v>
       </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
@@ -7295,51 +7297,49 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>123</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -7354,10 +7354,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="N19" t="n">
         <v>8</v>
@@ -7366,42 +7366,40 @@
         <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -7410,46 +7408,48 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>122</v>
       </c>
       <c r="M20" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O20" t="n">
         <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -7464,19 +7464,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
         <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7484,26 +7484,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -7518,52 +7518,56 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="M22" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -7572,52 +7576,54 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="M23" t="n">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>8</v>
       </c>
       <c r="P23" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" t="n">
-        <v>3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7626,55 +7632,53 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>3</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
-      </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
@@ -7682,19 +7686,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7702,26 +7706,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -7736,40 +7740,42 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="M26" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>16</v>
       </c>
       <c r="O26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F27" t="n">
         <v>3</v>
@@ -7781,7 +7787,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -7790,19 +7796,19 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
       <c r="P27" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
@@ -7812,32 +7818,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -7846,19 +7852,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M28" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O28" t="n">
         <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7866,32 +7872,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -7900,19 +7906,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7920,32 +7926,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -7954,19 +7960,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -7974,23 +7980,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -7999,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -8008,19 +8014,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8028,74 +8034,76 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M32" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>8</v>
       </c>
       <c r="P32" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D33" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
         <v>4</v>
@@ -8113,22 +8121,22 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8136,82 +8144,80 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D34" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N34" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="D35" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -8226,43 +8232,45 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="M35" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P35" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2</v>
       </c>
       <c r="C36" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D36" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -8271,7 +8279,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8280,19 +8288,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>8</v>
       </c>
       <c r="P36" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
@@ -8300,32 +8308,32 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8334,19 +8342,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M37" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8354,26 +8362,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E38" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -8385,22 +8393,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="M38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8408,20 +8416,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -8433,28 +8441,28 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M39" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8462,23 +8470,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D40" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E40" t="n">
         <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -8487,61 +8495,63 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8550,19 +8560,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -8570,53 +8580,53 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D42" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8624,17 +8634,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -8658,10 +8668,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -8670,7 +8680,7 @@
         <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8678,23 +8688,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -8709,22 +8719,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="M44" t="n">
         <v>25</v>
       </c>
       <c r="N44" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O44" t="n">
         <v>8</v>
       </c>
       <c r="P44" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8732,26 +8742,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -8766,40 +8776,42 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="M45" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P45" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -8811,7 +8823,7 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -8820,42 +8832,40 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -8876,10 +8886,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -8888,7 +8898,7 @@
         <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8896,23 +8906,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -8921,7 +8931,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -8930,42 +8940,40 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>8</v>
       </c>
       <c r="P48" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -8986,10 +8994,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M49" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -8998,7 +9006,7 @@
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -9006,53 +9014,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="M50" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P50" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9060,23 +9068,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -9085,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -9094,19 +9102,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M51" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9114,7 +9122,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -9124,7 +9132,7 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -9139,61 +9147,63 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M52" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O52" t="n">
         <v>8</v>
       </c>
       <c r="P52" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D53" t="n">
+        <v>19</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
         <v>5</v>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -9202,37 +9212,39 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="M53" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
         <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -9256,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
         <v>58</v>
@@ -9268,42 +9280,40 @@
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D55" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -9312,19 +9322,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M55" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N55" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9332,32 +9342,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -9366,19 +9376,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9386,17 +9396,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -9420,7 +9430,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" t="n">
         <v>53</v>
@@ -9432,7 +9442,7 @@
         <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9440,53 +9450,53 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D58" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9494,26 +9504,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -9525,76 +9535,78 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>45</v>
+        <v>-2</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>2</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="M60" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
         <v>8</v>
       </c>
       <c r="P60" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9602,17 +9614,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -9636,10 +9648,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M61" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -9648,7 +9660,7 @@
         <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9656,53 +9668,53 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
+        <v>34</v>
+      </c>
+      <c r="D62" t="n">
+        <v>19</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="n">
         <v>41</v>
       </c>
-      <c r="D62" t="n">
-        <v>30</v>
-      </c>
-      <c r="E62" t="n">
-        <v>5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>53</v>
-      </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9710,32 +9722,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9744,19 +9756,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9764,14 +9776,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D64" t="n">
         <v>6</v>
@@ -9780,7 +9792,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
@@ -9789,28 +9801,28 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M64" t="n">
         <v>25</v>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O64" t="n">
         <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9818,23 +9830,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D65" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -9852,7 +9864,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
@@ -9861,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P65" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9872,23 +9884,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D66" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -9906,7 +9918,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -9918,7 +9930,7 @@
         <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9926,26 +9938,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -9957,51 +9969,49 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O67" t="n">
         <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="n">
-        <v>1</v>
-      </c>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -10016,10 +10026,10 @@
         <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="M68" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>14</v>
@@ -10028,31 +10038,33 @@
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D69" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -10061,7 +10073,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10070,19 +10082,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10090,11 +10102,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="n">
         <v>0</v>
@@ -10115,13 +10127,13 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -10130,13 +10142,13 @@
         <v>25</v>
       </c>
       <c r="N70" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -10144,32 +10156,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>2</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10178,19 +10190,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M71" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O71" t="n">
         <v>8</v>
       </c>
       <c r="P71" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10198,32 +10210,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -10232,19 +10244,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P72" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -10252,20 +10264,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -10277,7 +10289,7 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -10286,19 +10298,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M73" t="n">
         <v>25</v>
       </c>
       <c r="N73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10306,20 +10318,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D74" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
         <v>1</v>
@@ -10340,7 +10352,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
@@ -10349,10 +10361,10 @@
         <v>8</v>
       </c>
       <c r="O74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -10360,7 +10372,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -10385,13 +10397,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -10400,13 +10412,13 @@
         <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O75" t="n">
         <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -10414,20 +10426,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -10439,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10448,29 +10460,27 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O76" t="n">
         <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="n">
-        <v>1</v>
-      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -10480,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -10501,48 +10511,46 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>25</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -10551,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10560,52 +10568,54 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
         <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>2</v>
       </c>
       <c r="C79" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -10614,27 +10624,29 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -10644,13 +10656,13 @@
         <v>11</v>
       </c>
       <c r="D80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -10668,7 +10680,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -10680,7 +10692,7 @@
         <v>8</v>
       </c>
       <c r="P80" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10688,23 +10700,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D81" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -10713,7 +10725,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -10722,19 +10734,19 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -10742,23 +10754,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -10767,7 +10779,7 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -10776,19 +10788,19 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O82" t="n">
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10796,23 +10808,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D83" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -10830,7 +10842,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -10839,10 +10851,10 @@
         <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P83" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10850,20 +10862,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -10875,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -10884,39 +10896,37 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O84" t="n">
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -10931,28 +10941,28 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10960,20 +10970,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -10994,7 +11004,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -11006,10 +11016,12 @@
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
+      <c r="R86" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11068,17 +11080,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B88" t="n">
         <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -11102,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -11114,7 +11126,7 @@
         <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11122,17 +11134,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -11156,7 +11168,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -11168,7 +11180,7 @@
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11176,17 +11188,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11210,7 +11222,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
@@ -11222,7 +11234,7 @@
         <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11230,7 +11242,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -11284,17 +11296,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -11315,7 +11327,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -11324,21 +11336,23 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
+      <c r="R92" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -11363,13 +11377,13 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>0</v>
@@ -11378,13 +11392,13 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11448,17 +11462,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -11479,19 +11493,19 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
         <v>10</v>
@@ -11502,17 +11516,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -11536,7 +11550,7 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -11548,7 +11562,7 @@
         <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -11556,7 +11570,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -11566,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -11587,25 +11601,133 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="n">
+      <c r="R97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
+        <v>4</v>
+      </c>
+      <c r="P98" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>4</v>
+      </c>
+      <c r="P99" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11620,7 +11742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11733,7 +11855,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ollie pope</t>
+          <t>tawanda muyeye</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -11752,7 +11874,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>laurie evans</t>
+          <t>adam milne</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -11800,12 +11922,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tawanda muyeye</t>
+          <t>tom kohler</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -11819,7 +11941,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>adam milne</t>
+          <t>tom moores</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -11867,12 +11989,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tom kohler</t>
+          <t>tom abell</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -11886,7 +12008,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tom moores</t>
+          <t>tom alsop</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -11934,12 +12056,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tom abell</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -11953,7 +12075,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>ollie pope</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12001,7 +12123,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>josh fillpi</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -12020,7 +12142,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>jos buttler</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -12068,12 +12190,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chris wood</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -12087,7 +12209,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>chris jordan</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -12135,12 +12257,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mustafizur rahman</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
@@ -12154,7 +12276,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -12202,7 +12324,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reece topley</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -12221,7 +12343,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>peter willey</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12263,73 +12385,6 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>scott currie</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12586,7 +12641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13331,6 +13386,96 @@
         <v>0</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>9</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>9</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>9</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>M9: Southern Brave v MI London</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>425</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -662,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>51</v>
+        <v>134</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>51</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -804,13 +804,13 @@
         <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>111</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>141</v>
+        <v>232</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1017,13 +1017,13 @@
         <v>12</v>
       </c>
       <c r="S8" t="n">
-        <v>161</v>
+        <v>256</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>322</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2007,13 +2007,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -2504,13 +2504,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2569,19 +2569,19 @@
         <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2711,19 +2711,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33">
@@ -3471,13 +3471,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3492,19 +3492,19 @@
         <v>-2</v>
       </c>
       <c r="Q43" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>64</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44">
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3853,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
     </row>
     <row r="49">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
         <v>53</v>
@@ -4764,13 +4764,13 @@
         <v>8</v>
       </c>
       <c r="S61" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="62">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5039,7 +5039,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>155</v>
+        <v>249</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5048,13 +5048,13 @@
         <v>8</v>
       </c>
       <c r="S65" t="n">
-        <v>171</v>
+        <v>269</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>171</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
         <v>15</v>
@@ -5403,13 +5403,13 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71">
@@ -5585,7 +5585,7 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K73" t="n">
         <v>6</v>
@@ -5612,13 +5612,13 @@
         <v>32</v>
       </c>
       <c r="S73" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74">
@@ -5919,7 +5919,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>scott currie</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K80" t="n">
         <v>9</v>
@@ -6079,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80" t="n">
         <v>0</v>
@@ -6094,16 +6094,16 @@
         <v>25</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S80" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81">
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1965</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="3">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1668</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="4">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1313</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="5">
@@ -6253,11 +6253,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1113</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="6">
@@ -6266,11 +6266,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1109</v>
+        <v>1273</v>
       </c>
     </row>
   </sheetData>
@@ -6284,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6382,26 +6382,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>90</v>
+        <v>173</v>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="M2" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>8</v>
@@ -6428,38 +6428,36 @@
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -6471,51 +6469,53 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="M3" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -6524,58 +6524,60 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M4" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O4" t="n">
         <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -6584,19 +6586,19 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -6606,32 +6608,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -6640,99 +6642,99 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>122</v>
       </c>
       <c r="D7" t="n">
+        <v>60</v>
+      </c>
+      <c r="E7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>160</v>
+      </c>
+      <c r="M7" t="n">
         <v>25</v>
       </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>48</v>
-      </c>
-      <c r="M7" t="n">
-        <v>124</v>
-      </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O7" t="n">
         <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>215</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D8" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -6750,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -6762,7 +6764,7 @@
         <v>8</v>
       </c>
       <c r="P8" t="n">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -6772,26 +6774,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>106</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -6800,133 +6802,127 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>141</v>
+        <v>48</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>8</v>
       </c>
       <c r="P9" t="n">
-        <v>161</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>155</v>
+      </c>
+      <c r="N10" t="n">
         <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
-      <c r="L10" t="n">
-        <v>106</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>40</v>
       </c>
       <c r="O10" t="n">
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="M11" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O11" t="n">
         <v>12</v>
@@ -6934,38 +6930,42 @@
       <c r="P11" t="n">
         <v>158</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -6974,54 +6974,52 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -7030,97 +7028,101 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>16</v>
+        <v>121</v>
       </c>
       <c r="M13" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O13" t="n">
         <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="M14" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
@@ -7129,7 +7131,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7138,19 +7140,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O15" t="n">
         <v>8</v>
       </c>
       <c r="P15" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7162,7 +7164,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
@@ -7201,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7212,53 +7214,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N17" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7266,20 +7268,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -7297,22 +7299,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>111</v>
+      </c>
+      <c r="N18" t="n">
         <v>18</v>
-      </c>
-      <c r="M18" t="n">
-        <v>103</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6</v>
       </c>
       <c r="O18" t="n">
         <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -7320,26 +7322,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -7351,22 +7353,22 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="M19" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7374,79 +7376,77 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>18</v>
+      </c>
+      <c r="M20" t="n">
+        <v>103</v>
+      </c>
+      <c r="N20" t="n">
         <v>6</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>122</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>8</v>
-      </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>6</v>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -7455,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -7464,40 +7464,42 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>137</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D22" t="n">
         <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
@@ -7509,7 +7511,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7518,56 +7520,52 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -7576,54 +7574,54 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="M23" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7632,52 +7630,56 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="M24" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+        <v>133</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7686,52 +7688,54 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="M25" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="N25" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>8</v>
       </c>
       <c r="P25" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -7740,54 +7744,52 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>68</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -7796,54 +7798,52 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>111</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -7852,19 +7852,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="N28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7872,14 +7872,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>1</v>
@@ -7891,13 +7891,13 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -7906,52 +7906,54 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="M29" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -7960,43 +7962,45 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="M30" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -8005,7 +8009,7 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -8014,19 +8018,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8034,20 +8038,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F32" t="n">
         <v>3</v>
@@ -8059,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8068,54 +8072,56 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>2</v>
       </c>
       <c r="C33" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8124,19 +8130,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O33" t="n">
         <v>8</v>
       </c>
       <c r="P33" t="n">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8144,32 +8150,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -8178,19 +8184,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="N34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8198,23 +8204,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D35" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="E35" t="n">
         <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -8223,7 +8229,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -8232,45 +8238,43 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O35" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D36" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -8279,7 +8283,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8288,52 +8292,54 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>88</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="D37" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8342,19 +8348,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8362,53 +8368,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
         <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N38" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8416,32 +8422,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>61</v>
+      </c>
+      <c r="D39" t="n">
+        <v>47</v>
+      </c>
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="C39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="D39" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8450,19 +8456,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="M39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P39" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8470,23 +8476,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D40" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -8501,42 +8507,40 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D41" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E41" t="n">
         <v>4</v>
@@ -8551,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8560,73 +8564,75 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>79</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="D42" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="M42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8634,53 +8640,53 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>2</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M43" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O43" t="n">
         <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8688,32 +8694,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8722,19 +8728,19 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="M44" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8742,23 +8748,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D45" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -8767,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -8776,19 +8782,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O45" t="n">
         <v>12</v>
       </c>
       <c r="P45" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="n">
@@ -8798,32 +8804,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -8832,52 +8838,54 @@
         <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="M46" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>2</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D47" t="n">
+        <v>30</v>
+      </c>
+      <c r="E47" t="n">
+        <v>4</v>
+      </c>
+      <c r="F47" t="n">
         <v>3</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8886,19 +8894,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="M47" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O47" t="n">
         <v>8</v>
       </c>
       <c r="P47" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8906,53 +8914,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8960,20 +8968,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -8994,10 +9002,10 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -9006,7 +9014,7 @@
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -9014,53 +9022,53 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N50" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9068,32 +9076,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -9102,19 +9110,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="M51" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9122,23 +9130,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -9147,54 +9155,52 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>-2</v>
+        <v>9</v>
       </c>
       <c r="M52" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N52" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="n">
-        <v>1</v>
-      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -9203,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -9212,19 +9218,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
@@ -9234,53 +9240,53 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
         <v>5</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>2</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2</v>
-      </c>
       <c r="M54" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O54" t="n">
         <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -9288,23 +9294,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
+        <v>11</v>
+      </c>
+      <c r="D55" t="n">
         <v>7</v>
       </c>
-      <c r="D55" t="n">
-        <v>5</v>
-      </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>2</v>
@@ -9322,19 +9328,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M55" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9342,53 +9348,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M56" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O56" t="n">
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9396,26 +9402,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>2</v>
       </c>
       <c r="C57" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -9430,10 +9436,10 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>4</v>
+        <v>63</v>
       </c>
       <c r="M57" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
@@ -9442,7 +9448,7 @@
         <v>8</v>
       </c>
       <c r="P57" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9450,71 +9456,73 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>2</v>
       </c>
       <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M58" t="n">
+        <v>50</v>
+      </c>
+      <c r="N58" t="n">
         <v>14</v>
-      </c>
-      <c r="D58" t="n">
-        <v>12</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>15</v>
-      </c>
-      <c r="M58" t="n">
-        <v>25</v>
-      </c>
-      <c r="N58" t="n">
-        <v>16</v>
       </c>
       <c r="O58" t="n">
         <v>8</v>
       </c>
       <c r="P58" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>2</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -9538,7 +9546,7 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
         <v>58</v>
@@ -9550,63 +9558,61 @@
         <v>8</v>
       </c>
       <c r="P59" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="D60" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>9</v>
+      </c>
+      <c r="M60" t="n">
+        <v>53</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>4</v>
       </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>48</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="n">
-        <v>8</v>
-      </c>
-      <c r="O60" t="n">
-        <v>8</v>
-      </c>
       <c r="P60" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9614,17 +9620,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -9648,10 +9654,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -9660,7 +9666,7 @@
         <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9668,23 +9674,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>2</v>
       </c>
       <c r="C62" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D62" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -9699,22 +9705,22 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
         <v>8</v>
       </c>
       <c r="P62" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9722,32 +9728,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>2</v>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9756,19 +9762,19 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M63" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" t="n">
         <v>8</v>
       </c>
       <c r="P63" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9776,32 +9782,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>2</v>
       </c>
       <c r="C64" t="n">
+        <v>34</v>
+      </c>
+      <c r="D64" t="n">
+        <v>19</v>
+      </c>
+      <c r="E64" t="n">
         <v>3</v>
       </c>
-      <c r="D64" t="n">
-        <v>6</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -9810,19 +9816,19 @@
         <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="M64" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O64" t="n">
         <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9830,26 +9836,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D65" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -9864,19 +9870,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
+        <v>2</v>
+      </c>
+      <c r="M65" t="n">
         <v>53</v>
       </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9884,23 +9890,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D66" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -9918,7 +9924,7 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
@@ -9927,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9938,14 +9944,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D67" t="n">
         <v>6</v>
@@ -9954,7 +9960,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>1</v>
@@ -9963,28 +9969,28 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
         <v>25</v>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O67" t="n">
         <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -9992,109 +9998,107 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>2</v>
       </c>
       <c r="C68" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N68" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>8</v>
       </c>
       <c r="P68" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D69" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E69" t="n">
+        <v>5</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>53</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" t="n">
         <v>4</v>
       </c>
-      <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>43</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="n">
-        <v>8</v>
-      </c>
       <c r="P69" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10102,7 +10106,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -10127,13 +10131,13 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -10142,13 +10146,13 @@
         <v>25</v>
       </c>
       <c r="N70" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -10156,53 +10160,53 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D71" t="n">
+        <v>6</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>10</v>
+      </c>
+      <c r="M71" t="n">
+        <v>25</v>
+      </c>
+      <c r="N71" t="n">
+        <v>8</v>
+      </c>
+      <c r="O71" t="n">
         <v>12</v>
       </c>
-      <c r="E71" t="n">
-        <v>3</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>2</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>22</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="n">
-        <v>16</v>
-      </c>
-      <c r="O71" t="n">
-        <v>8</v>
-      </c>
       <c r="P71" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10210,23 +10214,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
         <v>1</v>
@@ -10235,7 +10239,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -10244,19 +10248,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M72" t="n">
         <v>25</v>
       </c>
       <c r="N72" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -10264,26 +10268,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D73" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -10298,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="M73" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -10310,7 +10314,7 @@
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10318,23 +10322,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D74" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -10349,30 +10353,32 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O74" t="n">
         <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -10403,7 +10409,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -10412,13 +10418,13 @@
         <v>25</v>
       </c>
       <c r="N75" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O75" t="n">
         <v>8</v>
       </c>
       <c r="P75" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
@@ -10426,20 +10432,20 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -10451,7 +10457,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10460,19 +10466,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="O76" t="n">
         <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -10480,53 +10486,53 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2</v>
       </c>
       <c r="C77" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="M77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O77" t="n">
         <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -10534,32 +10540,32 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>2</v>
       </c>
       <c r="C78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10568,29 +10574,27 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N78" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O78" t="n">
         <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -10600,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -10609,13 +10613,13 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -10624,75 +10628,73 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="n">
-        <v>1</v>
-      </c>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>2</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N80" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O80" t="n">
         <v>8</v>
       </c>
       <c r="P80" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10700,20 +10702,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D81" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -10725,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -10734,52 +10736,54 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O81" t="n">
         <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -10788,43 +10792,45 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N82" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D83" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -10833,7 +10839,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -10842,19 +10848,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10862,23 +10868,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -10887,7 +10893,7 @@
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -10896,19 +10902,19 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O84" t="n">
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -10916,23 +10922,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -10947,22 +10953,22 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10970,20 +10976,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>2</v>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -10995,7 +11001,7 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -11004,42 +11010,40 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O86" t="n">
         <v>8</v>
       </c>
       <c r="P86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="n">
-        <v>1</v>
-      </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D87" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -11057,22 +11061,22 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O87" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -11134,20 +11138,20 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D89" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -11159,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -11168,19 +11172,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11188,17 +11192,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11213,7 +11217,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -11222,19 +11226,19 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11296,17 +11300,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -11321,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -11336,33 +11340,31 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O92" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P92" t="n">
         <v>12</v>
       </c>
       <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="n">
-        <v>1</v>
-      </c>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -11377,7 +11379,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11392,21 +11394,23 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P93" t="n">
         <v>12</v>
       </c>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
+      <c r="R93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -11416,7 +11420,7 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -11440,7 +11444,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -11452,17 +11456,15 @@
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="n">
-        <v>1</v>
-      </c>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -11472,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -11487,22 +11489,22 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
         <v>4</v>
@@ -11511,52 +11513,54 @@
         <v>10</v>
       </c>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
+      <c r="R95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>1</v>
       </c>
       <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
         <v>6</v>
-      </c>
-      <c r="D96" t="n">
-        <v>7</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>6</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
-        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>4</v>
@@ -11570,17 +11574,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -11601,16 +11605,16 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11624,7 +11628,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -11655,7 +11659,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -11664,13 +11668,13 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -11678,7 +11682,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tymal Mills</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -11688,7 +11692,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -11712,7 +11716,7 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -11724,10 +11728,64 @@
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="n">
+      <c r="R99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>4</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12343,7 +12401,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>scott currie</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12641,7 +12699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13476,6 +13534,96 @@
         <v>425</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>10</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>10</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>M10: Sunrisers Leeds v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -582,22 +582,22 @@
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>316</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>34</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -872,16 +872,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S6" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1292,7 +1292,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1301,13 +1301,13 @@
         <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>93</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14">
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1714,7 +1714,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         <v>8</v>
       </c>
       <c r="S18" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>133</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>124</v>
+        <v>176</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>170</v>
+        <v>245</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1865,13 +1865,13 @@
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>186</v>
+        <v>265</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>186</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="Q21" t="n">
         <v>25</v>
@@ -1936,13 +1936,13 @@
         <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -2211,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="Q25" t="n">
         <v>61</v>
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="S25" t="n">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>224</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2282,22 +2282,22 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="S26" t="n">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>120</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27">
@@ -2335,13 +2335,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" t="n">
         <v>10</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
@@ -2356,19 +2356,19 @@
         <v>12</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="R27" t="n">
         <v>8</v>
       </c>
       <c r="S27" t="n">
-        <v>53</v>
+        <v>140</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>106</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2640,19 +2640,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>216</v>
+        <v>245</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>216</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3001,13 +3001,13 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -3072,13 +3072,13 @@
         <v>8</v>
       </c>
       <c r="S37" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
         <v>2</v>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q38" t="n">
         <v>53</v>
@@ -3143,13 +3143,13 @@
         <v>6</v>
       </c>
       <c r="S38" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3214,13 +3214,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40">
@@ -3613,17 +3613,17 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>3</v>
+      </c>
+      <c r="K45" t="n">
+        <v>76</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>2</v>
       </c>
-      <c r="K45" t="n">
-        <v>43</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -3631,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S45" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3711,13 +3711,13 @@
         <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>138</v>
+        <v>184</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>138</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3782,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48">
@@ -3897,16 +3897,16 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -3915,22 +3915,22 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>-2</v>
+        <v>27</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K50" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3995,13 +3995,13 @@
         <v>8</v>
       </c>
       <c r="S50" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>14</v>
       </c>
       <c r="S51" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52">
@@ -4382,10 +4382,10 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4409,13 +4409,13 @@
         <v>16</v>
       </c>
       <c r="S56" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="T56" t="n">
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K62" t="n">
         <v>11</v>
@@ -4835,13 +4835,13 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63">
@@ -4950,13 +4950,13 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>138</v>
+      </c>
+      <c r="L64" t="n">
         <v>2</v>
-      </c>
-      <c r="K64" t="n">
-        <v>122</v>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
       </c>
       <c r="M64" t="n">
         <v>2</v>
@@ -4968,22 +4968,22 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="Q64" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="R64" t="n">
         <v>22</v>
       </c>
       <c r="S64" t="n">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>215</v>
+        <v>269</v>
       </c>
     </row>
     <row r="65">
@@ -5163,7 +5163,7 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K67" t="n">
         <v>24</v>
@@ -5172,7 +5172,7 @@
         <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -5187,16 +5187,16 @@
         <v>53</v>
       </c>
       <c r="R67" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="S67" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68">
@@ -5234,10 +5234,10 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -5252,7 +5252,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q68" t="n">
         <v>25</v>
@@ -5261,13 +5261,13 @@
         <v>6</v>
       </c>
       <c r="S68" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69">
@@ -5305,10 +5305,10 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L69" t="n">
         <v>4</v>
@@ -5323,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q69" t="n">
         <v>103</v>
@@ -5332,13 +5332,13 @@
         <v>6</v>
       </c>
       <c r="S69" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70">
@@ -5447,13 +5447,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
         <v>14</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M71" t="n">
         <v>2</v>
@@ -5468,19 +5468,19 @@
         <v>15</v>
       </c>
       <c r="Q71" t="n">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="R71" t="n">
         <v>16</v>
       </c>
       <c r="S71" t="n">
-        <v>64</v>
+        <v>151</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>64</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72">
@@ -5999,13 +5999,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -6020,19 +6020,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="R79" t="n">
         <v>18</v>
       </c>
       <c r="S79" t="n">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>142</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80">
@@ -6141,13 +6141,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M81" t="n">
         <v>1</v>
@@ -6162,19 +6162,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="R81" t="n">
         <v>8</v>
       </c>
       <c r="S81" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>41</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -6218,7 +6218,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2116</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="3">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1701</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="4">
@@ -6240,11 +6240,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1532</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="5">
@@ -6253,11 +6253,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1313</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="6">
@@ -6270,7 +6270,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1273</v>
+        <v>1496</v>
       </c>
     </row>
   </sheetData>
@@ -6284,7 +6284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6438,81 +6438,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>122</v>
+        <v>177</v>
       </c>
       <c r="M3" t="n">
-        <v>114</v>
+        <v>58</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -6521,28 +6519,28 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
         <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -6552,26 +6550,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -6583,51 +6581,53 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6636,58 +6636,60 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="M6" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
       </c>
       <c r="P6" t="n">
-        <v>216</v>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+        <v>256</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E7" t="n">
         <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -6696,19 +6698,19 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M7" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -6718,32 +6720,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -6752,102 +6754,102 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>186</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="n">
+        <v>133</v>
+      </c>
+      <c r="D9" t="n">
+        <v>95</v>
+      </c>
+      <c r="E9" t="n">
+        <v>13</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>184</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q9" t="n">
         <v>2</v>
       </c>
-      <c r="C9" t="n">
-        <v>36</v>
-      </c>
-      <c r="D9" t="n">
-        <v>25</v>
-      </c>
-      <c r="E9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48</v>
-      </c>
-      <c r="M9" t="n">
-        <v>124</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -6862,10 +6864,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M10" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -6874,98 +6876,96 @@
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>48</v>
+      </c>
+      <c r="M11" t="n">
+        <v>124</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>106</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>40</v>
-      </c>
-      <c r="O11" t="n">
-        <v>12</v>
-      </c>
       <c r="P11" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -6974,19 +6974,19 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -6994,144 +6994,144 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>78</v>
+      </c>
+      <c r="D13" t="n">
+        <v>39</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
-        <v>88</v>
-      </c>
-      <c r="D13" t="n">
-        <v>50</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="O13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
+        <v>109</v>
+      </c>
+      <c r="D15" t="n">
+        <v>78</v>
+      </c>
+      <c r="E15" t="n">
         <v>12</v>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7140,46 +7140,50 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>144</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" t="n">
         <v>16</v>
       </c>
-      <c r="M15" t="n">
-        <v>106</v>
-      </c>
-      <c r="N15" t="n">
-        <v>16</v>
-      </c>
-      <c r="O15" t="n">
-        <v>8</v>
-      </c>
       <c r="P15" t="n">
-        <v>146</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -7194,10 +7198,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="M16" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -7206,7 +7210,7 @@
         <v>12</v>
       </c>
       <c r="P16" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7214,23 +7218,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>4</v>
@@ -7239,7 +7243,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -7248,19 +7252,19 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M17" t="n">
-        <v>134</v>
+        <v>106</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7268,26 +7272,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -7299,76 +7303,78 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="M18" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>82</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="O19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7376,87 +7382,89 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="M20" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P20" t="n">
-        <v>139</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
-        <v>89</v>
-      </c>
-      <c r="D21" t="n">
-        <v>46</v>
-      </c>
-      <c r="E21" t="n">
-        <v>6</v>
-      </c>
-      <c r="F21" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -7464,45 +7472,43 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>3</v>
       </c>
       <c r="C22" t="n">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7511,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7520,43 +7526,45 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>137</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>3</v>
       </c>
       <c r="C23" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="D23" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -7565,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -7574,45 +7582,43 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7621,7 +7627,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7630,56 +7636,52 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7688,42 +7690,40 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>53</v>
+        <v>134</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>1</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -7744,10 +7744,10 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M26" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -7756,7 +7756,7 @@
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -7764,53 +7764,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
       <c r="M27" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="O27" t="n">
         <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -7818,23 +7818,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
         <v>4</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -7852,19 +7852,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M28" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7872,32 +7872,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -7906,45 +7906,43 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-2</v>
+        <v>109</v>
       </c>
       <c r="M29" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O29" t="n">
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D30" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E30" t="n">
+        <v>9</v>
+      </c>
+      <c r="F30" t="n">
         <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7959,58 +7957,58 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>5</v>
       </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
@@ -8018,19 +8016,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8038,23 +8036,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -8072,7 +8070,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -8084,44 +8082,42 @@
         <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8130,19 +8126,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="N33" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8150,26 +8146,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>2</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -8184,10 +8180,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="M34" t="n">
-        <v>86</v>
+        <v>53</v>
       </c>
       <c r="N34" t="n">
         <v>8</v>
@@ -8196,41 +8192,43 @@
         <v>8</v>
       </c>
       <c r="P34" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>53</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>4</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>2</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
@@ -8238,19 +8236,19 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N35" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -8258,32 +8256,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8292,54 +8290,52 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8348,19 +8344,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="M37" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8368,32 +8364,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -8402,43 +8398,45 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="M38" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -8447,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8456,19 +8454,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8476,26 +8474,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -8510,10 +8508,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N40" t="n">
         <v>8</v>
@@ -8522,7 +8520,7 @@
         <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -8530,32 +8528,32 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8564,45 +8562,43 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P41" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="D42" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -8611,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -8620,73 +8616,77 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="n">
+        <v>61</v>
+      </c>
+      <c r="D43" t="n">
+        <v>53</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>2</v>
       </c>
-      <c r="C43" t="n">
-        <v>45</v>
-      </c>
-      <c r="D43" t="n">
-        <v>34</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2</v>
-      </c>
-      <c r="F43" t="n">
-        <v>4</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8694,32 +8694,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
+        <v>53</v>
+      </c>
+      <c r="D44" t="n">
+        <v>29</v>
+      </c>
+      <c r="E44" t="n">
         <v>4</v>
       </c>
-      <c r="D44" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8728,185 +8728,183 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="M44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>82</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>3</v>
       </c>
       <c r="C45" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>53</v>
-      </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N45" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>12</v>
       </c>
       <c r="P45" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>2</v>
       </c>
       <c r="C46" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="D46" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>8</v>
       </c>
       <c r="P46" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
         <v>2</v>
       </c>
-      <c r="C47" t="n">
-        <v>45</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3</v>
+      </c>
+      <c r="M47" t="n">
+        <v>50</v>
+      </c>
+      <c r="N47" t="n">
         <v>30</v>
       </c>
-      <c r="E47" t="n">
-        <v>4</v>
-      </c>
-      <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>55</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>16</v>
-      </c>
       <c r="O47" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P47" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8914,53 +8912,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="N48" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8968,20 +8966,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>2</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -8993,7 +8991,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -9002,19 +9000,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M49" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O49" t="n">
         <v>8</v>
       </c>
       <c r="P49" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -9022,32 +9020,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -9056,19 +9054,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="M50" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O50" t="n">
         <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9076,32 +9074,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -9110,52 +9108,54 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="M51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>74</v>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -9164,19 +9164,19 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="M52" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O52" t="n">
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -9184,26 +9184,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -9218,10 +9218,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -9230,30 +9230,28 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
         <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -9265,28 +9263,28 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M54" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N54" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -9294,32 +9292,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="D55" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -9328,19 +9326,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9348,53 +9346,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2</v>
       </c>
       <c r="C56" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>2</v>
       </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
       <c r="L56" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="M56" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O56" t="n">
         <v>8</v>
       </c>
       <c r="P56" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9406,16 +9404,16 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D57" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
@@ -9436,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
@@ -9445,10 +9443,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P57" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9456,17 +9454,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -9481,64 +9479,62 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="N58" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="n">
-        <v>1</v>
-      </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="n">
+        <v>39</v>
+      </c>
+      <c r="D59" t="n">
+        <v>20</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>2</v>
       </c>
-      <c r="C59" t="n">
-        <v>2</v>
-      </c>
-      <c r="D59" t="n">
-        <v>5</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
@@ -9546,73 +9542,75 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="M59" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O59" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" t="n">
         <v>7</v>
       </c>
-      <c r="D60" t="n">
-        <v>5</v>
-      </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
         <v>2</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M60" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O60" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P60" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9620,20 +9618,20 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -9651,22 +9649,22 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M61" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9674,20 +9672,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D62" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E62" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -9705,76 +9703,78 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O62" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
         <v>2</v>
       </c>
-      <c r="C63" t="n">
-        <v>14</v>
-      </c>
       <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2</v>
+      </c>
+      <c r="M63" t="n">
+        <v>61</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" t="n">
         <v>12</v>
       </c>
-      <c r="E63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>2</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>15</v>
-      </c>
-      <c r="M63" t="n">
-        <v>25</v>
-      </c>
-      <c r="N63" t="n">
-        <v>16</v>
-      </c>
-      <c r="O63" t="n">
-        <v>8</v>
-      </c>
       <c r="P63" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
         <v>34</v>
@@ -9807,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -9822,13 +9822,13 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P64" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9836,20 +9836,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D65" t="n">
         <v>7</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -9870,19 +9870,19 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M65" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9890,20 +9890,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D66" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -9915,7 +9915,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -9924,19 +9924,19 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9944,53 +9944,53 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="n">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
         <v>2</v>
       </c>
-      <c r="C67" t="n">
-        <v>3</v>
-      </c>
-      <c r="D67" t="n">
-        <v>6</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
       <c r="H67" t="n">
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M67" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N67" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P67" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -9998,26 +9998,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" t="n">
+        <v>48</v>
+      </c>
+      <c r="D68" t="n">
+        <v>34</v>
+      </c>
+      <c r="E68" t="n">
+        <v>6</v>
+      </c>
+      <c r="F68" t="n">
         <v>2</v>
       </c>
-      <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
       <c r="G68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -10032,73 +10032,75 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="M68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C69" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P69" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10106,32 +10108,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>2</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -10140,52 +10142,54 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="M70" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O70" t="n">
         <v>8</v>
       </c>
       <c r="P70" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10194,19 +10198,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10214,26 +10218,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -10245,49 +10249,51 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M72" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N72" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O72" t="n">
         <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -10302,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -10314,7 +10320,7 @@
         <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10322,20 +10328,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D74" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -10347,117 +10353,117 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="M74" t="n">
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B75" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" t="n">
+        <v>27</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
         <v>2</v>
       </c>
-      <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>1</v>
-      </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M75" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O75" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>2</v>
       </c>
       <c r="C76" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10466,19 +10472,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N76" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O76" t="n">
         <v>8</v>
       </c>
       <c r="P76" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -10486,20 +10492,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D77" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F77" t="n">
         <v>1</v>
@@ -10511,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -10520,19 +10526,19 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P77" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
@@ -10540,20 +10546,20 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
@@ -10574,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M78" t="n">
         <v>25</v>
@@ -10583,10 +10589,10 @@
         <v>8</v>
       </c>
       <c r="O78" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -10594,7 +10600,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -10613,34 +10619,34 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -10652,13 +10658,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -10682,7 +10688,7 @@
         <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
         <v>25</v>
@@ -10691,10 +10697,10 @@
         <v>6</v>
       </c>
       <c r="O80" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P80" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10702,20 +10708,20 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B81" t="n">
         <v>2</v>
       </c>
       <c r="C81" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D81" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -10736,7 +10742,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -10748,42 +10754,40 @@
         <v>8</v>
       </c>
       <c r="P81" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -10792,42 +10796,40 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>-2</v>
+        <v>25</v>
       </c>
       <c r="M82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P82" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="n">
-        <v>1</v>
-      </c>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -10839,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -10848,19 +10850,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10868,32 +10870,32 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B84" t="n">
         <v>2</v>
       </c>
       <c r="C84" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -10902,43 +10904,45 @@
         <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>12</v>
+        <v>-2</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N84" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>8</v>
       </c>
       <c r="P84" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C85" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -10947,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -10956,19 +10960,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P85" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10976,11 +10980,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -10995,13 +10999,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -11013,16 +11017,16 @@
         <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N86" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P86" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -11030,23 +11034,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D87" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -11055,28 +11059,28 @@
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P87" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -11084,23 +11088,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D88" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11118,7 +11122,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -11127,10 +11131,10 @@
         <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11138,33 +11142,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
         <v>2</v>
       </c>
-      <c r="F89" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
@@ -11172,19 +11176,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P89" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11192,53 +11196,53 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C90" t="n">
+        <v>5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="n">
+        <v>5</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
         <v>6</v>
       </c>
-      <c r="D90" t="n">
-        <v>4</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>6</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>8</v>
-      </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11246,20 +11250,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -11271,7 +11275,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -11280,19 +11284,19 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -11300,17 +11304,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -11325,7 +11329,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -11334,19 +11338,19 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
         <v>8</v>
       </c>
-      <c r="O92" t="n">
-        <v>4</v>
-      </c>
       <c r="P92" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -11354,17 +11358,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -11379,7 +11383,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11388,29 +11392,27 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="n">
-        <v>1</v>
-      </c>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -11464,14 +11466,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
         <v>2</v>
@@ -11489,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11498,19 +11500,19 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P95" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="n">
@@ -11520,7 +11522,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -11545,13 +11547,13 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -11560,13 +11562,13 @@
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O96" t="n">
         <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -11574,47 +11576,47 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
         <v>6</v>
-      </c>
-      <c r="D97" t="n">
-        <v>7</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>6</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
-        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
@@ -11628,17 +11630,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -11659,16 +11661,16 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
@@ -11682,7 +11684,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -11713,7 +11715,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -11722,13 +11724,13 @@
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -11736,7 +11738,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tymal Mills</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -11746,7 +11748,7 @@
         <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -11770,7 +11772,7 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -11782,10 +11784,64 @@
         <v>4</v>
       </c>
       <c r="P100" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4</v>
+      </c>
+      <c r="P101" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="n">
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12699,7 +12755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13624,6 +13680,186 @@
         <v>151</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>11</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>11</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>11</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>11</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>M11: Welsh Fire v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>12</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>12</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>12</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>12</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>M12: MI London v London Spirit</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -1132,40 +1132,40 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="S10" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11">
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1221,22 +1221,22 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="S11" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="L23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="Q23" t="n">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>180</v>
+        <v>282</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>180</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24">
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="L28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
@@ -2424,22 +2424,22 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="Q28" t="n">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="R28" t="n">
         <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29">
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2779,22 +2779,22 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34">
@@ -2903,16 +2903,16 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2921,22 +2921,22 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R35" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="S35" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3344,25 +3344,25 @@
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S41" t="n">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>128</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
         <v>2</v>
@@ -3427,13 +3427,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43">
@@ -4160,23 +4160,27 @@
       <c r="E53" t="b">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>tom alsop</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>tom abell</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tom Abell</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -4191,7 +4195,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q53" t="n">
         <v>0</v>
@@ -4200,13 +4204,13 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T53" t="n">
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -4311,16 +4315,16 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4329,22 +4333,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56">
@@ -4453,10 +4457,10 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4471,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4480,13 +4484,13 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>92</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58">
@@ -4524,10 +4528,10 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4536,28 +4540,28 @@
         <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S58" t="n">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>153</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59">
@@ -4595,16 +4599,16 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4613,22 +4617,22 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="S59" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60">
@@ -4666,16 +4670,16 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
@@ -4684,22 +4688,22 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S60" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61">
@@ -5092,16 +5096,16 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>3</v>
+      </c>
+      <c r="K66" t="n">
+        <v>26</v>
+      </c>
+      <c r="L66" t="n">
         <v>2</v>
       </c>
-      <c r="K66" t="n">
-        <v>19</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -5110,22 +5114,22 @@
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q66" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R66" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S66" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67">
@@ -5723,13 +5727,13 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
         <v>2</v>
@@ -5741,22 +5745,22 @@
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q75" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R75" t="n">
         <v>28</v>
       </c>
       <c r="S75" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
     </row>
     <row r="76">
@@ -5794,7 +5798,7 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -5803,7 +5807,7 @@
         <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -5812,22 +5816,22 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="Q76" t="n">
         <v>25</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S76" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77">
@@ -5919,7 +5923,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>brydon carse</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6218,7 +6222,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2200</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="3">
@@ -6231,7 +6235,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1904</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="4">
@@ -6244,7 +6248,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1901</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="5">
@@ -6257,7 +6261,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1732</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="6">
@@ -6270,7 +6274,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1496</v>
+        <v>1697</v>
       </c>
     </row>
   </sheetData>
@@ -6284,7 +6288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6382,32 +6386,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>173</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -6416,23 +6420,21 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>249</v>
+        <v>93</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="N2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -6494,23 +6496,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -6528,7 +6530,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -6540,7 +6542,7 @@
         <v>12</v>
       </c>
       <c r="P4" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q4" t="n">
         <v>2</v>
@@ -6550,26 +6552,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -6584,10 +6586,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>122</v>
+        <v>245</v>
       </c>
       <c r="M5" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>8</v>
@@ -6596,59 +6598,57 @@
         <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
         <v>12</v>
@@ -6657,149 +6657,153 @@
         <v>256</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>118</v>
+        <v>169</v>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>159</v>
+        <v>232</v>
       </c>
       <c r="M7" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M8" t="n">
-        <v>229</v>
+        <v>61</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -6808,48 +6812,46 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="N9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -6864,10 +6866,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>164</v>
+        <v>81</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N10" t="n">
         <v>8</v>
@@ -6876,90 +6878,92 @@
         <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>133</v>
+      </c>
+      <c r="D11" t="n">
+        <v>95</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>184</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>24</v>
+      </c>
+      <c r="O11" t="n">
+        <v>16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
-        <v>36</v>
-      </c>
-      <c r="D11" t="n">
-        <v>25</v>
-      </c>
-      <c r="E11" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>48</v>
-      </c>
-      <c r="M11" t="n">
-        <v>124</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>8</v>
-      </c>
-      <c r="P11" t="n">
-        <v>180</v>
-      </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -6974,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="M12" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>8</v>
@@ -6986,32 +6990,34 @@
         <v>12</v>
       </c>
       <c r="P12" t="n">
-        <v>175</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+        <v>184</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>95</v>
+      </c>
+      <c r="D13" t="n">
+        <v>60</v>
+      </c>
+      <c r="E13" t="n">
+        <v>11</v>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
-        <v>78</v>
-      </c>
-      <c r="D13" t="n">
-        <v>39</v>
-      </c>
-      <c r="E13" t="n">
-        <v>8</v>
-      </c>
-      <c r="F13" t="n">
-        <v>5</v>
-      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
@@ -7025,44 +7031,42 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -7083,22 +7087,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="O14" t="n">
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
@@ -7106,27 +7110,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
@@ -7140,92 +7144,92 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="N15" t="n">
         <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P15" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="M16" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -7234,37 +7238,37 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>136</v>
+      </c>
+      <c r="N17" t="n">
+        <v>18</v>
+      </c>
+      <c r="O17" t="n">
         <v>16</v>
       </c>
-      <c r="M17" t="n">
-        <v>106</v>
-      </c>
-      <c r="N17" t="n">
-        <v>24</v>
-      </c>
-      <c r="O17" t="n">
-        <v>12</v>
-      </c>
       <c r="P17" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7272,23 +7276,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -7297,117 +7301,119 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="M19" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -7416,45 +7422,43 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P20" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>4</v>
@@ -7463,7 +7467,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -7472,19 +7476,19 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M21" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O21" t="n">
         <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7492,23 +7496,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7517,7 +7521,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7526,75 +7530,73 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O22" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>28</v>
+      </c>
+      <c r="M23" t="n">
+        <v>103</v>
+      </c>
+      <c r="N23" t="n">
         <v>6</v>
       </c>
-      <c r="F23" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>128</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8</v>
-      </c>
       <c r="O23" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -7602,23 +7604,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>3</v>
       </c>
       <c r="C24" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D24" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
         <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7627,7 +7629,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7636,40 +7638,42 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q24" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -7681,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7690,19 +7694,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O25" t="n">
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7710,32 +7714,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -7744,44 +7748,46 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="M26" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D27" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -7795,22 +7801,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -7818,32 +7824,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" t="n">
         <v>6</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -7852,19 +7858,19 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>111</v>
       </c>
       <c r="M28" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7872,32 +7878,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>3</v>
       </c>
       <c r="C29" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>4</v>
       </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -7906,19 +7912,19 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="N29" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7926,23 +7932,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7951,63 +7957,61 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
-        <v>1</v>
-      </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -8016,19 +8020,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="M31" t="n">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="N31" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8036,20 +8040,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
         <v>4</v>
@@ -8070,7 +8074,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -8082,7 +8086,7 @@
         <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -8092,23 +8096,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -8117,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8126,19 +8130,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="M33" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O33" t="n">
         <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8146,23 +8150,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>24</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>2</v>
-      </c>
-      <c r="C34" t="n">
-        <v>48</v>
-      </c>
-      <c r="D34" t="n">
-        <v>26</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2</v>
-      </c>
-      <c r="F34" t="n">
-        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>2</v>
@@ -8171,7 +8175,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -8180,102 +8184,102 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="M34" t="n">
         <v>53</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="O34" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P34" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="M35" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -8290,10 +8294,10 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="M36" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -8302,40 +8306,42 @@
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>128</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8344,19 +8350,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>12</v>
       </c>
       <c r="P37" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8364,17 +8370,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -8389,28 +8395,28 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="M38" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O38" t="n">
         <v>12</v>
       </c>
       <c r="P38" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="n">
@@ -8420,32 +8426,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="D39" t="n">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8454,19 +8460,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O39" t="n">
         <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
@@ -8474,20 +8480,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>3</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -8499,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8508,46 +8514,48 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M40" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O40" t="n">
         <v>12</v>
       </c>
       <c r="P40" t="n">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>3</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -8562,10 +8570,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M41" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="N41" t="n">
         <v>8</v>
@@ -8574,7 +8582,7 @@
         <v>12</v>
       </c>
       <c r="P41" t="n">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -8582,26 +8590,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B42" t="n">
         <v>3</v>
       </c>
       <c r="C42" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -8616,10 +8624,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>94</v>
+        <v>-2</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -8628,11 +8636,9 @@
         <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="n">
         <v>1</v>
       </c>
@@ -8640,26 +8646,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>3</v>
       </c>
       <c r="C43" t="n">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="D43" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="E43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -8671,22 +8677,22 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N43" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O43" t="n">
         <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8694,24 +8700,24 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E44" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" t="n">
         <v>4</v>
       </c>
-      <c r="F44" t="n">
-        <v>3</v>
-      </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
@@ -8719,84 +8725,82 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>11</v>
+      </c>
+      <c r="E45" t="n">
         <v>2</v>
       </c>
-      <c r="D45" t="n">
-        <v>5</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M45" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O45" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P45" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8804,18 +8808,18 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" t="n">
         <v>7</v>
       </c>
-      <c r="D46" t="n">
-        <v>5</v>
-      </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
@@ -8838,73 +8842,75 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M46" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>3</v>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="D47" t="n">
+        <v>54</v>
+      </c>
+      <c r="E47" t="n">
         <v>6</v>
       </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>96</v>
       </c>
       <c r="M47" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>12</v>
       </c>
       <c r="P47" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8912,17 +8918,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -8937,7 +8943,7 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -8946,19 +8952,19 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O48" t="n">
         <v>12</v>
       </c>
       <c r="P48" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8966,32 +8972,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C49" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -9000,46 +9006,50 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="M49" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P49" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -9054,10 +9064,10 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N50" t="n">
         <v>8</v>
@@ -9066,7 +9076,7 @@
         <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9074,20 +9084,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D51" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F51" t="n">
         <v>3</v>
@@ -9108,7 +9118,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -9117,36 +9127,36 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
+        <v>99</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D52" t="n">
         <v>29</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -9164,7 +9174,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -9176,25 +9186,27 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>92</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -9218,10 +9230,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -9230,7 +9242,7 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -9238,32 +9250,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -9272,19 +9284,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M54" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="N54" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
@@ -9292,53 +9304,53 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="C55" t="n">
-        <v>52</v>
-      </c>
-      <c r="D55" t="n">
-        <v>28</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O55" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P55" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9346,53 +9358,53 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
         <v>4</v>
       </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
-      </c>
-      <c r="L56" t="n">
-        <v>55</v>
-      </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N56" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P56" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9400,23 +9412,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D57" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -9425,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -9434,19 +9446,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M57" t="n">
         <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O57" t="n">
         <v>12</v>
       </c>
       <c r="P57" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9454,32 +9466,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -9488,19 +9500,19 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M58" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
         <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9508,32 +9520,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -9542,48 +9554,46 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N59" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>2</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -9595,22 +9605,22 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M60" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N60" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="O60" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P60" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9618,53 +9628,53 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D61" t="n">
+        <v>28</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
         <v>5</v>
       </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0</v>
-      </c>
       <c r="G61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="M61" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P61" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9672,23 +9682,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D62" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -9697,28 +9707,28 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O62" t="n">
         <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="n">
@@ -9728,26 +9738,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D63" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -9762,10 +9772,10 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="M63" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -9774,7 +9784,7 @@
         <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9782,53 +9792,53 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
         <v>2</v>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N64" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>12</v>
       </c>
       <c r="P64" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9836,20 +9846,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -9867,22 +9877,22 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M65" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O65" t="n">
         <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -9890,20 +9900,20 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D66" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -9921,37 +9931,39 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
         <v>3</v>
@@ -9960,7 +9972,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>2</v>
@@ -9978,10 +9990,10 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -9990,7 +10002,7 @@
         <v>12</v>
       </c>
       <c r="P67" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -9998,27 +10010,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B68" t="n">
         <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D68" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="E68" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
         <v>2</v>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
@@ -10032,10 +10044,10 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
@@ -10044,42 +10056,40 @@
         <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>1</v>
-      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69" t="n">
+        <v>34</v>
+      </c>
+      <c r="D69" t="n">
         <v>19</v>
       </c>
-      <c r="D69" t="n">
-        <v>10</v>
-      </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
         <v>2</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10088,19 +10098,19 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="M69" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O69" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P69" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10108,32 +10118,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="n">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" t="n">
         <v>2</v>
       </c>
-      <c r="C70" t="n">
-        <v>23</v>
-      </c>
-      <c r="D70" t="n">
-        <v>14</v>
-      </c>
-      <c r="E70" t="n">
-        <v>4</v>
-      </c>
-      <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -10142,54 +10152,52 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N70" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10198,19 +10206,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M71" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10218,53 +10226,53 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B72" t="n">
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>-2</v>
+        <v>27</v>
       </c>
       <c r="M72" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="O72" t="n">
         <v>8</v>
       </c>
       <c r="P72" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
@@ -10274,17 +10282,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -10308,19 +10316,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10328,26 +10336,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -10362,10 +10370,10 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N74" t="n">
         <v>0</v>
@@ -10374,7 +10382,7 @@
         <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
@@ -10382,53 +10390,53 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D75" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="E75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N75" t="n">
+        <v>14</v>
+      </c>
+      <c r="O75" t="n">
         <v>16</v>
       </c>
-      <c r="O75" t="n">
-        <v>12</v>
-      </c>
       <c r="P75" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
@@ -10438,32 +10446,32 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10472,19 +10480,19 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -10492,86 +10500,88 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D77" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
         <v>30</v>
       </c>
-      <c r="E77" t="n">
-        <v>5</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>53</v>
-      </c>
       <c r="M77" t="n">
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P77" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D78" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10580,19 +10590,19 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M78" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -10600,7 +10610,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -10625,13 +10635,13 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -10640,13 +10650,13 @@
         <v>25</v>
       </c>
       <c r="N79" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O79" t="n">
         <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -10654,53 +10664,53 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>3</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="M80" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>12</v>
       </c>
       <c r="P80" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10708,53 +10718,53 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D81" t="n">
+        <v>6</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>10</v>
+      </c>
+      <c r="M81" t="n">
+        <v>25</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8</v>
+      </c>
+      <c r="O81" t="n">
         <v>12</v>
       </c>
-      <c r="E81" t="n">
-        <v>3</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>2</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>22</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>16</v>
-      </c>
-      <c r="O81" t="n">
-        <v>8</v>
-      </c>
       <c r="P81" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -10762,20 +10772,20 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
+        <v>31</v>
+      </c>
+      <c r="D82" t="n">
         <v>24</v>
       </c>
-      <c r="D82" t="n">
-        <v>26</v>
-      </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -10796,7 +10806,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10805,10 +10815,10 @@
         <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P82" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10816,7 +10826,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -10835,34 +10845,34 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N83" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10870,17 +10880,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -10901,45 +10911,43 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="M84" t="n">
         <v>25</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O84" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P84" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="n">
-        <v>1</v>
-      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D85" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
@@ -10960,7 +10968,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -10969,10 +10977,10 @@
         <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10980,32 +10988,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -11014,19 +11022,19 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P86" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -11034,26 +11042,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B87" t="n">
+        <v>3</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
         <v>2</v>
       </c>
-      <c r="C87" t="n">
-        <v>10</v>
-      </c>
-      <c r="D87" t="n">
-        <v>8</v>
-      </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -11068,43 +11076,45 @@
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>12</v>
+        <v>-4</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N87" t="n">
         <v>8</v>
       </c>
       <c r="O87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+      <c r="R87" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -11113,7 +11123,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -11122,19 +11132,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11142,11 +11152,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -11161,13 +11171,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -11179,16 +11189,16 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N89" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11196,14 +11206,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" t="n">
         <v>5</v>
@@ -11221,28 +11231,28 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O90" t="n">
         <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11250,17 +11260,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D91" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E91" t="n">
         <v>2</v>
@@ -11284,7 +11294,7 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -11296,7 +11306,7 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -11304,23 +11314,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11338,7 +11348,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -11347,10 +11357,10 @@
         <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -11358,17 +11368,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -11383,7 +11393,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11392,19 +11402,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
+        <v>16</v>
+      </c>
+      <c r="O93" t="n">
         <v>8</v>
       </c>
-      <c r="O93" t="n">
-        <v>4</v>
-      </c>
       <c r="P93" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11412,17 +11422,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -11437,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11446,19 +11456,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
         <v>8</v>
       </c>
-      <c r="O94" t="n">
-        <v>4</v>
-      </c>
       <c r="P94" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -11466,17 +11476,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -11491,7 +11501,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11500,39 +11510,37 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O95" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="n">
-        <v>1</v>
-      </c>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -11547,7 +11555,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11556,19 +11564,19 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
         <v>8</v>
       </c>
-      <c r="O96" t="n">
-        <v>4</v>
-      </c>
       <c r="P96" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -11576,7 +11584,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Harry Howell</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -11601,13 +11609,13 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -11616,13 +11624,13 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O97" t="n">
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -11630,17 +11638,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B98" t="n">
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -11655,7 +11663,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11664,19 +11672,19 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
         <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -11738,7 +11746,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -11769,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -11778,13 +11786,13 @@
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O100" t="n">
         <v>4</v>
       </c>
       <c r="P100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -11792,7 +11800,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Benny Howell</t>
+          <t>Tymal Mills</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -11802,7 +11810,7 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -11826,7 +11834,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -11838,10 +11846,64 @@
         <v>4</v>
       </c>
       <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Benny Howell</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
         <v>2</v>
       </c>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="n">
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11856,7 +11918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12103,12 +12165,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tom abell</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -12122,7 +12184,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>tom alsop</t>
+          <t>ollie pope</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -12170,7 +12232,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>josh fillpi</t>
+          <t>chris wood</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12189,7 +12251,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ollie pope</t>
+          <t>chris jordan</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12237,12 +12299,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>chris wood</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -12256,7 +12318,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>chris jordan</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -12304,12 +12366,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mustafizur rahman</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -12323,7 +12385,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -12371,7 +12433,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reece topley</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -12390,7 +12452,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>peter willey</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -12432,73 +12494,6 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>brydon carse</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12755,7 +12750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13860,6 +13855,96 @@
         <v>84</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>13</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>13</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>13</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>13</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>13</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>M13: Southern Brave v Birmingham Phoenix</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>305</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>90</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -662,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -804,13 +804,13 @@
         <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>22</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>232</v>
+        <v>312</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1017,13 +1017,13 @@
         <v>12</v>
       </c>
       <c r="S8" t="n">
-        <v>256</v>
+        <v>340</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>512</v>
+        <v>680</v>
       </c>
     </row>
     <row r="9">
@@ -1487,16 +1487,16 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1505,22 +1505,22 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1652,13 +1652,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18">
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
         <v>176</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1865,13 +1865,13 @@
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -2504,13 +2504,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30">
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -2717,13 +2717,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33">
@@ -3613,17 +3613,17 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>4</v>
+      </c>
+      <c r="K45" t="n">
+        <v>148</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>3</v>
       </c>
-      <c r="K45" t="n">
-        <v>76</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2</v>
-      </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -3631,22 +3631,22 @@
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S45" t="n">
-        <v>137</v>
+        <v>251</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>137</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -3711,13 +3711,13 @@
         <v>8</v>
       </c>
       <c r="S46" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="T46" t="n">
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>184</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47">
@@ -5167,13 +5167,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K67" t="n">
         <v>24</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M67" t="n">
         <v>5</v>
@@ -5188,19 +5188,19 @@
         <v>28</v>
       </c>
       <c r="Q67" t="n">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="R67" t="n">
         <v>44</v>
       </c>
       <c r="S67" t="n">
-        <v>137</v>
+        <v>224</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>137</v>
+        <v>224</v>
       </c>
     </row>
     <row r="68">
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" t="n">
         <v>15</v>
@@ -5407,13 +5407,13 @@
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="71">
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K71" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="L71" t="n">
         <v>4</v>
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="Q71" t="n">
         <v>108</v>
@@ -5478,13 +5478,13 @@
         <v>16</v>
       </c>
       <c r="S71" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>151</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72">
@@ -5589,16 +5589,16 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
         <v>6</v>
       </c>
       <c r="L73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N73" t="n">
         <v>0</v>
@@ -5610,19 +5610,19 @@
         <v>7</v>
       </c>
       <c r="Q73" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="R73" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="S73" t="n">
-        <v>129</v>
+        <v>210</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>129</v>
+        <v>210</v>
       </c>
     </row>
     <row r="74">
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6172,13 +6172,13 @@
         <v>8</v>
       </c>
       <c r="S81" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2505</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="3">
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2038</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="4">
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1994</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="5">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1746</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="6">
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1697</v>
+        <v>1800</v>
       </c>
     </row>
   </sheetData>
@@ -6386,111 +6386,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>224</v>
+      </c>
+      <c r="D2" t="n">
+        <v>131</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>312</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>12</v>
+      </c>
+      <c r="O2" t="n">
+        <v>16</v>
+      </c>
+      <c r="P2" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
-        <v>70</v>
-      </c>
-      <c r="D2" t="n">
-        <v>51</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>93</v>
-      </c>
-      <c r="M2" t="n">
-        <v>177</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>12</v>
-      </c>
-      <c r="P2" t="n">
-        <v>282</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>138</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
+        <v>93</v>
+      </c>
+      <c r="M3" t="n">
         <v>177</v>
       </c>
-      <c r="M3" t="n">
-        <v>58</v>
-      </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -6552,82 +6552,82 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>176</v>
+        <v>138</v>
       </c>
       <c r="D5" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
         <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>176</v>
       </c>
       <c r="D6" t="n">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="E6" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F6" t="n">
         <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -6642,22 +6642,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>122</v>
+        <v>243</v>
       </c>
       <c r="M6" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -6666,47 +6666,47 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>169</v>
+        <v>90</v>
       </c>
       <c r="D7" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>232</v>
+        <v>122</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -6715,40 +6715,42 @@
         <v>256</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>148</v>
+      </c>
+      <c r="D8" t="n">
+        <v>76</v>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>118</v>
-      </c>
-      <c r="D8" t="n">
-        <v>82</v>
-      </c>
-      <c r="E8" t="n">
-        <v>9</v>
-      </c>
-      <c r="F8" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
@@ -6756,108 +6758,112 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>159</v>
+        <v>205</v>
       </c>
       <c r="M8" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="M9" t="n">
-        <v>229</v>
+        <v>61</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -6866,54 +6872,52 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6922,49 +6926,49 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>184</v>
+        <v>81</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N11" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P11" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>7</v>
       </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
@@ -6978,152 +6982,150 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="N12" t="n">
         <v>8</v>
       </c>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P12" t="n">
-        <v>184</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N13" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>177</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="M14" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O14" t="n">
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>177</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7135,7 +7137,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -7144,19 +7146,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
@@ -7164,24 +7166,24 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" t="n">
         <v>8</v>
       </c>
-      <c r="F16" t="n">
-        <v>5</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
@@ -7189,86 +7191,84 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
+        <v>29</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="M17" t="n">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="N17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -7276,23 +7276,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>95</v>
+      </c>
+      <c r="D18" t="n">
+        <v>60</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
         <v>4</v>
-      </c>
-      <c r="C18" t="n">
-        <v>88</v>
-      </c>
-      <c r="D18" t="n">
-        <v>52</v>
-      </c>
-      <c r="E18" t="n">
-        <v>8</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -7304,13 +7304,13 @@
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -7319,137 +7319,139 @@
         <v>36</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P18" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>177</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>149</v>
+      </c>
+      <c r="N19" t="n">
         <v>12</v>
-      </c>
-      <c r="F19" t="n">
-        <v>5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>144</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>8</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>78</v>
+      </c>
+      <c r="D20" t="n">
+        <v>39</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>3</v>
       </c>
-      <c r="C20" t="n">
-        <v>46</v>
-      </c>
-      <c r="D20" t="n">
-        <v>34</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="M20" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>158</v>
-      </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
         <v>2</v>
@@ -7458,37 +7460,37 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>136</v>
+      </c>
+      <c r="N21" t="n">
+        <v>18</v>
+      </c>
+      <c r="O21" t="n">
         <v>16</v>
       </c>
-      <c r="M21" t="n">
-        <v>106</v>
-      </c>
-      <c r="N21" t="n">
-        <v>24</v>
-      </c>
-      <c r="O21" t="n">
-        <v>12</v>
-      </c>
       <c r="P21" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
@@ -7496,23 +7498,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7527,22 +7529,22 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O22" t="n">
         <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -7550,77 +7552,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="D23" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="M23" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D24" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7629,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7638,45 +7642,47 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>4</v>
@@ -7685,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7694,19 +7700,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M25" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N25" t="n">
+        <v>24</v>
+      </c>
+      <c r="O25" t="n">
         <v>16</v>
       </c>
-      <c r="O25" t="n">
-        <v>12</v>
-      </c>
       <c r="P25" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7714,32 +7720,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>3</v>
       </c>
       <c r="C26" t="n">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="D26" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -7748,45 +7754,43 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>12</v>
       </c>
       <c r="P26" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
+        <v>158</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="n">
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -7795,7 +7799,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -7804,19 +7808,19 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -7824,23 +7828,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
         <v>6</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -7849,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -7858,40 +7862,42 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -7909,22 +7915,22 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="M29" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7932,32 +7938,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>4</v>
       </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -7966,19 +7972,19 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>98</v>
+        <v>17</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="N30" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
@@ -7986,32 +7992,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>3</v>
       </c>
       <c r="C31" t="n">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -8020,19 +8026,19 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="M31" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8040,24 +8046,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>3</v>
       </c>
       <c r="C32" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E32" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" t="n">
         <v>7</v>
       </c>
-      <c r="F32" t="n">
-        <v>4</v>
-      </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
@@ -8065,7 +8071,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8074,45 +8080,43 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O32" t="n">
         <v>12</v>
       </c>
       <c r="P32" t="n">
-        <v>141</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -8121,7 +8125,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8130,19 +8134,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>12</v>
       </c>
       <c r="P33" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8150,32 +8154,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -8184,19 +8188,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>28</v>
+        <v>98</v>
       </c>
       <c r="M34" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P34" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8204,23 +8208,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -8229,63 +8233,63 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="n">
-        <v>137</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8294,23 +8298,21 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>122</v>
+        <v>12</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>134</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
@@ -8320,7 +8322,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -8359,10 +8361,10 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P37" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8370,55 +8372,57 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38" t="n">
+        <v>90</v>
+      </c>
+      <c r="D38" t="n">
+        <v>51</v>
+      </c>
+      <c r="E38" t="n">
+        <v>9</v>
+      </c>
+      <c r="F38" t="n">
         <v>4</v>
       </c>
-      <c r="D38" t="n">
-        <v>9</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="M38" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>131</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="n">
         <v>1</v>
       </c>
@@ -8426,56 +8430,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>3</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
+        <v>9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M39" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="N39" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="O39" t="n">
         <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -8864,32 +8870,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
         <v>3</v>
       </c>
-      <c r="C47" t="n">
-        <v>75</v>
-      </c>
-      <c r="D47" t="n">
-        <v>54</v>
-      </c>
-      <c r="E47" t="n">
-        <v>6</v>
-      </c>
-      <c r="F47" t="n">
-        <v>5</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8898,19 +8904,19 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P47" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
@@ -8918,53 +8924,53 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>60</v>
+      </c>
+      <c r="D48" t="n">
+        <v>38</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
         <v>3</v>
       </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="M48" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O48" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8972,32 +8978,32 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B49" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
         <v>3</v>
       </c>
-      <c r="C49" t="n">
-        <v>69</v>
-      </c>
-      <c r="D49" t="n">
-        <v>46</v>
-      </c>
-      <c r="E49" t="n">
-        <v>6</v>
-      </c>
-      <c r="F49" t="n">
-        <v>3</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
       <c r="H49" t="n">
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -9006,57 +9012,53 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>3</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>3</v>
       </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1</v>
-      </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
@@ -9064,19 +9066,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M50" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O50" t="n">
         <v>12</v>
       </c>
       <c r="P50" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9084,23 +9086,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D51" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -9118,7 +9120,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -9127,40 +9129,38 @@
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P51" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
         <v>3</v>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
@@ -9174,10 +9174,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N52" t="n">
         <v>8</v>
@@ -9186,36 +9186,34 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -9230,10 +9228,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="M53" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -9242,34 +9240,38 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>97</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -9284,100 +9286,104 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="M54" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>3</v>
       </c>
       <c r="C55" t="n">
+        <v>53</v>
+      </c>
+      <c r="D55" t="n">
+        <v>29</v>
+      </c>
+      <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="n">
         <v>3</v>
       </c>
-      <c r="D55" t="n">
-        <v>6</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="M55" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>12</v>
       </c>
       <c r="P55" t="n">
-        <v>95</v>
-      </c>
-      <c r="Q55" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1</v>
+      </c>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -9392,19 +9398,19 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="M56" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9412,32 +9418,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="n">
+        <v>7</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
         <v>3</v>
       </c>
-      <c r="C57" t="n">
-        <v>53</v>
-      </c>
-      <c r="D57" t="n">
-        <v>30</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>7</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -9446,19 +9452,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
         <v>8</v>
       </c>
-      <c r="O57" t="n">
-        <v>12</v>
-      </c>
       <c r="P57" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9466,53 +9472,53 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>3</v>
       </c>
       <c r="C58" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N58" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O58" t="n">
         <v>12</v>
       </c>
       <c r="P58" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9520,17 +9526,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>3</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -9554,10 +9560,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -9566,7 +9572,7 @@
         <v>12</v>
       </c>
       <c r="P59" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -9574,32 +9580,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -9608,19 +9614,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="M60" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P60" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9628,17 +9634,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D61" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
@@ -9662,7 +9668,7 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -9671,10 +9677,10 @@
         <v>8</v>
       </c>
       <c r="O61" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9682,32 +9688,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
         <v>3</v>
       </c>
-      <c r="C62" t="n">
-        <v>39</v>
-      </c>
-      <c r="D62" t="n">
-        <v>20</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" t="n">
-        <v>5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -9716,75 +9722,73 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
         <v>16</v>
       </c>
-      <c r="O62" t="n">
-        <v>12</v>
-      </c>
       <c r="P62" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="n">
-        <v>1</v>
-      </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
         <v>4</v>
       </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>69</v>
-      </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P63" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
@@ -9792,32 +9796,32 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -9826,19 +9830,19 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="M64" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P64" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
@@ -9846,136 +9850,136 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D65" t="n">
+        <v>20</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
         <v>5</v>
       </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0</v>
-      </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
         <v>2</v>
       </c>
-      <c r="H65" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="M65" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O65" t="n">
         <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="N66" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>3</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="D67" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -9990,10 +9994,10 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="M67" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
         <v>0</v>
@@ -10002,7 +10006,7 @@
         <v>12</v>
       </c>
       <c r="P67" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -10010,20 +10014,20 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="n">
         <v>3</v>
       </c>
-      <c r="C68" t="n">
-        <v>11</v>
-      </c>
-      <c r="D68" t="n">
-        <v>7</v>
-      </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -10044,19 +10048,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P68" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -10064,32 +10068,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>3</v>
       </c>
       <c r="C69" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
         <v>2</v>
       </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10098,19 +10102,19 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N69" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O69" t="n">
         <v>12</v>
       </c>
       <c r="P69" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10118,86 +10122,88 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="D70" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="M70" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O70" t="n">
         <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B71" t="n">
         <v>3</v>
       </c>
       <c r="C71" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D71" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="E71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10206,19 +10212,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>12</v>
       </c>
       <c r="P71" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10226,32 +10232,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B72" t="n">
+        <v>3</v>
+      </c>
+      <c r="C72" t="n">
+        <v>7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
         <v>2</v>
       </c>
-      <c r="C72" t="n">
-        <v>23</v>
-      </c>
-      <c r="D72" t="n">
-        <v>14</v>
-      </c>
-      <c r="E72" t="n">
-        <v>4</v>
-      </c>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>0</v>
-      </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -10260,54 +10266,52 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N72" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P72" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="n">
-        <v>1</v>
-      </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B73" t="n">
         <v>3</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -10316,19 +10320,19 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="M73" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O73" t="n">
         <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10336,32 +10340,32 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -10370,37 +10374,39 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="M74" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O74" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P74" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -10409,63 +10415,61 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="n">
-        <v>1</v>
-      </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B76" t="n">
         <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -10480,10 +10484,10 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N76" t="n">
         <v>0</v>
@@ -10492,7 +10496,7 @@
         <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
@@ -10500,53 +10504,53 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B77" t="n">
+        <v>4</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
         <v>3</v>
       </c>
-      <c r="C77" t="n">
-        <v>27</v>
-      </c>
-      <c r="D77" t="n">
-        <v>22</v>
-      </c>
-      <c r="E77" t="n">
-        <v>3</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>2</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>30</v>
-      </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N77" t="n">
+        <v>14</v>
+      </c>
+      <c r="O77" t="n">
         <v>16</v>
       </c>
-      <c r="O77" t="n">
-        <v>12</v>
-      </c>
       <c r="P77" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
@@ -10556,86 +10560,88 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D78" t="n">
+        <v>22</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
         <v>30</v>
       </c>
-      <c r="E78" t="n">
-        <v>5</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>53</v>
-      </c>
       <c r="M78" t="n">
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -10644,16 +10650,16 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M79" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P79" t="n">
         <v>57</v>
@@ -10664,33 +10670,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B80" t="n">
+        <v>2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" t="n">
         <v>3</v>
       </c>
-      <c r="C80" t="n">
-        <v>30</v>
-      </c>
-      <c r="D80" t="n">
-        <v>21</v>
-      </c>
-      <c r="E80" t="n">
-        <v>1</v>
-      </c>
-      <c r="F80" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" t="n">
-        <v>1</v>
-      </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
@@ -10698,16 +10704,16 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N80" t="n">
+        <v>24</v>
+      </c>
+      <c r="O80" t="n">
         <v>8</v>
-      </c>
-      <c r="O80" t="n">
-        <v>12</v>
       </c>
       <c r="P80" t="n">
         <v>57</v>
@@ -10718,32 +10724,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -10752,19 +10758,19 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="M81" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P81" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -10772,26 +10778,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D82" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -10806,19 +10812,19 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N82" t="n">
         <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P82" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10826,26 +10832,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -10857,22 +10863,22 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M83" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10934,53 +10940,53 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B85" t="n">
         <v>2</v>
       </c>
       <c r="C85" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O85" t="n">
         <v>8</v>
       </c>
       <c r="P85" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -11152,17 +11158,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -11171,13 +11177,13 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -11186,19 +11192,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M89" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P89" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11260,26 +11266,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -11294,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -11306,7 +11312,7 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -11314,23 +11320,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D92" t="n">
         <v>19</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -11348,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -11360,7 +11366,7 @@
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -11368,23 +11374,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11393,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11402,19 +11408,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11422,17 +11428,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>2</v>
       </c>
       <c r="C94" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -11447,7 +11453,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11456,19 +11462,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O94" t="n">
         <v>8</v>
       </c>
       <c r="P94" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -12750,7 +12756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13945,6 +13951,96 @@
         <v>305</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>14</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>14</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>14</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>14</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>14</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>M14: Manchester Super Giants v Trent Rockets</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1150,7 +1150,7 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1159,13 +1159,13 @@
         <v>48</v>
       </c>
       <c r="S10" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>116</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -1203,16 +1203,16 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -1221,22 +1221,22 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="S11" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
         <v>24</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1298,16 +1298,16 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1372,13 +1372,13 @@
         <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1714,22 +1714,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>54</v>
+        <v>134</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S18" t="n">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>148</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -2069,22 +2069,22 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="Q23" t="n">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>282</v>
+        <v>372</v>
       </c>
     </row>
     <row r="24">
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -2211,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="Q25" t="n">
         <v>61</v>
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="S25" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
         <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2353,22 +2353,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="n">
         <v>108</v>
       </c>
       <c r="R27" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S27" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>280</v>
+        <v>326</v>
       </c>
     </row>
     <row r="28">
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="L28" t="n">
         <v>5</v>
@@ -2424,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="Q28" t="n">
         <v>136</v>
@@ -2433,13 +2433,13 @@
         <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
         <v>12</v>
@@ -2788,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34">
@@ -2903,13 +2903,13 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35" t="n">
         <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
@@ -2924,19 +2924,19 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="R35" t="n">
         <v>14</v>
       </c>
       <c r="S35" t="n">
-        <v>66</v>
+        <v>196</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>66</v>
+        <v>196</v>
       </c>
     </row>
     <row r="36">
@@ -2974,13 +2974,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2989,25 +2989,25 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
-        <v>146</v>
+        <v>209</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>146</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
         <v>1</v>
@@ -3072,13 +3072,13 @@
         <v>8</v>
       </c>
       <c r="S37" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38">
@@ -3116,40 +3116,40 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
       </c>
       <c r="L38" t="n">
+        <v>4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
         <v>2</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
       </c>
       <c r="P38" t="n">
         <v>7</v>
       </c>
       <c r="Q38" t="n">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S38" t="n">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>78</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39">
@@ -3187,14 +3187,14 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>3</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>2</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -3205,22 +3205,22 @@
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q39" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3350,19 +3350,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>149</v>
+        <v>210</v>
       </c>
       <c r="R41" t="n">
         <v>12</v>
       </c>
       <c r="S41" t="n">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>177</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42">
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q42" t="n">
         <v>53</v>
@@ -3427,13 +3427,13 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="T42" t="n">
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -3566,16 +3566,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3782,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48">
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3924,13 +3924,13 @@
         <v>36</v>
       </c>
       <c r="S49" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50">
@@ -3968,17 +3968,17 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>4</v>
+      </c>
+      <c r="K50" t="n">
+        <v>76</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>3</v>
       </c>
-      <c r="K50" t="n">
-        <v>56</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
@@ -3986,22 +3986,22 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="S50" t="n">
-        <v>92</v>
+        <v>135</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>92</v>
+        <v>135</v>
       </c>
     </row>
     <row r="51">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>14</v>
       </c>
       <c r="S51" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
     </row>
     <row r="52">
@@ -4093,29 +4093,33 @@
       <c r="E52" t="b">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>tom moores</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>tom kohler cadmore</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tom Kohler-Cadmore</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
@@ -4124,22 +4128,22 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -4315,16 +4319,16 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4333,22 +4337,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="S55" t="n">
-        <v>146</v>
+        <v>210</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>146</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56">
@@ -4457,10 +4461,10 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K57" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -4475,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4484,13 +4488,13 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="T57" t="n">
         <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58">
@@ -4528,10 +4532,10 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -4546,7 +4550,7 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>129</v>
+        <v>177</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4555,13 +4559,13 @@
         <v>36</v>
       </c>
       <c r="S58" t="n">
-        <v>177</v>
+        <v>229</v>
       </c>
       <c r="T58" t="n">
         <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>177</v>
+        <v>229</v>
       </c>
     </row>
     <row r="59">
@@ -4599,16 +4603,16 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -4617,22 +4621,22 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="S59" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60">
@@ -4670,10 +4674,10 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K60" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4688,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q60" t="n">
         <v>0</v>
@@ -4697,13 +4701,13 @@
         <v>8</v>
       </c>
       <c r="S60" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="T60" t="n">
         <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61">
@@ -4812,13 +4816,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4830,22 +4834,22 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q62" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
     </row>
     <row r="63">
@@ -4883,16 +4887,16 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
@@ -4901,22 +4905,22 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="Q63" t="n">
         <v>94</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S63" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64">
@@ -4954,16 +4958,16 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>4</v>
+      </c>
+      <c r="K64" t="n">
+        <v>145</v>
+      </c>
+      <c r="L64" t="n">
         <v>3</v>
       </c>
-      <c r="K64" t="n">
-        <v>138</v>
-      </c>
-      <c r="L64" t="n">
-        <v>2</v>
-      </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -4972,22 +4976,22 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Q64" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="R64" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S64" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
     </row>
     <row r="65">
@@ -5096,13 +5100,13 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" t="n">
+        <v>44</v>
+      </c>
+      <c r="L66" t="n">
         <v>3</v>
-      </c>
-      <c r="K66" t="n">
-        <v>26</v>
-      </c>
-      <c r="L66" t="n">
-        <v>2</v>
       </c>
       <c r="M66" t="n">
         <v>2</v>
@@ -5114,22 +5118,22 @@
         <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="Q66" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="R66" t="n">
         <v>22</v>
       </c>
       <c r="S66" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="T66" t="n">
         <v>1</v>
       </c>
       <c r="U66" t="n">
-        <v>117</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67">
@@ -5238,13 +5242,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
         <v>4</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5253,25 +5257,25 @@
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P68" t="n">
         <v>4</v>
       </c>
       <c r="Q68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R68" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="S68" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>47</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
@@ -5505,26 +5509,30 @@
       <c r="E72" t="b">
         <v>0</v>
       </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>chris jordan</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>chris wood</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Chris Wood</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -5536,22 +5544,22 @@
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="T72" t="n">
         <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="73">
@@ -5727,16 +5735,16 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K75" t="n">
         <v>15</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -5748,19 +5756,19 @@
         <v>17</v>
       </c>
       <c r="Q75" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="R75" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="S75" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76">
@@ -5798,13 +5806,13 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
         <v>1</v>
@@ -5816,22 +5824,22 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="Q76" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="R76" t="n">
         <v>8</v>
       </c>
       <c r="S76" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="T76" t="n">
         <v>1</v>
       </c>
       <c r="U76" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77">
@@ -6222,7 +6230,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2523</v>
+        <v>2804</v>
       </c>
     </row>
     <row r="3">
@@ -6231,11 +6239,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sd</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2156</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="4">
@@ -6244,11 +6252,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>sd</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2153</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="5">
@@ -6257,11 +6265,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1971</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="6">
@@ -6270,11 +6278,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1800</v>
+        <v>2145</v>
       </c>
     </row>
   </sheetData>
@@ -6288,7 +6296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6386,26 +6394,26 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Marcus Stoinis</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>224</v>
+        <v>73</v>
       </c>
       <c r="D2" t="n">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -6414,185 +6422,185 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>312</v>
+        <v>96</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>16</v>
       </c>
       <c r="P2" t="n">
-        <v>340</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marcus Stoinis</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>224</v>
+      </c>
+      <c r="D3" t="n">
+        <v>131</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>312</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16</v>
+      </c>
+      <c r="P3" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D3" t="n">
-        <v>51</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>93</v>
-      </c>
-      <c r="M3" t="n">
-        <v>177</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>12</v>
-      </c>
-      <c r="P3" t="n">
-        <v>282</v>
-      </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>145</v>
+      </c>
+      <c r="D4" t="n">
+        <v>83</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>173</v>
-      </c>
-      <c r="D4" t="n">
-        <v>87</v>
-      </c>
-      <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" t="n">
-        <v>14</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>269</v>
+        <v>313</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>138</v>
+        <v>173</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>177</v>
+        <v>249</v>
       </c>
       <c r="M5" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>12</v>
@@ -6601,7 +6609,7 @@
         <v>269</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
@@ -6666,26 +6674,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6700,23 +6708,21 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="N7" t="n">
         <v>8</v>
       </c>
       <c r="O7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
         <v>256</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>1</v>
       </c>
@@ -6724,53 +6730,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -6786,13 +6792,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E9" t="n">
         <v>9</v>
@@ -6816,7 +6822,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M9" t="n">
         <v>61</v>
@@ -6825,10 +6831,10 @@
         <v>14</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
@@ -6838,86 +6844,90 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="M10" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
         <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>245</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
+        <v>251</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6926,33 +6936,31 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>136</v>
+        <v>229</v>
       </c>
       <c r="N11" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6973,28 +6981,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -7002,26 +7010,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -7033,22 +7041,22 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="M13" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P13" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
@@ -7056,32 +7064,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -7090,108 +7098,108 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O14" t="n">
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
+        <v>130</v>
+      </c>
+      <c r="D15" t="n">
+        <v>83</v>
+      </c>
+      <c r="E15" t="n">
+        <v>15</v>
+      </c>
+      <c r="F15" t="n">
         <v>6</v>
       </c>
-      <c r="D15" t="n">
-        <v>4</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="M15" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O15" t="n">
         <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -7200,54 +7208,52 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N16" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
       </c>
       <c r="P16" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>133</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -7256,40 +7262,42 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>184</v>
       </c>
       <c r="M17" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O17" t="n">
         <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>182</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>224</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
         <v>4</v>
@@ -7301,51 +7309,49 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>177</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -7357,28 +7363,28 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M19" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
@@ -7386,245 +7392,243 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="O20" t="n">
         <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>4</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>130</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="M21" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
         <v>16</v>
       </c>
       <c r="P21" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
         <v>5</v>
       </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
         <v>3</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>116</v>
-      </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="N22" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>168</v>
+        <v>196</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>4</v>
       </c>
       <c r="C23" t="n">
+        <v>38</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>42</v>
+      </c>
+      <c r="M23" t="n">
         <v>108</v>
       </c>
-      <c r="D23" t="n">
-        <v>72</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>144</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -7633,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7642,56 +7646,52 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>168</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7700,19 +7700,19 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="M25" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N25" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7720,23 +7720,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D26" t="n">
         <v>34</v>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
@@ -7745,28 +7745,28 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M26" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
@@ -7774,23 +7774,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D27" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -7802,52 +7802,56 @@
         <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -7859,51 +7863,49 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O28" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P28" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -7915,55 +7917,57 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>28</v>
+        <v>155</v>
       </c>
       <c r="M29" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>16</v>
       </c>
       <c r="P29" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -7972,43 +7976,45 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="M30" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>149</v>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -8026,7 +8032,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -8035,34 +8041,38 @@
         <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P31" t="n">
-        <v>148</v>
-      </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -8071,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8080,43 +8090,45 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O32" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P32" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q32" t="inlineStr"/>
+        <v>166</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1</v>
+      </c>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
         <v>4</v>
@@ -8125,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8134,19 +8146,19 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M33" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P33" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8154,32 +8166,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -8188,19 +8200,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N34" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O34" t="n">
         <v>16</v>
       </c>
       <c r="P34" t="n">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8208,88 +8220,86 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
-        <v>94</v>
-      </c>
-      <c r="D35" t="n">
-        <v>64</v>
-      </c>
-      <c r="E35" t="n">
-        <v>7</v>
-      </c>
-      <c r="F35" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
-        <v>141</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8298,37 +8308,41 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="M36" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="n">
-        <v>140</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -8337,34 +8351,34 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="O37" t="n">
         <v>16</v>
       </c>
       <c r="P37" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8372,26 +8386,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E38" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -8403,80 +8417,76 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>31</v>
+      </c>
+      <c r="D39" t="n">
+        <v>25</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="C39" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" t="n">
-        <v>9</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>4</v>
-      </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="M39" t="n">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="N39" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
@@ -8486,32 +8496,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8520,54 +8530,52 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="M40" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>64</v>
+        <v>99</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8576,40 +8584,42 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="M41" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>124</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -8630,75 +8640,73 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>-2</v>
+        <v>17</v>
       </c>
       <c r="M42" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P42" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>4</v>
+      </c>
+      <c r="C43" t="n">
+        <v>69</v>
+      </c>
+      <c r="D43" t="n">
+        <v>58</v>
+      </c>
+      <c r="E43" t="n">
         <v>3</v>
       </c>
-      <c r="C43" t="n">
-        <v>26</v>
-      </c>
-      <c r="D43" t="n">
-        <v>20</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
       <c r="F43" t="n">
+        <v>6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>3</v>
       </c>
-      <c r="G43" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
-        <v>33</v>
+        <v>84</v>
       </c>
       <c r="M43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="O43" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P43" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8706,23 +8714,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="D44" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -8737,22 +8745,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>56</v>
+        <v>111</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
@@ -8760,53 +8768,53 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>4</v>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>104</v>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>92</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>17</v>
+        <v>129</v>
       </c>
       <c r="M45" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>16</v>
       </c>
       <c r="P45" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8814,88 +8822,86 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="n">
+        <v>7</v>
+      </c>
+      <c r="M46" t="n">
+        <v>106</v>
+      </c>
+      <c r="N46" t="n">
         <v>12</v>
-      </c>
-      <c r="D46" t="n">
-        <v>7</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>12</v>
-      </c>
-      <c r="M46" t="n">
-        <v>83</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8904,73 +8910,77 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M47" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>16</v>
       </c>
       <c r="P47" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="N48" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8978,33 +8988,33 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="D49" t="n">
+        <v>43</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
         <v>5</v>
       </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
       <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>3</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
@@ -9012,19 +9022,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="M49" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O49" t="n">
         <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -9032,32 +9042,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="D50" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -9066,19 +9076,19 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N50" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P50" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
@@ -9086,80 +9096,82 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>3</v>
       </c>
       <c r="C51" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O51" t="n">
         <v>12</v>
       </c>
       <c r="P51" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>3</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -9174,10 +9186,10 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="M52" t="n">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="N52" t="n">
         <v>8</v>
@@ -9186,7 +9198,7 @@
         <v>12</v>
       </c>
       <c r="P52" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -9194,26 +9206,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>3</v>
       </c>
       <c r="C53" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -9228,10 +9240,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>94</v>
+        <v>-2</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -9240,11 +9252,9 @@
         <v>12</v>
       </c>
       <c r="P53" t="n">
-        <v>106</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>1</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="n">
         <v>1</v>
       </c>
@@ -9252,27 +9262,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
         <v>3</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
@@ -9286,19 +9296,19 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
+        <v>12</v>
+      </c>
+      <c r="M54" t="n">
         <v>83</v>
       </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P54" t="n">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
@@ -9308,27 +9318,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>4</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>3</v>
       </c>
-      <c r="C55" t="n">
-        <v>53</v>
-      </c>
-      <c r="D55" t="n">
-        <v>29</v>
-      </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
@@ -9342,75 +9352,73 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N55" t="n">
         <v>8</v>
       </c>
       <c r="O55" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P55" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>86</v>
+      </c>
+      <c r="N56" t="n">
         <v>8</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>80</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
@@ -9418,53 +9426,53 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" t="n">
+        <v>60</v>
+      </c>
+      <c r="D57" t="n">
+        <v>38</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6</v>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
         <v>2</v>
       </c>
-      <c r="C57" t="n">
-        <v>7</v>
-      </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="M57" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O57" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P57" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9472,53 +9480,53 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
         <v>3</v>
       </c>
-      <c r="C58" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>6</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" t="n">
-        <v>3</v>
-      </c>
       <c r="M58" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="N58" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O58" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9526,17 +9534,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -9560,43 +9568,45 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="M59" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B60" t="n">
         <v>3</v>
       </c>
       <c r="C60" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F60" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -9605,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -9614,19 +9624,19 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>12</v>
       </c>
       <c r="P60" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9634,23 +9644,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D61" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -9659,7 +9669,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -9674,13 +9684,13 @@
         <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
         <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9688,7 +9698,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -9713,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -9725,16 +9735,16 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O62" t="n">
         <v>16</v>
       </c>
       <c r="P62" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9742,32 +9752,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9776,97 +9786,103 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="M63" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
+        <v>106</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B64" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" t="n">
+        <v>66</v>
+      </c>
+      <c r="D64" t="n">
+        <v>44</v>
+      </c>
+      <c r="E64" t="n">
+        <v>8</v>
+      </c>
+      <c r="F64" t="n">
+        <v>3</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>81</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>20</v>
+      </c>
+      <c r="P64" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="n">
         <v>2</v>
       </c>
-      <c r="C64" t="n">
-        <v>52</v>
-      </c>
-      <c r="D64" t="n">
-        <v>28</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" t="n">
-        <v>5</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>68</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="n">
-        <v>8</v>
-      </c>
-      <c r="O64" t="n">
-        <v>8</v>
-      </c>
-      <c r="P64" t="n">
-        <v>84</v>
-      </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B65" t="n">
         <v>3</v>
       </c>
       <c r="C65" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -9875,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -9884,48 +9900,48 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O65" t="n">
         <v>12</v>
       </c>
       <c r="P65" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="n">
-        <v>1</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -9940,10 +9956,10 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
@@ -9952,31 +9968,33 @@
         <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D67" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -9994,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -10003,10 +10021,10 @@
         <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P67" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -10014,27 +10032,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
@@ -10048,19 +10066,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M68" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P68" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -10068,32 +10086,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10102,103 +10120,103 @@
         <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="M69" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>3</v>
       </c>
       <c r="C70" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D70" t="n">
         <v>30</v>
       </c>
       <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>72</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="n">
         <v>8</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" t="n">
-        <v>51</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="n">
-        <v>14</v>
       </c>
       <c r="O70" t="n">
         <v>12</v>
       </c>
       <c r="P70" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B71" t="n">
+        <v>4</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
         <v>3</v>
       </c>
-      <c r="C71" t="n">
-        <v>11</v>
-      </c>
-      <c r="D71" t="n">
-        <v>7</v>
-      </c>
-      <c r="E71" t="n">
-        <v>2</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>2</v>
-      </c>
       <c r="H71" t="n">
         <v>0</v>
       </c>
@@ -10212,19 +10230,19 @@
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N71" t="n">
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P71" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10232,23 +10250,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>2</v>
@@ -10257,7 +10275,7 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -10266,19 +10284,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M72" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O72" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P72" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -10286,24 +10304,24 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D73" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
         <v>5</v>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
@@ -10320,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -10329,10 +10347,10 @@
         <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P73" t="n">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10340,89 +10358,87 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
         <v>2</v>
       </c>
-      <c r="C74" t="n">
-        <v>23</v>
-      </c>
-      <c r="D74" t="n">
-        <v>14</v>
-      </c>
-      <c r="E74" t="n">
-        <v>4</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0</v>
-      </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N74" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="O74" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P74" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B75" t="n">
         <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
         <v>2</v>
       </c>
-      <c r="H75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" t="n">
-        <v>0</v>
-      </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
@@ -10430,37 +10446,39 @@
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M75" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O75" t="n">
         <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
         <v>2</v>
       </c>
       <c r="D76" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -10475,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10484,37 +10502,39 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
+        <v>-2</v>
+      </c>
+      <c r="M76" t="n">
+        <v>58</v>
+      </c>
+      <c r="N76" t="n">
+        <v>8</v>
+      </c>
+      <c r="O76" t="n">
+        <v>16</v>
+      </c>
+      <c r="P76" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="n">
         <v>2</v>
       </c>
-      <c r="M76" t="n">
-        <v>53</v>
-      </c>
-      <c r="N76" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" t="n">
-        <v>12</v>
-      </c>
-      <c r="P76" t="n">
-        <v>67</v>
-      </c>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -10523,69 +10543,67 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="N77" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>16</v>
       </c>
       <c r="P77" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>1</v>
-      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>3</v>
       </c>
       <c r="C78" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -10594,24 +10612,22 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N78" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>12</v>
       </c>
       <c r="P78" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="n">
-        <v>1</v>
-      </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10620,19 +10636,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D79" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -10650,7 +10666,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -10659,10 +10675,10 @@
         <v>8</v>
       </c>
       <c r="O79" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P79" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
@@ -10670,32 +10686,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B80" t="n">
+        <v>4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>9</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
         <v>2</v>
       </c>
-      <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>1</v>
-      </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -10704,19 +10720,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M80" t="n">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N80" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P80" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10724,80 +10740,82 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D81" t="n">
+        <v>22</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>2</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
         <v>30</v>
       </c>
-      <c r="E81" t="n">
-        <v>5</v>
-      </c>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>53</v>
-      </c>
       <c r="M81" t="n">
         <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P81" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B82" t="n">
         <v>3</v>
       </c>
       <c r="C82" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -10812,10 +10830,10 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="M82" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
         <v>8</v>
@@ -10824,7 +10842,7 @@
         <v>12</v>
       </c>
       <c r="P82" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10832,53 +10850,53 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>2</v>
       </c>
       <c r="C83" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>25</v>
+      </c>
+      <c r="N83" t="n">
         <v>24</v>
-      </c>
-      <c r="E83" t="n">
-        <v>5</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>36</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="n">
-        <v>8</v>
       </c>
       <c r="O83" t="n">
         <v>8</v>
       </c>
       <c r="P83" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10886,26 +10904,26 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D84" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -10917,22 +10935,22 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="M84" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P84" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr"/>
@@ -10940,53 +10958,53 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B85" t="n">
+        <v>4</v>
+      </c>
+      <c r="C85" t="n">
+        <v>24</v>
+      </c>
+      <c r="D85" t="n">
+        <v>26</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
         <v>2</v>
       </c>
-      <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" t="n">
-        <v>1</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" t="n">
-        <v>1</v>
-      </c>
       <c r="J85" t="n">
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O85" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P85" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -10994,17 +11012,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B86" t="n">
         <v>3</v>
       </c>
       <c r="C86" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D86" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -11013,7 +11031,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -11028,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
+        <v>10</v>
+      </c>
+      <c r="M86" t="n">
         <v>25</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
       </c>
       <c r="N86" t="n">
         <v>8</v>
@@ -11040,7 +11058,7 @@
         <v>12</v>
       </c>
       <c r="P86" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -11048,17 +11066,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -11079,57 +11097,55 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>25</v>
       </c>
       <c r="N87" t="n">
+        <v>14</v>
+      </c>
+      <c r="O87" t="n">
         <v>8</v>
       </c>
-      <c r="O87" t="n">
-        <v>12</v>
-      </c>
       <c r="P87" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="n">
-        <v>2</v>
-      </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -11138,19 +11154,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="N88" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P88" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11158,17 +11174,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -11183,7 +11199,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -11192,19 +11208,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
+        <v>32</v>
+      </c>
+      <c r="O89" t="n">
         <v>8</v>
       </c>
-      <c r="O89" t="n">
-        <v>12</v>
-      </c>
       <c r="P89" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11212,17 +11228,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>3</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D90" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11237,7 +11253,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -11246,19 +11262,19 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M90" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O90" t="n">
         <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11320,33 +11336,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
         <v>2</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
@@ -11354,19 +11370,19 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P92" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -11374,23 +11390,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B93" t="n">
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D93" t="n">
         <v>19</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -11408,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
@@ -11420,7 +11436,7 @@
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11428,23 +11444,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11453,7 +11469,7 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -11462,19 +11478,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -11482,17 +11498,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -11507,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11516,19 +11532,19 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
+        <v>16</v>
+      </c>
+      <c r="O95" t="n">
         <v>8</v>
       </c>
-      <c r="O95" t="n">
-        <v>4</v>
-      </c>
       <c r="P95" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -11536,17 +11552,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B96" t="n">
         <v>2</v>
       </c>
       <c r="C96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -11567,22 +11583,22 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O96" t="n">
         <v>8</v>
       </c>
       <c r="P96" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -11590,17 +11606,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Harry Howell</t>
+          <t>Moeen Ali</t>
         </is>
       </c>
       <c r="B97" t="n">
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -11624,7 +11640,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M97" t="n">
         <v>0</v>
@@ -11636,7 +11652,7 @@
         <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -11644,11 +11660,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -11669,13 +11685,13 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -11684,13 +11700,13 @@
         <v>0</v>
       </c>
       <c r="N98" t="n">
+        <v>12</v>
+      </c>
+      <c r="O98" t="n">
         <v>8</v>
       </c>
-      <c r="O98" t="n">
-        <v>4</v>
-      </c>
       <c r="P98" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -11698,17 +11714,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>1</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -11723,28 +11739,28 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
         <v>4</v>
       </c>
       <c r="P99" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -11752,17 +11768,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -11783,22 +11799,22 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P100" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -11806,17 +11822,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Tom Kohler-Cadmore</t>
         </is>
       </c>
       <c r="B101" t="n">
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -11831,7 +11847,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11840,19 +11856,19 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O101" t="n">
         <v>4</v>
       </c>
       <c r="P101" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -11860,56 +11876,218 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>Ed Barnard</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>8</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Harry Howell</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
+        <v>8</v>
+      </c>
+      <c r="O103" t="n">
+        <v>4</v>
+      </c>
+      <c r="P103" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
+        <v>4</v>
+      </c>
+      <c r="P104" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
         <v>-2</v>
       </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
-        <v>4</v>
-      </c>
-      <c r="P102" t="n">
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>4</v>
+      </c>
+      <c r="P105" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="n">
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11924,7 +12102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12104,12 +12282,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tom kohler</t>
+          <t>josh fillpi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
@@ -12123,7 +12301,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>tom moores</t>
+          <t>ollie pope</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -12171,12 +12349,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>josh fillpi</t>
+          <t>mustafizur rahman</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>ssw</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -12190,7 +12368,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ollie pope</t>
+          <t>sam curran</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -12238,7 +12416,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>chris wood</t>
+          <t>reece topley</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -12257,7 +12435,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>chris jordan</t>
+          <t>peter willey</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12305,12 +12483,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mustafizur rahman</t>
+          <t>bradley currie</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ssw</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -12324,7 +12502,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>sam curran</t>
+          <t>scott currie</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -12366,140 +12544,6 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>reece topley</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>peter willey</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>bradley currie</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>lg</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>scott currie</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>no_stats_yet</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12756,7 +12800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14041,6 +14085,186 @@
         <v>18</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>15</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>15</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>15</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>15</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>M15: Birmingham Phoenix v Welsh Fire</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>16</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>16</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>16</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>16</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>M16: London Spirit v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>195</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -564,16 +564,16 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -582,22 +582,22 @@
         <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="S2" t="n">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="T2" t="n">
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>346</v>
+        <v>534</v>
       </c>
     </row>
     <row r="3">
@@ -635,10 +635,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -662,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -804,13 +804,13 @@
         <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -866,22 +866,22 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S6" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -946,13 +946,13 @@
         <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8">
@@ -990,10 +990,10 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1002,28 +1002,28 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="S8" t="n">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>680</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>99</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15">
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="S15" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16">
@@ -1625,16 +1625,16 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -1643,22 +1643,22 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S17" t="n">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>96</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18">
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>144</v>
+        <v>179</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1794,13 +1794,13 @@
         <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>168</v>
+        <v>207</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>168</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20">
@@ -1838,16 +1838,16 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>176</v>
+        <v>240</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1856,22 +1856,22 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>243</v>
+        <v>331</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S20" t="n">
-        <v>267</v>
+        <v>367</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>267</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1998,7 +1998,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2007,13 +2007,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>106</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
@@ -2122,17 +2122,17 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>113</v>
+      </c>
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="K24" t="n">
-        <v>90</v>
-      </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -2140,22 +2140,22 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="Q24" t="n">
         <v>114</v>
       </c>
       <c r="R24" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="S24" t="n">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="T24" t="n">
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>512</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
         <v>0</v>
@@ -2282,22 +2282,22 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="S26" t="n">
-        <v>224</v>
+        <v>348</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>224</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27">
@@ -2477,13 +2477,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2495,22 +2495,22 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>79</v>
+        <v>146</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>79</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
       </c>
       <c r="L30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2569,19 +2569,19 @@
         <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>94</v>
+        <v>159</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>94</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2640,19 +2640,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>245</v>
+        <v>274</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>245</v>
+        <v>274</v>
       </c>
     </row>
     <row r="32">
@@ -2690,13 +2690,13 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2708,22 +2708,22 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>119</v>
+        <v>180</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>136</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33">
@@ -2832,16 +2832,16 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -2853,19 +2853,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R34" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="S34" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="T34" t="n">
         <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35">
@@ -3471,16 +3471,16 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -3492,19 +3492,19 @@
         <v>-2</v>
       </c>
       <c r="Q43" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S43" t="n">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>121</v>
+        <v>166</v>
       </c>
     </row>
     <row r="44">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -3640,13 +3640,13 @@
         <v>30</v>
       </c>
       <c r="S45" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="T45" t="n">
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
         <v>75</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3853,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="49">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4772,13 +4772,13 @@
         <v>8</v>
       </c>
       <c r="S61" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>98</v>
+        <v>118</v>
       </c>
     </row>
     <row r="62">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5056,13 +5056,13 @@
         <v>8</v>
       </c>
       <c r="S65" t="n">
-        <v>269</v>
+        <v>325</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>269</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66">
@@ -5171,13 +5171,13 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K67" t="n">
         <v>24</v>
       </c>
       <c r="L67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M67" t="n">
         <v>5</v>
@@ -5192,19 +5192,19 @@
         <v>28</v>
       </c>
       <c r="Q67" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="R67" t="n">
         <v>44</v>
       </c>
       <c r="S67" t="n">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>224</v>
+        <v>253</v>
       </c>
     </row>
     <row r="68">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
         <v>1</v>
       </c>
       <c r="P69" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q69" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="R69" t="n">
         <v>6</v>
       </c>
       <c r="S69" t="n">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>153</v>
+        <v>211</v>
       </c>
     </row>
     <row r="70">
@@ -5384,13 +5384,13 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
@@ -5402,22 +5402,22 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q70" t="n">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
       <c r="S70" t="n">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71">
@@ -5455,13 +5455,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M71" t="n">
         <v>2</v>
@@ -5473,22 +5473,22 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q71" t="n">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="R71" t="n">
         <v>16</v>
       </c>
       <c r="S71" t="n">
-        <v>182</v>
+        <v>220</v>
       </c>
       <c r="T71" t="n">
         <v>1</v>
       </c>
       <c r="U71" t="n">
-        <v>182</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L73" t="n">
         <v>5</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Q73" t="n">
         <v>139</v>
@@ -5624,13 +5624,13 @@
         <v>48</v>
       </c>
       <c r="S73" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74">
@@ -5931,7 +5931,7 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>scott currie</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6011,13 +6011,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K79" t="n">
         <v>1</v>
       </c>
       <c r="L79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M79" t="n">
         <v>0</v>
@@ -6032,19 +6032,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="R79" t="n">
         <v>18</v>
       </c>
       <c r="S79" t="n">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="T79" t="n">
         <v>1</v>
       </c>
       <c r="U79" t="n">
-        <v>171</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
         <v>9</v>
@@ -6109,13 +6109,13 @@
         <v>8</v>
       </c>
       <c r="S80" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81">
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>8</v>
       </c>
       <c r="S81" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
       </c>
       <c r="U81" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2804</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="3">
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2525</v>
+        <v>2776</v>
       </c>
     </row>
     <row r="4">
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2418</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="5">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2217</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="6">
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2145</v>
+        <v>2390</v>
       </c>
     </row>
   </sheetData>
@@ -6296,7 +6296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6448,23 +6448,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="D3" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -6473,166 +6473,168 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>145</v>
+        <v>226</v>
       </c>
       <c r="D4" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>314</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>20</v>
+      </c>
+      <c r="P4" t="n">
+        <v>358</v>
+      </c>
+      <c r="Q4" t="n">
         <v>3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>184</v>
-      </c>
-      <c r="M4" t="n">
-        <v>83</v>
-      </c>
-      <c r="N4" t="n">
-        <v>30</v>
-      </c>
-      <c r="O4" t="n">
-        <v>16</v>
-      </c>
-      <c r="P4" t="n">
-        <v>313</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>195</v>
+      </c>
+      <c r="D5" t="n">
+        <v>126</v>
+      </c>
+      <c r="E5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>276</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>52</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>173</v>
-      </c>
-      <c r="D5" t="n">
-        <v>87</v>
-      </c>
-      <c r="E5" t="n">
-        <v>13</v>
-      </c>
-      <c r="F5" t="n">
-        <v>14</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>249</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>12</v>
-      </c>
-      <c r="P5" t="n">
-        <v>269</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>176</v>
+        <v>214</v>
       </c>
       <c r="D6" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6650,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -6662,70 +6664,68 @@
         <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>267</v>
+        <v>325</v>
       </c>
       <c r="Q6" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1</v>
-      </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="M7" t="n">
-        <v>136</v>
+        <v>83</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>256</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6734,29 +6734,29 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>113</v>
+      </c>
+      <c r="D8" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>90</v>
-      </c>
-      <c r="D8" t="n">
-        <v>69</v>
-      </c>
-      <c r="E8" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
@@ -6764,19 +6764,19 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="M8" t="n">
         <v>114</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>256</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -6788,112 +6788,110 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>9</v>
       </c>
-      <c r="F9" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>61</v>
+        <v>254</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>191</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>56</v>
+      </c>
+      <c r="O10" t="n">
         <v>20</v>
       </c>
-      <c r="F10" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>205</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" t="n">
-        <v>16</v>
-      </c>
       <c r="P10" t="n">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -6902,32 +6900,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -6936,19 +6934,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M11" t="n">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -6956,17 +6954,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -6981,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -6990,19 +6988,19 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="O12" t="n">
         <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
@@ -7010,20 +7008,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>7</v>
@@ -7035,55 +7033,59 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="O13" t="n">
         <v>20</v>
       </c>
       <c r="P13" t="n">
-        <v>237</v>
-      </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -7098,10 +7100,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M14" t="n">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="N14" t="n">
         <v>8</v>
@@ -7110,61 +7112,63 @@
         <v>16</v>
       </c>
       <c r="P14" t="n">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N15" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="O15" t="n">
         <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>229</v>
+        <v>255</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -7178,7 +7182,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -7193,7 +7197,7 @@
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -7211,16 +7215,16 @@
         <v>28</v>
       </c>
       <c r="M16" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="N16" t="n">
         <v>44</v>
       </c>
       <c r="O16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>224</v>
+        <v>253</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -7228,63 +7232,61 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="N17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -7294,13 +7296,13 @@
         <v>124</v>
       </c>
       <c r="D18" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -7315,22 +7317,22 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="O18" t="n">
         <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -7338,107 +7340,109 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>4</v>
       </c>
       <c r="C19" t="n">
+        <v>130</v>
+      </c>
+      <c r="D19" t="n">
+        <v>83</v>
+      </c>
+      <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="n">
         <v>6</v>
       </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>177</v>
       </c>
       <c r="M19" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="O19" t="n">
         <v>16</v>
       </c>
       <c r="P19" t="n">
-        <v>210</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>6</v>
       </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M20" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -7446,32 +7450,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="D21" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -7480,54 +7484,52 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -7536,54 +7538,52 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="M22" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -7592,19 +7592,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -7612,20 +7612,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>5</v>
       </c>
       <c r="C24" t="n">
+        <v>124</v>
+      </c>
+      <c r="D24" t="n">
         <v>102</v>
       </c>
-      <c r="D24" t="n">
-        <v>84</v>
-      </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
@@ -7637,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7646,19 +7646,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O24" t="n">
         <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -7666,53 +7666,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
         <v>6</v>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="n">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7720,78 +7720,82 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>44</v>
+        <v>138</v>
       </c>
       <c r="D26" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>53</v>
+        <v>179</v>
       </c>
       <c r="M26" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>174</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>4</v>
       </c>
       <c r="C27" t="n">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" t="n">
         <v>8</v>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -7799,35 +7803,33 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7836,7 +7838,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -7851,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -7869,16 +7871,16 @@
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="N28" t="n">
         <v>18</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -7886,58 +7888,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>111</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="E29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>155</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -7946,19 +7948,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7976,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -7985,10 +7987,10 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -7998,23 +8000,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E31" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -8032,7 +8034,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -8041,47 +8043,45 @@
         <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="D32" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8090,75 +8090,73 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
+        <v>102</v>
+      </c>
+      <c r="D33" t="n">
+        <v>84</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>127</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>32</v>
+      </c>
+      <c r="O33" t="n">
         <v>20</v>
       </c>
-      <c r="D33" t="n">
-        <v>15</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>23</v>
-      </c>
-      <c r="M33" t="n">
-        <v>108</v>
-      </c>
-      <c r="N33" t="n">
-        <v>16</v>
-      </c>
-      <c r="O33" t="n">
-        <v>16</v>
-      </c>
       <c r="P33" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
@@ -8166,32 +8164,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -8200,19 +8198,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="M34" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="N34" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O34" t="n">
         <v>16</v>
       </c>
       <c r="P34" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8220,23 +8218,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
@@ -8245,7 +8243,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -8254,19 +8252,19 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="M35" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N35" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="O35" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P35" t="n">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
@@ -8274,23 +8272,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -8299,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8308,77 +8306,75 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P36" t="n">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
-      <c r="R36" t="n">
-        <v>1</v>
-      </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
         <v>3</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>4</v>
-      </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="M37" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="N37" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="O37" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P37" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
@@ -8386,86 +8382,88 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>4</v>
       </c>
       <c r="C38" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="D38" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="E38" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="M38" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O38" t="n">
         <v>16</v>
       </c>
       <c r="P38" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q38" t="inlineStr"/>
+        <v>166</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -8474,19 +8472,19 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>35</v>
+        <v>-2</v>
       </c>
       <c r="M39" t="n">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="N39" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O39" t="n">
         <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="n">
@@ -8496,32 +8494,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="D40" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8530,19 +8528,19 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N40" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
@@ -8550,26 +8548,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>4</v>
       </c>
       <c r="C41" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -8584,10 +8582,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -8596,42 +8594,40 @@
         <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -8640,19 +8636,19 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P42" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
@@ -8660,53 +8656,53 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
         <v>3</v>
       </c>
-      <c r="F43" t="n">
-        <v>6</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N43" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O43" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P43" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8714,23 +8710,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="E44" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -8739,7 +8735,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -8748,40 +8744,44 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="O44" t="n">
         <v>12</v>
       </c>
       <c r="P44" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D45" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F45" t="n">
         <v>5</v>
@@ -8802,7 +8802,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -8811,43 +8811,47 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P45" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B46" t="n">
         <v>4</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -8856,19 +8860,19 @@
         <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M46" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="N46" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="O46" t="n">
         <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
@@ -8876,23 +8880,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>4</v>
       </c>
       <c r="C47" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -8901,7 +8905,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8910,56 +8914,52 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
         <v>16</v>
       </c>
       <c r="P47" t="n">
-        <v>136</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -8968,43 +8968,45 @@
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="M48" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O48" t="n">
         <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -9022,7 +9024,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -9034,7 +9036,7 @@
         <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -9042,26 +9044,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="D50" t="n">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -9076,10 +9078,10 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>135</v>
       </c>
       <c r="M50" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
@@ -9088,34 +9090,36 @@
         <v>16</v>
       </c>
       <c r="P50" t="n">
-        <v>133</v>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="D51" t="n">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -9127,78 +9131,76 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>127</v>
       </c>
       <c r="M51" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="n">
-        <v>1</v>
-      </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>4</v>
+      </c>
+      <c r="C52" t="n">
+        <v>69</v>
+      </c>
+      <c r="D52" t="n">
+        <v>58</v>
+      </c>
+      <c r="E52" t="n">
         <v>3</v>
       </c>
-      <c r="C52" t="n">
-        <v>64</v>
-      </c>
-      <c r="D52" t="n">
-        <v>50</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>6</v>
       </c>
-      <c r="F52" t="n">
-        <v>2</v>
-      </c>
       <c r="G52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="M52" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O52" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P52" t="n">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
@@ -9206,20 +9208,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -9240,48 +9242,46 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>-2</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P53" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="n">
-        <v>1</v>
-      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B54" t="n">
+        <v>4</v>
+      </c>
+      <c r="C54" t="n">
+        <v>104</v>
+      </c>
+      <c r="D54" t="n">
+        <v>92</v>
+      </c>
+      <c r="E54" t="n">
         <v>5</v>
       </c>
-      <c r="C54" t="n">
-        <v>12</v>
-      </c>
-      <c r="D54" t="n">
-        <v>7</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -9296,54 +9296,52 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="M54" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="n">
-        <v>1</v>
-      </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -9352,19 +9350,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="M55" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O55" t="n">
         <v>16</v>
       </c>
       <c r="P55" t="n">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9372,32 +9370,32 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -9406,73 +9404,77 @@
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="M56" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D57" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
         <v>2</v>
       </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>1</v>
-      </c>
       <c r="L57" t="n">
-        <v>72</v>
+        <v>7</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N57" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O57" t="n">
         <v>16</v>
       </c>
       <c r="P57" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9480,33 +9482,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B58" t="n">
         <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="D58" t="n">
+        <v>43</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" t="n">
         <v>5</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
       <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
         <v>3</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1</v>
-      </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
@@ -9514,19 +9516,19 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="M58" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="O58" t="n">
         <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9534,26 +9536,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -9568,10 +9570,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="M59" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
@@ -9580,34 +9582,32 @@
         <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="n">
-        <v>1</v>
-      </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>69</v>
+      </c>
+      <c r="D60" t="n">
+        <v>46</v>
+      </c>
+      <c r="E60" t="n">
+        <v>7</v>
+      </c>
+      <c r="F60" t="n">
         <v>3</v>
       </c>
-      <c r="C60" t="n">
-        <v>75</v>
-      </c>
-      <c r="D60" t="n">
-        <v>54</v>
-      </c>
-      <c r="E60" t="n">
-        <v>6</v>
-      </c>
-      <c r="F60" t="n">
-        <v>5</v>
-      </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
@@ -9615,28 +9615,28 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O60" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
@@ -9644,80 +9644,82 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B61" t="n">
         <v>3</v>
       </c>
       <c r="C61" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
         <v>2</v>
       </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>72</v>
-      </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N61" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O61" t="n">
         <v>12</v>
       </c>
       <c r="P61" t="n">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -9732,19 +9734,19 @@
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M62" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="N62" t="n">
         <v>8</v>
       </c>
       <c r="O62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P62" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9752,17 +9754,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D63" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E63" t="n">
         <v>6</v>
@@ -9777,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -9792,45 +9794,43 @@
         <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P63" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B64" t="n">
         <v>5</v>
       </c>
       <c r="C64" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="D64" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" t="n">
         <v>3</v>
       </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
       <c r="H64" t="n">
         <v>0</v>
       </c>
@@ -9844,10 +9844,10 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -9856,37 +9856,37 @@
         <v>20</v>
       </c>
       <c r="P64" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
         <v>3</v>
       </c>
-      <c r="C65" t="n">
-        <v>53</v>
-      </c>
-      <c r="D65" t="n">
-        <v>29</v>
-      </c>
-      <c r="E65" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" t="n">
-        <v>3</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0</v>
-      </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
@@ -9900,45 +9900,43 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N65" t="n">
         <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P65" t="n">
-        <v>98</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
         <v>3</v>
@@ -9947,7 +9945,7 @@
         <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -9956,75 +9954,73 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O66" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P66" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="n">
-        <v>1</v>
-      </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B67" t="n">
         <v>4</v>
       </c>
       <c r="C67" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>3</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="n">
+        <v>86</v>
+      </c>
+      <c r="N67" t="n">
         <v>8</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>80</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="n">
-        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>16</v>
       </c>
       <c r="P67" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -10032,23 +10028,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="n">
+        <v>7</v>
+      </c>
+      <c r="D68" t="n">
         <v>3</v>
       </c>
-      <c r="C68" t="n">
-        <v>4</v>
-      </c>
-      <c r="D68" t="n">
-        <v>5</v>
-      </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
         <v>3</v>
@@ -10066,19 +10062,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M68" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N68" t="n">
         <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P68" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -10086,23 +10082,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="D69" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E69" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -10111,28 +10107,28 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="M69" t="n">
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="n">
@@ -10142,32 +10138,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B70" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
         <v>3</v>
       </c>
-      <c r="C70" t="n">
-        <v>53</v>
-      </c>
-      <c r="D70" t="n">
-        <v>30</v>
-      </c>
-      <c r="E70" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" t="n">
-        <v>7</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
       <c r="H70" t="n">
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -10176,27 +10172,29 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>72</v>
+        <v>-2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P70" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -10221,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -10233,16 +10231,16 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O71" t="n">
         <v>16</v>
       </c>
       <c r="P71" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10250,56 +10248,58 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>81</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>20</v>
+      </c>
+      <c r="P72" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="n">
         <v>2</v>
       </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="n">
-        <v>2</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>4</v>
-      </c>
-      <c r="M72" t="n">
-        <v>50</v>
-      </c>
-      <c r="N72" t="n">
-        <v>16</v>
-      </c>
-      <c r="O72" t="n">
-        <v>16</v>
-      </c>
-      <c r="P72" t="n">
-        <v>86</v>
-      </c>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10308,16 +10308,16 @@
         </is>
       </c>
       <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>62</v>
+      </c>
+      <c r="D73" t="n">
+        <v>33</v>
+      </c>
+      <c r="E73" t="n">
         <v>2</v>
-      </c>
-      <c r="C73" t="n">
-        <v>52</v>
-      </c>
-      <c r="D73" t="n">
-        <v>28</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
       </c>
       <c r="F73" t="n">
         <v>5</v>
@@ -10338,7 +10338,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -10347,10 +10347,10 @@
         <v>8</v>
       </c>
       <c r="O73" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P73" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
@@ -10358,26 +10358,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -10389,46 +10389,48 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M74" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
         <v>12</v>
       </c>
-      <c r="O74" t="n">
-        <v>16</v>
-      </c>
       <c r="P74" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C75" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -10437,28 +10439,28 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
+        <v>14</v>
+      </c>
+      <c r="O75" t="n">
         <v>16</v>
       </c>
-      <c r="O75" t="n">
-        <v>12</v>
-      </c>
       <c r="P75" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
@@ -10468,17 +10470,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Saqib Mahmood</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -10487,13 +10489,13 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -10502,55 +10504,53 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N76" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O76" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="n">
-        <v>2</v>
-      </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>4</v>
       </c>
       <c r="C77" t="n">
+        <v>39</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
         <v>2</v>
       </c>
-      <c r="D77" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>2</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="n">
-        <v>0</v>
-      </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
@@ -10558,43 +10558,45 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="M77" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O77" t="n">
         <v>16</v>
       </c>
       <c r="P77" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
+      <c r="R77" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
@@ -10609,22 +10611,22 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M78" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O78" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
@@ -10632,26 +10634,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sean Dickson</t>
+          <t>Saqib Mahmood</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>4</v>
       </c>
       <c r="C79" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D79" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -10666,10 +10668,10 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>50</v>
+        <v>-2</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N79" t="n">
         <v>8</v>
@@ -10678,40 +10680,42 @@
         <v>16</v>
       </c>
       <c r="P79" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Usman Tariq</t>
+          <t>Sean Dickson</t>
         </is>
       </c>
       <c r="B80" t="n">
         <v>4</v>
       </c>
       <c r="C80" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D80" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -10720,19 +10724,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="M80" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O80" t="n">
         <v>16</v>
       </c>
       <c r="P80" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
@@ -10740,32 +10744,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jason Roy</t>
+          <t>Usman Tariq</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C81" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -10774,45 +10778,43 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
         <v>16</v>
       </c>
-      <c r="O81" t="n">
-        <v>12</v>
-      </c>
       <c r="P81" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="n">
-        <v>1</v>
-      </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Laurie Evans</t>
+          <t>Tim David</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D82" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -10830,7 +10832,7 @@
         <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -10839,10 +10841,10 @@
         <v>8</v>
       </c>
       <c r="O82" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P82" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
@@ -10850,20 +10852,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Matthew Revis</t>
+          <t>Matthew Potts</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -10875,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -10884,19 +10886,19 @@
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M83" t="n">
         <v>25</v>
       </c>
       <c r="N83" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O83" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="P83" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
@@ -10904,77 +10906,79 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Thomas Rew</t>
+          <t>Jason Roy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D84" t="n">
+        <v>22</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
         <v>30</v>
       </c>
-      <c r="E84" t="n">
-        <v>5</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>53</v>
-      </c>
       <c r="M84" t="n">
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O84" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P84" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Asa Tribe</t>
+          <t>Aneurin Donald</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D85" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -10983,7 +10987,7 @@
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -10992,19 +10996,19 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="P85" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -11012,17 +11016,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Matthew Potts</t>
+          <t>Asa Tribe</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D86" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -11031,13 +11035,13 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -11046,19 +11050,19 @@
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O86" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P86" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr"/>
@@ -11066,26 +11070,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Laurie Evans</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -11097,22 +11101,22 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M87" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O87" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P87" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr"/>
@@ -11120,20 +11124,20 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Matthew Revis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -11145,7 +11149,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -11154,19 +11158,19 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O88" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P88" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
@@ -11174,23 +11178,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>Thomas Rew</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -11199,7 +11203,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -11208,19 +11212,19 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
@@ -11228,17 +11232,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tim David</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -11247,7 +11251,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -11259,22 +11263,22 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N90" t="n">
+        <v>14</v>
+      </c>
+      <c r="O90" t="n">
         <v>8</v>
       </c>
-      <c r="O90" t="n">
-        <v>12</v>
-      </c>
       <c r="P90" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11282,20 +11286,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B91" t="n">
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -11316,10 +11320,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M91" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N91" t="n">
         <v>0</v>
@@ -11328,7 +11332,7 @@
         <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -11336,17 +11340,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -11355,13 +11359,13 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -11370,16 +11374,16 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N92" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P92" t="n">
         <v>29</v>
@@ -11390,33 +11394,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
         <v>2</v>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
@@ -11424,19 +11428,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P93" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11444,23 +11448,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B94" t="n">
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D94" t="n">
         <v>19</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -11478,7 +11482,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -11490,7 +11494,7 @@
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -11498,23 +11502,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -11523,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -11532,19 +11536,19 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -11552,7 +11556,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -11577,28 +11581,28 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O96" t="n">
         <v>8</v>
       </c>
       <c r="P96" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -11606,17 +11610,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Moeen Ali</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -11631,28 +11635,28 @@
         <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N97" t="n">
+        <v>6</v>
+      </c>
+      <c r="O97" t="n">
         <v>8</v>
       </c>
-      <c r="O97" t="n">
-        <v>4</v>
-      </c>
       <c r="P97" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -11660,17 +11664,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Moeen Ali</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -11685,28 +11689,28 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P98" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -11714,17 +11718,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -11739,28 +11743,28 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
+        <v>12</v>
+      </c>
+      <c r="O99" t="n">
         <v>8</v>
       </c>
-      <c r="O99" t="n">
-        <v>4</v>
-      </c>
       <c r="P99" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
@@ -11768,17 +11772,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -11793,7 +11797,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -11802,19 +11806,19 @@
         <v>0</v>
       </c>
       <c r="L100" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O100" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P100" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -11822,17 +11826,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Tom Kohler-Cadmore</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -11847,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11856,19 +11860,19 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
         <v>8</v>
       </c>
-      <c r="O101" t="n">
-        <v>4</v>
-      </c>
       <c r="P101" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -11876,17 +11880,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ed Barnard</t>
+          <t>Tom Kohler-Cadmore</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -11910,7 +11914,7 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -11922,7 +11926,7 @@
         <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
@@ -11984,7 +11988,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Tymal Mills</t>
+          <t>Ed Barnard</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -12009,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -12024,13 +12028,13 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O104" t="n">
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr"/>
@@ -12038,56 +12042,164 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>Tymal Mills</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" t="n">
+        <v>4</v>
+      </c>
+      <c r="P105" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Liam Patterson-White</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>4</v>
+      </c>
+      <c r="P106" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>Benny Howell</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
         <v>-2</v>
       </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" t="n">
-        <v>4</v>
-      </c>
-      <c r="P105" t="n">
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="n">
+        <v>4</v>
+      </c>
+      <c r="P107" t="n">
         <v>2</v>
       </c>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="n">
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12502,7 +12614,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>scott currie</t>
+          <t>brydon carse</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -12800,7 +12912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14265,6 +14377,186 @@
         <v>195</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>17</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>17</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>17</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>17</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>17</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>M17: Trent Rockets v Sunrisers Leeds</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>18</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>18</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>18</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>18</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>18</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>M18: MI London v Manchester Super Giants</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
         <v>124</v>
@@ -1221,7 +1221,7 @@
         <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1230,13 +1230,13 @@
         <v>52</v>
       </c>
       <c r="S11" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
@@ -1696,16 +1696,16 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1714,22 +1714,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="S18" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="T18" t="n">
         <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>332</v>
+        <v>394</v>
       </c>
     </row>
     <row r="19">
@@ -1909,14 +1909,14 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>124</v>
+      </c>
+      <c r="L21" t="n">
         <v>3</v>
       </c>
-      <c r="K21" t="n">
-        <v>64</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
       <c r="M21" t="n">
         <v>1</v>
       </c>
@@ -1927,22 +1927,22 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>79</v>
+        <v>164</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="R21" t="n">
         <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>124</v>
+        <v>266</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>124</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>73</v>
+        <v>128</v>
       </c>
       <c r="L23" t="n">
         <v>9</v>
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="Q23" t="n">
         <v>260</v>
@@ -2078,13 +2078,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>372</v>
+        <v>456</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>372</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24">
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L33" t="n">
         <v>3</v>
@@ -2779,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
         <v>83</v>
@@ -2788,13 +2788,13 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
@@ -2903,16 +2903,16 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -2921,22 +2921,22 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="R35" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S35" t="n">
-        <v>196</v>
+        <v>269</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>196</v>
+        <v>269</v>
       </c>
     </row>
     <row r="36">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2983,7 +2983,7 @@
         <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
@@ -2998,16 +2998,16 @@
         <v>187</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="S36" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37">
@@ -3116,7 +3116,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -3125,7 +3125,7 @@
         <v>4</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -3140,16 +3140,16 @@
         <v>106</v>
       </c>
       <c r="R38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="S38" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="39">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -3350,19 +3350,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="R41" t="n">
         <v>12</v>
       </c>
       <c r="S41" t="n">
-        <v>242</v>
+        <v>271</v>
       </c>
       <c r="T41" t="n">
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>242</v>
+        <v>271</v>
       </c>
     </row>
     <row r="42">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -3566,16 +3566,16 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="T44" t="n">
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3995,13 +3995,13 @@
         <v>24</v>
       </c>
       <c r="S50" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="T50" t="n">
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51">
@@ -4110,10 +4110,10 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -4137,13 +4137,13 @@
         <v>8</v>
       </c>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="T52" t="n">
         <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
@@ -4346,13 +4346,13 @@
         <v>40</v>
       </c>
       <c r="S55" t="n">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="T55" t="n">
         <v>1</v>
       </c>
       <c r="U55" t="n">
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="56">
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
@@ -4630,13 +4630,13 @@
         <v>32</v>
       </c>
       <c r="S59" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="T59" t="n">
         <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60">
@@ -4887,10 +4887,10 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -4905,7 +4905,7 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="Q63" t="n">
         <v>94</v>
@@ -4914,13 +4914,13 @@
         <v>8</v>
       </c>
       <c r="S63" t="n">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="T63" t="n">
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="64">
@@ -4958,13 +4958,13 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K64" t="n">
         <v>145</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M64" t="n">
         <v>3</v>
@@ -4976,22 +4976,22 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q64" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="R64" t="n">
         <v>30</v>
       </c>
       <c r="S64" t="n">
-        <v>313</v>
+        <v>376</v>
       </c>
       <c r="T64" t="n">
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>313</v>
+        <v>376</v>
       </c>
     </row>
     <row r="65">
@@ -5242,13 +5242,13 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K68" t="n">
         <v>4</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
@@ -5263,19 +5263,19 @@
         <v>4</v>
       </c>
       <c r="Q68" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="R68" t="n">
         <v>12</v>
       </c>
       <c r="S68" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="T68" t="n">
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>82</v>
+        <v>111</v>
       </c>
     </row>
     <row r="69">
@@ -5735,16 +5735,16 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M75" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
@@ -5753,22 +5753,22 @@
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q75" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="R75" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="S75" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="T75" t="n">
         <v>1</v>
       </c>
       <c r="U75" t="n">
-        <v>156</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76">
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3118</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="3">
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2776</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="4">
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2750</v>
+        <v>2811</v>
       </c>
     </row>
     <row r="5">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2566</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="6">
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2390</v>
+        <v>2564</v>
       </c>
     </row>
   </sheetData>
@@ -6398,19 +6398,19 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>128</v>
+      </c>
+      <c r="D2" t="n">
+        <v>95</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
         <v>4</v>
-      </c>
-      <c r="C2" t="n">
-        <v>73</v>
-      </c>
-      <c r="D2" t="n">
-        <v>56</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
       <c r="G2" t="n">
         <v>9</v>
@@ -6428,7 +6428,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="M2" t="n">
         <v>260</v>
@@ -6437,67 +6437,69 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>372</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
+        <v>456</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="D3" t="n">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>331</v>
+        <v>182</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N3" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O3" t="n">
         <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -6506,23 +6508,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D4" t="n">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -6531,54 +6533,56 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
-      <c r="R4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -6587,28 +6591,28 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
@@ -6618,23 +6622,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D6" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6643,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -6652,78 +6656,78 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="D7" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>184</v>
+        <v>301</v>
       </c>
       <c r="M7" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O7" t="n">
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -6842,81 +6846,77 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="N10" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P10" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
         <v>7</v>
@@ -6931,168 +6931,172 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M11" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P11" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>5</v>
       </c>
       <c r="C12" t="n">
+        <v>132</v>
+      </c>
+      <c r="D12" t="n">
+        <v>67</v>
+      </c>
+      <c r="E12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="M12" t="n">
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="O12" t="n">
         <v>20</v>
       </c>
       <c r="P12" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E13" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P13" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
@@ -7100,55 +7104,53 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="N14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>1</v>
-      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>123</v>
-      </c>
-      <c r="D15" t="n">
-        <v>90</v>
-      </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>2</v>
       </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
@@ -7156,273 +7158,277 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="N15" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="O15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="M16" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O16" t="n">
         <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>253</v>
-      </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>77</v>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" t="n">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7</v>
-      </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M17" t="n">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P17" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N18" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="O18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P18" t="n">
-        <v>237</v>
-      </c>
-      <c r="Q18" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
         <v>6</v>
       </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>177</v>
+        <v>28</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N19" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>229</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="n">
+        <v>145</v>
+      </c>
+      <c r="D20" t="n">
+        <v>119</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>5</v>
       </c>
-      <c r="C20" t="n">
-        <v>15</v>
-      </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>6</v>
-      </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
@@ -7430,19 +7436,19 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="M20" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P20" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -7450,128 +7456,132 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>124</v>
+      </c>
+      <c r="D21" t="n">
+        <v>77</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>5</v>
       </c>
-      <c r="C21" t="n">
-        <v>39</v>
-      </c>
-      <c r="D21" t="n">
-        <v>30</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="M21" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P21" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="M22" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P22" t="n">
-        <v>211</v>
-      </c>
-      <c r="Q22" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -7583,28 +7593,28 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O23" t="n">
         <v>20</v>
       </c>
       <c r="P23" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -7612,32 +7622,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="D24" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -7646,19 +7656,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="O24" t="n">
         <v>20</v>
       </c>
       <c r="P24" t="n">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -7666,53 +7676,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>39</v>
+      </c>
+      <c r="D25" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" t="n">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M25" t="n">
-        <v>187</v>
+        <v>141</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -7720,90 +7730,86 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="D26" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
         <v>6</v>
       </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O26" t="n">
         <v>20</v>
       </c>
       <c r="P26" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>130</v>
+        <v>9</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -7812,108 +7818,110 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>177</v>
+        <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="M28" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
         <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>200</v>
-      </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -7922,45 +7930,43 @@
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M29" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="N29" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="O29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D30" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7978,7 +7984,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -7987,10 +7993,10 @@
         <v>8</v>
       </c>
       <c r="O30" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P30" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -8000,88 +8006,86 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N31" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O31" t="n">
         <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>182</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D32" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8090,19 +8094,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O32" t="n">
         <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -8110,23 +8114,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="E33" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -8135,7 +8139,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -8144,47 +8148,49 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="O33" t="n">
         <v>20</v>
       </c>
       <c r="P33" t="n">
-        <v>179</v>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
         <v>6</v>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3</v>
-      </c>
       <c r="H34" t="n">
         <v>0</v>
       </c>
@@ -8198,19 +8204,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>94</v>
+        <v>166</v>
       </c>
       <c r="N34" t="n">
         <v>8</v>
       </c>
       <c r="O34" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P34" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
@@ -8218,78 +8224,80 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D35" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="M35" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="O35" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P35" t="n">
-        <v>174</v>
-      </c>
-      <c r="Q35" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" t="n">
+        <v>108</v>
+      </c>
+      <c r="D36" t="n">
+        <v>92</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" t="n">
         <v>4</v>
       </c>
-      <c r="C36" t="n">
-        <v>111</v>
-      </c>
-      <c r="D36" t="n">
-        <v>63</v>
-      </c>
-      <c r="E36" t="n">
-        <v>7</v>
-      </c>
-      <c r="F36" t="n">
-        <v>11</v>
-      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
@@ -8297,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8306,54 +8314,52 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P36" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>12</v>
+        <v>117</v>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -8362,52 +8368,54 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="M37" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O37" t="n">
         <v>20</v>
       </c>
       <c r="P37" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="D38" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="E38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -8416,110 +8424,106 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>134</v>
+        <v>19</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P38" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>4</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>-2</v>
+        <v>53</v>
       </c>
       <c r="M39" t="n">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="N39" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O39" t="n">
         <v>16</v>
       </c>
       <c r="P39" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B40" t="n">
         <v>4</v>
       </c>
       <c r="C40" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8528,52 +8532,54 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>23</v>
+        <v>155</v>
       </c>
       <c r="M40" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>16</v>
       </c>
       <c r="P40" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+        <v>171</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>5</v>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" t="n">
         <v>4</v>
       </c>
-      <c r="C41" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" t="n">
-        <v>5</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>5</v>
-      </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8582,19 +8588,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="M41" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
@@ -8602,17 +8608,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -8636,73 +8642,75 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="M42" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="N42" t="n">
         <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P42" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43" t="n">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
         <v>15</v>
       </c>
-      <c r="D43" t="n">
-        <v>11</v>
-      </c>
       <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
         <v>2</v>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>4</v>
-      </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M43" t="n">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="N43" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="O43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P43" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
@@ -8710,90 +8718,86 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>4</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>107</v>
-      </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N44" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P44" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
         <v>5</v>
       </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -8802,50 +8806,46 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O45" t="n">
         <v>20</v>
       </c>
       <c r="P45" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="D46" t="n">
+        <v>57</v>
+      </c>
+      <c r="E46" t="n">
         <v>9</v>
       </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -8857,46 +8857,50 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="M46" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="O46" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P46" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C47" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="D47" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -8905,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8914,43 +8918,47 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P47" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B48" t="n">
         <v>4</v>
       </c>
       <c r="C48" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
@@ -8959,54 +8967,52 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="M48" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N48" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="O48" t="n">
         <v>16</v>
       </c>
       <c r="P48" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="n">
-        <v>1</v>
-      </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" t="n">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="D49" t="n">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="E49" t="n">
         <v>6</v>
       </c>
       <c r="F49" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -9015,7 +9021,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -9024,19 +9030,19 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P49" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -9044,63 +9050,61 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B50" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
         <v>4</v>
       </c>
-      <c r="C50" t="n">
-        <v>99</v>
-      </c>
-      <c r="D50" t="n">
-        <v>68</v>
-      </c>
-      <c r="E50" t="n">
-        <v>8</v>
-      </c>
-      <c r="F50" t="n">
-        <v>4</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
       <c r="H50" t="n">
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P50" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -9110,10 +9114,10 @@
         <v>99</v>
       </c>
       <c r="D51" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
         <v>7</v>
@@ -9134,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -9146,7 +9150,7 @@
         <v>16</v>
       </c>
       <c r="P51" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9154,26 +9158,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D52" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E52" t="n">
+        <v>4</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" t="n">
         <v>3</v>
-      </c>
-      <c r="F52" t="n">
-        <v>6</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -9185,55 +9189,57 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N52" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O52" t="n">
         <v>16</v>
       </c>
       <c r="P52" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D53" t="n">
+        <v>53</v>
+      </c>
+      <c r="E53" t="n">
         <v>6</v>
       </c>
-      <c r="E53" t="n">
-        <v>2</v>
-      </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -9242,19 +9248,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="M53" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O53" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P53" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
@@ -9262,23 +9268,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D54" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -9296,7 +9302,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -9308,31 +9314,33 @@
         <v>16</v>
       </c>
       <c r="P54" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q54" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1</v>
+      </c>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B55" t="n">
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D55" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -9341,7 +9349,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -9350,19 +9358,19 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O55" t="n">
         <v>16</v>
       </c>
       <c r="P55" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9370,23 +9378,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="D56" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -9395,53 +9403,49 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
+        <v>10</v>
+      </c>
+      <c r="D57" t="n">
         <v>6</v>
       </c>
-      <c r="D57" t="n">
-        <v>5</v>
-      </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -9459,22 +9463,22 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M57" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N57" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P57" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9486,13 +9490,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D58" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E58" t="n">
         <v>4</v>
@@ -9516,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -9525,10 +9529,10 @@
         <v>24</v>
       </c>
       <c r="O58" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P58" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
@@ -9536,33 +9540,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="D59" t="n">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E59" t="n">
+        <v>6</v>
+      </c>
+      <c r="F59" t="n">
         <v>2</v>
       </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
         <v>4</v>
       </c>
-      <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
@@ -9570,19 +9574,19 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="M59" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O59" t="n">
         <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -9590,23 +9594,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E60" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -9615,49 +9619,53 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P60" t="n">
-        <v>132</v>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>1</v>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
         <v>9</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -9669,84 +9677,82 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="M61" t="n">
         <v>103</v>
       </c>
       <c r="N61" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P61" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="n">
-        <v>1</v>
-      </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B62" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>69</v>
+      </c>
+      <c r="D62" t="n">
+        <v>46</v>
+      </c>
+      <c r="E62" t="n">
+        <v>7</v>
+      </c>
+      <c r="F62" t="n">
         <v>3</v>
       </c>
-      <c r="C62" t="n">
-        <v>64</v>
-      </c>
-      <c r="D62" t="n">
-        <v>50</v>
-      </c>
-      <c r="E62" t="n">
-        <v>6</v>
-      </c>
-      <c r="F62" t="n">
-        <v>2</v>
-      </c>
       <c r="G62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="M62" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O62" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P62" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9754,26 +9760,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" t="n">
         <v>4</v>
       </c>
-      <c r="C63" t="n">
-        <v>67</v>
-      </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="E63" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -9785,27 +9791,27 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="N63" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O63" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P63" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
+        <v>131</v>
+      </c>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9814,13 +9820,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -9844,7 +9850,7 @@
         <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M64" t="n">
         <v>83</v>
@@ -9853,10 +9859,10 @@
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P64" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="n">
@@ -9866,26 +9872,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -9900,37 +9906,39 @@
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M65" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
         <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P65" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q65" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B66" t="n">
         <v>5</v>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -9954,10 +9962,10 @@
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="N66" t="n">
         <v>8</v>
@@ -9966,7 +9974,7 @@
         <v>20</v>
       </c>
       <c r="P66" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
@@ -9974,17 +9982,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -10008,19 +10016,19 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N67" t="n">
         <v>8</v>
       </c>
       <c r="O67" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P67" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
@@ -10028,32 +10036,32 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Ben McKinney</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>7</v>
+        <v>66</v>
       </c>
       <c r="D68" t="n">
+        <v>46</v>
+      </c>
+      <c r="E68" t="n">
+        <v>8</v>
+      </c>
+      <c r="F68" t="n">
         <v>3</v>
       </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
-      </c>
       <c r="G68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -10062,46 +10070,48 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="M68" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O68" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P68" t="n">
         <v>111</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
+      <c r="R68" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ryan Rickelton</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B69" t="n">
         <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D69" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E69" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -10116,10 +10126,10 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>94</v>
+        <v>9</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
@@ -10128,24 +10138,22 @@
         <v>16</v>
       </c>
       <c r="P69" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="n">
-        <v>1</v>
-      </c>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Adam Zampa</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B70" t="n">
         <v>4</v>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70" t="n">
         <v>1</v>
@@ -10163,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -10172,39 +10180,37 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="M70" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O70" t="n">
         <v>16</v>
       </c>
       <c r="P70" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="n">
-        <v>1</v>
-      </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>Chris Woakes</t>
         </is>
       </c>
       <c r="B71" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" t="n">
         <v>4</v>
       </c>
-      <c r="C71" t="n">
-        <v>0</v>
-      </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -10219,28 +10225,28 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M71" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="N71" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O71" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P71" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
@@ -10248,24 +10254,24 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>75</v>
+      </c>
+      <c r="D72" t="n">
+        <v>57</v>
+      </c>
+      <c r="E72" t="n">
+        <v>6</v>
+      </c>
+      <c r="F72" t="n">
         <v>5</v>
       </c>
-      <c r="C72" t="n">
-        <v>66</v>
-      </c>
-      <c r="D72" t="n">
-        <v>44</v>
-      </c>
-      <c r="E72" t="n">
-        <v>8</v>
-      </c>
-      <c r="F72" t="n">
-        <v>3</v>
-      </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
@@ -10282,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -10291,45 +10297,45 @@
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P72" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tom Alsop</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B73" t="n">
+        <v>4</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
         <v>3</v>
       </c>
-      <c r="C73" t="n">
-        <v>62</v>
-      </c>
-      <c r="D73" t="n">
-        <v>33</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
-      <c r="F73" t="n">
-        <v>5</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0</v>
-      </c>
       <c r="H73" t="n">
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -10338,52 +10344,54 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>79</v>
+        <v>-2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="N73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P73" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Andrew Tye</t>
+          <t>Tom Alsop</t>
         </is>
       </c>
       <c r="B74" t="n">
         <v>3</v>
       </c>
       <c r="C74" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -10392,75 +10400,73 @@
         <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="M74" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O74" t="n">
         <v>12</v>
       </c>
       <c r="P74" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="n">
-        <v>1</v>
-      </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>James Rew</t>
+          <t>Andrew Tye</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="D75" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E75" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N75" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P75" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="n">
@@ -10470,86 +10476,88 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nathan Sowter</t>
+          <t>James Rew</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="M76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="O76" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P76" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tom Moores</t>
+          <t>Nathan Sowter</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -10558,78 +10566,78 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N77" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="O77" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P77" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="n">
-        <v>2</v>
-      </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Tom Moores</t>
         </is>
       </c>
       <c r="B78" t="n">
         <v>4</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
         <v>2</v>
       </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="M78" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O78" t="n">
         <v>16</v>
       </c>
       <c r="P78" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+      <c r="R78" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11232,53 +11240,53 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Daniel Worrall</t>
+          <t>Phil Salt</t>
         </is>
       </c>
       <c r="B90" t="n">
+        <v>3</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>2</v>
       </c>
-      <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" t="n">
-        <v>1</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>1</v>
-      </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="O90" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P90" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
@@ -11286,20 +11294,20 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Chris Wood</t>
+          <t>Daniel Worrall</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -11311,28 +11319,28 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O91" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
@@ -11340,20 +11348,20 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Olly Stone</t>
+          <t>Chris Wood</t>
         </is>
       </c>
       <c r="B92" t="n">
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
@@ -11374,10 +11382,10 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M92" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="N92" t="n">
         <v>0</v>
@@ -11386,7 +11394,7 @@
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr"/>
@@ -11394,21 +11402,21 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ben Kellaway</t>
+          <t>Tom Kohler-Cadmore</t>
         </is>
       </c>
       <c r="B93" t="n">
+        <v>2</v>
+      </c>
+      <c r="C93" t="n">
+        <v>24</v>
+      </c>
+      <c r="D93" t="n">
+        <v>20</v>
+      </c>
+      <c r="E93" t="n">
         <v>3</v>
       </c>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
-      <c r="D93" t="n">
-        <v>5</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
@@ -11419,7 +11427,7 @@
         <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -11428,19 +11436,19 @@
         <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="M93" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O93" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P93" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
@@ -11448,33 +11456,33 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tom Abell</t>
+          <t>Ben Kellaway</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C94" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
         <v>2</v>
       </c>
-      <c r="F94" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
       <c r="J94" t="n">
         <v>0</v>
       </c>
@@ -11482,19 +11490,19 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P94" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr"/>
@@ -11502,26 +11510,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kiran Carlson</t>
+          <t>Olly Stone</t>
         </is>
       </c>
       <c r="B95" t="n">
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -11536,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N95" t="n">
         <v>0</v>
@@ -11548,7 +11556,7 @@
         <v>4</v>
       </c>
       <c r="P95" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr"/>
@@ -11556,21 +11564,21 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Peter Willey</t>
+          <t>Tom Abell</t>
         </is>
       </c>
       <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>22</v>
+      </c>
+      <c r="D96" t="n">
+        <v>19</v>
+      </c>
+      <c r="E96" t="n">
         <v>2</v>
       </c>
-      <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
@@ -11581,7 +11589,7 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -11590,19 +11598,19 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P96" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr"/>
@@ -11610,23 +11618,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Willey</t>
+          <t>Kiran Carlson</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -11641,22 +11649,22 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M97" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P97" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
@@ -11664,17 +11672,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Moeen Ali</t>
+          <t>Peter Willey</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -11689,7 +11697,7 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -11698,19 +11706,19 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
+        <v>16</v>
+      </c>
+      <c r="O98" t="n">
         <v>8</v>
       </c>
-      <c r="O98" t="n">
-        <v>4</v>
-      </c>
       <c r="P98" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
@@ -11718,17 +11726,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Phil Salt</t>
+          <t>Moeen Ali</t>
         </is>
       </c>
       <c r="B99" t="n">
         <v>2</v>
       </c>
       <c r="C99" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -11743,82 +11751,84 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O99" t="n">
         <v>8</v>
       </c>
       <c r="P99" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
+      <c r="R99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Ollie Pope</t>
+          <t>Willey</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>8</v>
+      </c>
+      <c r="N100" t="n">
         <v>6</v>
       </c>
-      <c r="D100" t="n">
-        <v>4</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>6</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
+      <c r="O100" t="n">
         <v>8</v>
       </c>
-      <c r="O100" t="n">
-        <v>4</v>
-      </c>
       <c r="P100" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
@@ -11826,17 +11836,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Saif Zaib</t>
+          <t>Ollie Pope</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -11851,7 +11861,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -11860,19 +11870,19 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O101" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P101" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
@@ -11880,17 +11890,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Tom Kohler-Cadmore</t>
+          <t>Saif Zaib</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -11905,7 +11915,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -11914,19 +11924,19 @@
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
         <v>8</v>
       </c>
-      <c r="O102" t="n">
-        <v>4</v>
-      </c>
       <c r="P102" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr"/>
@@ -12912,7 +12922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14557,6 +14567,96 @@
         <v>188</v>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>19</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>19</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>f9</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>19</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>lg</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>19</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sd</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>19</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>M19: Welsh Fire v Southern Brave</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ssw</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Hundred_Fantasy_Points.xlsx
+++ b/Hundred_Fantasy_Points.xlsx
@@ -1345,16 +1345,16 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1363,22 +1363,22 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="S13" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>153</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>127</v>
+        <v>212</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>151</v>
+        <v>240</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>151</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" t="n">
         <v>95</v>
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -2004,16 +2004,16 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S22" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23">
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -2211,7 +2211,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>164</v>
+        <v>213</v>
       </c>
       <c r="Q25" t="n">
         <v>61</v>
@@ -2220,13 +2220,13 @@
         <v>14</v>
       </c>
       <c r="S25" t="n">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>255</v>
+        <v>308</v>
       </c>
     </row>
     <row r="26">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="L27" t="n">
         <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -2353,22 +2353,22 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="Q27" t="n">
         <v>108</v>
       </c>
       <c r="R27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="S27" t="n">
-        <v>163</v>
+        <v>208</v>
       </c>
       <c r="T27" t="n">
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>326</v>
+        <v>416</v>
       </c>
     </row>
     <row r="28">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
@@ -2575,13 +2575,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31">
@@ -3045,14 +3045,14 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
         <v>4</v>
       </c>
-      <c r="K37" t="n">
-        <v>1</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3</v>
-      </c>
       <c r="M37" t="n">
         <v>1</v>
       </c>
@@ -3066,19 +3066,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="R37" t="n">
         <v>8</v>
       </c>
       <c r="S37" t="n">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3214,13 +3214,13 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40">
@@ -3471,13 +3471,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M43" t="n">
         <v>1</v>
@@ -3492,19 +3492,19 @@
         <v>-2</v>
       </c>
       <c r="Q43" t="n">
-        <v>144</v>
+        <v>205</v>
       </c>
       <c r="R43" t="n">
         <v>8</v>
       </c>
       <c r="S43" t="n">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="T43" t="n">
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>166</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44">
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -3782,13 +3782,13 @@
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="T47" t="n">
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="48">
@@ -3826,16 +3826,16 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N48" t="n">
         <v>0</v>
@@ -3844,22 +3844,22 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S48" t="n">
-        <v>110</v>
+        <v>261</v>
       </c>
       <c r="T48" t="n">
         <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>110</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
         <v>79</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
@@ -3924,13 +3924,13 @@
         <v>36</v>
       </c>
       <c r="S49" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="T49" t="n">
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -4057,7 +4057,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>14</v>
       </c>
       <c r="S51" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="T51" t="n">
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -4772,13 +4772,13 @@
         <v>8</v>
       </c>
       <c r="S61" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="T61" t="n">
         <v>1</v>
       </c>
       <c r="U61" t="n">
-        <v>118</v>
+        <v>135</v>
       </c>
     </row>
     <row r="62">
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="L62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4834,22 +4834,22 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>14</v>
+        <v>128</v>
       </c>
       <c r="Q62" t="n">
-        <v>103</v>
+        <v>128</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>133</v>
+        <v>276</v>
       </c>
       <c r="T62" t="n">
         <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>133</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63">
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>214</v>
+        <v>290</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>301</v>
+        <v>412</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5056,13 +5056,13 @@
         <v>8</v>
       </c>
       <c r="S65" t="n">
-        <v>325</v>
+        <v>440</v>
       </c>
       <c r="T65" t="n">
         <v>1</v>
       </c>
       <c r="U65" t="n">
-        <v>325</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66">
@@ -5860,29 +5860,33 @@
       <c r="E77" t="b">
         <v>0</v>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>peter willey</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>reece topley</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Reece Topley</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>no_stats_yet</t>
+          <t>exact/alias</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N77" t="n">
         <v>0</v>
@@ -5894,19 +5898,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="T77" t="n">
         <v>1</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78">
@@ -6082,13 +6086,13 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K80" t="n">
         <v>9</v>
       </c>
       <c r="L80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M80" t="n">
         <v>1</v>
@@ -6103,19 +6107,19 @@
         <v>10</v>
       </c>
       <c r="Q80" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="R80" t="n">
         <v>8</v>
       </c>
       <c r="S80" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="T80" t="n">
         <v>1</v>
       </c>
       <c r="U80" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="81">
@@ -6230,7 +6234,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3221</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="3">
@@ -6243,7 +6247,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2963</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="4">
@@ -6256,7 +6260,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2811</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="5">
@@ -6265,11 +6269,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>lg</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2746</v>
+        <v>2917</v>
       </c>
     </row>
     <row r="6">
@@ -6278,11 +6282,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lg</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2564</v>
+        <v>2876</v>
       </c>
     </row>
   </sheetData>
@@ -6296,7 +6300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R107"/>
+  <dimension ref="A1:R108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6450,114 +6454,112 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rachin Ravindra</t>
+          <t>Mitchell Marsh</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>182</v>
+        <v>412</v>
       </c>
       <c r="M3" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
         <v>20</v>
       </c>
       <c r="P3" t="n">
-        <v>376</v>
+        <v>440</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ben Duckett</t>
+          <t>Rachin Ravindra</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>240</v>
+        <v>145</v>
       </c>
       <c r="D4" t="n">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>331</v>
+        <v>182</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="N4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -6566,23 +6568,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jos Buttler</t>
+          <t>Ben Duckett</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="D5" t="n">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -6591,54 +6593,56 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
         <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="Q5" t="n">
         <v>3</v>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Will Jacks</t>
+          <t>Jos Buttler</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="D6" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -6647,28 +6651,28 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>276</v>
+        <v>314</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
         <v>20</v>
       </c>
       <c r="P6" t="n">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
@@ -6678,23 +6682,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mitchell Marsh</t>
+          <t>Will Jacks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -6703,7 +6707,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -6712,112 +6716,110 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sam Curran</t>
+          <t>Liam Livingstone</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="M8" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="N8" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="O8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Richard Gleeson</t>
+          <t>Sam Curran</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -6826,46 +6828,50 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
-        <v>254</v>
+        <v>114</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>274</v>
-      </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
+        <v>304</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Adil Rashid</t>
+          <t>David Willey</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -6877,324 +6883,326 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M10" t="n">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P10" t="n">
-        <v>271</v>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+        <v>276</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jofra Archer</t>
+          <t>Richard Gleeson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>9</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nicholas Pooran</t>
+          <t>Adil Rashid</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="N12" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="O12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P12" t="n">
-        <v>267</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Matthew Short</t>
+          <t>Jofra Archer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>124</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>91</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>164</v>
+        <v>11</v>
       </c>
       <c r="M13" t="n">
-        <v>78</v>
+        <v>212</v>
       </c>
       <c r="N13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="O13" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P13" t="n">
-        <v>266</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <v>269</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rashid Khan</t>
+          <t>Nicholas Pooran</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
         <v>2</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="M14" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="O14" t="n">
         <v>20</v>
       </c>
       <c r="P14" t="n">
-        <v>259</v>
-      </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
+        <v>267</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sonny Baker</t>
+          <t>Matthew Short</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>124</v>
       </c>
       <c r="D15" t="n">
+        <v>91</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="M15" t="n">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="N15" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P15" t="n">
-        <v>258</v>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+        <v>266</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Finn Allen</t>
+          <t>Ryan Rickelton</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -7203,28 +7211,28 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
         <v>20</v>
       </c>
       <c r="P16" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -7236,33 +7244,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rehan Ahmed</t>
+          <t>Rashid Khan</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -7270,55 +7278,53 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="M17" t="n">
-        <v>136</v>
+        <v>211</v>
       </c>
       <c r="N17" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P17" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Liam Livingstone</t>
+          <t>Sonny Baker</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
         <v>4</v>
       </c>
-      <c r="C18" t="n">
-        <v>123</v>
-      </c>
-      <c r="D18" t="n">
-        <v>90</v>
-      </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
@@ -7326,156 +7332,160 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>164</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="N18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
-        <v>255</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Craig Overton</t>
+          <t>Finn Allen</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>79</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>28</v>
+        <v>207</v>
       </c>
       <c r="M19" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O19" t="n">
         <v>20</v>
       </c>
       <c r="P19" t="n">
-        <v>253</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>David Miller</t>
+          <t>Rehan Ahmed</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="D20" t="n">
-        <v>119</v>
+        <v>50</v>
       </c>
       <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>96</v>
+      </c>
+      <c r="M20" t="n">
+        <v>136</v>
+      </c>
+      <c r="N20" t="n">
         <v>8</v>
       </c>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>175</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>40</v>
-      </c>
       <c r="O20" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P20" t="n">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Jamie Smith</t>
+          <t>Craig Overton</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>24</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
         <v>6</v>
-      </c>
-      <c r="C21" t="n">
-        <v>124</v>
-      </c>
-      <c r="D21" t="n">
-        <v>77</v>
-      </c>
-      <c r="E21" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -7487,48 +7497,46 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>163</v>
+        <v>28</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N21" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="O21" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Joe Clarke</t>
+          <t>Harry Brook</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="D22" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -7537,28 +7545,28 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>177</v>
+        <v>212</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -7568,87 +7576,89 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lockie Ferguson</t>
+          <t>Jamie Smith</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>124</v>
+      </c>
+      <c r="D23" t="n">
+        <v>77</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>5</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="M23" t="n">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P23" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gus Atkinson</t>
+          <t>David Miller</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="n">
+        <v>145</v>
+      </c>
+      <c r="D24" t="n">
+        <v>119</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>5</v>
       </c>
-      <c r="C24" t="n">
-        <v>15</v>
-      </c>
-      <c r="D24" t="n">
-        <v>11</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6</v>
-      </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
@@ -7656,19 +7666,19 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="M24" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P24" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
@@ -7676,32 +7686,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mitchell Santner</t>
+          <t>Nathan Ellis</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -7710,94 +7720,98 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>43</v>
+        <v>-2</v>
       </c>
       <c r="M25" t="n">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="N25" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="O25" t="n">
         <v>20</v>
       </c>
       <c r="P25" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tom Curran</t>
+          <t>Joe Clarke</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="M26" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P26" t="n">
-        <v>211</v>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1</v>
+      </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Josh Tongue</t>
+          <t>Lockie Ferguson</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -7809,28 +7823,28 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O27" t="n">
         <v>20</v>
       </c>
       <c r="P27" t="n">
-        <v>210</v>
+        <v>229</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -7838,33 +7852,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>James Vince</t>
+          <t>Gus Atkinson</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>138</v>
+        <v>15</v>
       </c>
       <c r="D28" t="n">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>6</v>
       </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
@@ -7872,77 +7886,73 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="N28" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="O28" t="n">
         <v>20</v>
       </c>
       <c r="P28" t="n">
-        <v>207</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Chris Jordan</t>
+          <t>Mitchell Santner</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>2</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>6</v>
-      </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
+        <v>43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>141</v>
+      </c>
+      <c r="N29" t="n">
+        <v>16</v>
+      </c>
+      <c r="O29" t="n">
         <v>20</v>
       </c>
-      <c r="M29" t="n">
-        <v>100</v>
-      </c>
-      <c r="N29" t="n">
-        <v>60</v>
-      </c>
-      <c r="O29" t="n">
-        <v>24</v>
-      </c>
       <c r="P29" t="n">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
@@ -7950,23 +7960,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tom Banton</t>
+          <t>Dewald Brevis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -7975,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -7984,42 +7994,40 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
-        <v>201</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trent Boult</t>
+          <t>Tom Curran</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E31" t="n">
         <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -8037,22 +8045,22 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="M31" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="O31" t="n">
         <v>20</v>
       </c>
       <c r="P31" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
@@ -8060,32 +8068,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nikhil Chaudhary</t>
+          <t>Josh Tongue</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -8094,19 +8102,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>94</v>
+        <v>180</v>
       </c>
       <c r="N32" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>20</v>
       </c>
       <c r="P32" t="n">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
@@ -8114,26 +8122,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Joe Root</t>
+          <t>Jamie Overton</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>124</v>
+        <v>47</v>
       </c>
       <c r="D33" t="n">
-        <v>109</v>
+        <v>30</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -8148,10 +8156,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="N33" t="n">
         <v>24</v>
@@ -8160,36 +8168,34 @@
         <v>20</v>
       </c>
       <c r="P33" t="n">
-        <v>197</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sam Cook</t>
+          <t>James Vince</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -8204,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="M34" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>8</v>
@@ -8216,88 +8222,90 @@
         <v>20</v>
       </c>
       <c r="P34" t="n">
-        <v>194</v>
-      </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tim Seifert</t>
+          <t>Chris Jordan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="D35" t="n">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
         <v>6</v>
       </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="O35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P35" t="n">
-        <v>192</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Tristan Stubbs</t>
+          <t>Tom Banton</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="D36" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="E36" t="n">
+        <v>11</v>
+      </c>
+      <c r="F36" t="n">
         <v>8</v>
       </c>
-      <c r="F36" t="n">
-        <v>4</v>
-      </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
@@ -8305,7 +8313,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -8314,108 +8322,108 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>134</v>
+        <v>177</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="O36" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P36" t="n">
-        <v>190</v>
-      </c>
-      <c r="Q36" t="inlineStr"/>
+        <v>201</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Aiden Markram</t>
+          <t>Trent Boult</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>117</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="N37" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O37" t="n">
         <v>20</v>
       </c>
       <c r="P37" t="n">
-        <v>182</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Liam Dawson</t>
+          <t>Nikhil Chaudhary</t>
         </is>
       </c>
       <c r="B38" t="n">
         <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="D38" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -8424,19 +8432,19 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="M38" t="n">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O38" t="n">
         <v>20</v>
       </c>
       <c r="P38" t="n">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
@@ -8444,86 +8452,88 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mitchell Owen</t>
+          <t>Joe Root</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="E39" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>2</v>
-      </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="M39" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O39" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P39" t="n">
-        <v>174</v>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lhuan-dre Pretorius</t>
+          <t>Sam Cook</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -8532,54 +8542,52 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P40" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Calvin Harrison</t>
+          <t>Tim Seifert</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>5</v>
       </c>
       <c r="C41" t="n">
+        <v>125</v>
+      </c>
+      <c r="D41" t="n">
+        <v>84</v>
+      </c>
+      <c r="E41" t="n">
         <v>12</v>
       </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -8588,52 +8596,54 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="M41" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O41" t="n">
         <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>166</v>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nathan Ellis</t>
+          <t>Tristan Stubbs</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>6</v>
+      </c>
+      <c r="C42" t="n">
+        <v>108</v>
+      </c>
+      <c r="D42" t="n">
+        <v>92</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" t="n">
         <v>4</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
       <c r="G42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -8642,102 +8652,102 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>-2</v>
+        <v>134</v>
       </c>
       <c r="M42" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="O42" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="P42" t="n">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="n">
-        <v>1</v>
-      </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jamie Overton</t>
+          <t>Aiden Markram</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
+        <v>117</v>
+      </c>
+      <c r="D43" t="n">
+        <v>92</v>
+      </c>
+      <c r="E43" t="n">
+        <v>15</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>154</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>8</v>
+      </c>
+      <c r="O43" t="n">
         <v>20</v>
       </c>
-      <c r="D43" t="n">
-        <v>15</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>23</v>
-      </c>
-      <c r="M43" t="n">
-        <v>108</v>
-      </c>
-      <c r="N43" t="n">
-        <v>16</v>
-      </c>
-      <c r="O43" t="n">
-        <v>16</v>
-      </c>
       <c r="P43" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q43" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brydon Carse</t>
+          <t>Lhuan-dre Pretorius</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>66</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -8752,40 +8762,42 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="M44" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P44" t="n">
-        <v>159</v>
-      </c>
-      <c r="Q44" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mohammad Amir</t>
+          <t>Liam Dawson</t>
         </is>
       </c>
       <c r="B45" t="n">
         <v>5</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -8797,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -8806,19 +8818,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M45" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="N45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>20</v>
       </c>
       <c r="P45" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
@@ -8826,90 +8838,86 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jonny Bairstow</t>
+          <t>Mitchell Owen</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>4</v>
+      </c>
+      <c r="C46" t="n">
+        <v>44</v>
+      </c>
+      <c r="D46" t="n">
+        <v>34</v>
+      </c>
+      <c r="E46" t="n">
         <v>3</v>
-      </c>
-      <c r="C46" t="n">
-        <v>79</v>
-      </c>
-      <c r="D46" t="n">
-        <v>57</v>
-      </c>
-      <c r="E46" t="n">
-        <v>9</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="N46" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P46" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Heinrich Klaasen</t>
+          <t>Calvin Harrison</t>
         </is>
       </c>
       <c r="B47" t="n">
         <v>5</v>
       </c>
       <c r="C47" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D47" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -8918,42 +8926,38 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>135</v>
+        <v>16</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O47" t="n">
         <v>20</v>
       </c>
       <c r="P47" t="n">
-        <v>155</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>James Coles</t>
+          <t>Brydon Carse</t>
         </is>
       </c>
       <c r="B48" t="n">
+        <v>5</v>
+      </c>
+      <c r="C48" t="n">
         <v>4</v>
       </c>
-      <c r="C48" t="n">
+      <c r="D48" t="n">
         <v>5</v>
       </c>
-      <c r="D48" t="n">
-        <v>9</v>
-      </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
@@ -8961,34 +8965,34 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>4</v>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2</v>
-      </c>
-      <c r="L48" t="n">
-        <v>5</v>
-      </c>
       <c r="M48" t="n">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="N48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P48" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
@@ -8996,23 +9000,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Philip Salt</t>
+          <t>Jonny Bairstow</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" t="n">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="D49" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -9021,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -9030,52 +9034,56 @@
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>134</v>
+        <v>105</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O49" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>154</v>
-      </c>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
+        <v>157</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Marco Jansen</t>
+          <t>James Coles</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>5</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
       <c r="G50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
         <v>4</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -9084,46 +9092,48 @@
         <v>2</v>
       </c>
       <c r="L50" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="N50" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O50" t="n">
         <v>20</v>
       </c>
       <c r="P50" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dewald Brevis</t>
+          <t>Mohammad Amir</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -9138,19 +9148,19 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N51" t="n">
         <v>8</v>
       </c>
       <c r="O51" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P51" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -9158,32 +9168,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Scott Currie</t>
+          <t>Heinrich Klaasen</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C52" t="n">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -9192,21 +9202,23 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="M52" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P52" t="n">
-        <v>153</v>
-      </c>
-      <c r="Q52" t="inlineStr"/>
+        <v>155</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
@@ -9214,24 +9226,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sherfane Rutherford</t>
+          <t>Zak Crawley</t>
         </is>
       </c>
       <c r="B53" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" t="n">
+        <v>95</v>
+      </c>
+      <c r="D53" t="n">
+        <v>62</v>
+      </c>
+      <c r="E53" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" t="n">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
-        <v>87</v>
-      </c>
-      <c r="D53" t="n">
-        <v>53</v>
-      </c>
-      <c r="E53" t="n">
-        <v>6</v>
-      </c>
-      <c r="F53" t="n">
-        <v>7</v>
-      </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
@@ -9239,7 +9251,7 @@
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -9248,43 +9260,47 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="O53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P53" t="n">
-        <v>152</v>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
+        <v>154</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Will Smeed</t>
+          <t>Philip Salt</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D54" t="n">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="E54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -9302,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -9311,66 +9327,64 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P54" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Harry Brook</t>
+          <t>Marco Jansen</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
         <v>4</v>
       </c>
-      <c r="C55" t="n">
-        <v>99</v>
-      </c>
-      <c r="D55" t="n">
-        <v>63</v>
-      </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
         <v>7</v>
       </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>127</v>
-      </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="N55" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O55" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P55" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
@@ -9378,26 +9392,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Donovan Ferreira</t>
+          <t>Scott Currie</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
         <v>3</v>
-      </c>
-      <c r="F56" t="n">
-        <v>6</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -9409,55 +9423,57 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="N56" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="O56" t="n">
         <v>16</v>
       </c>
       <c r="P56" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Noor Ahmad</t>
+          <t>Sherfane Rutherford</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="D57" t="n">
+        <v>53</v>
+      </c>
+      <c r="E57" t="n">
         <v>6</v>
       </c>
-      <c r="E57" t="n">
-        <v>2</v>
-      </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -9466,19 +9482,19 @@
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="M57" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P57" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
@@ -9486,24 +9502,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jordan Cox</t>
+          <t>Will Smeed</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" t="n">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D58" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="n">
         <v>4</v>
       </c>
-      <c r="F58" t="n">
-        <v>5</v>
-      </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
@@ -9511,7 +9527,7 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -9520,44 +9536,46 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P58" t="n">
-        <v>145</v>
-      </c>
-      <c r="Q58" t="inlineStr"/>
+        <v>151</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
       <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Leus du Plooy</t>
+          <t>Donovan Ferreira</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>4</v>
       </c>
       <c r="C59" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D59" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="n">
         <v>6</v>
       </c>
-      <c r="F59" t="n">
-        <v>2</v>
-      </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
@@ -9565,28 +9583,28 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="O59" t="n">
         <v>16</v>
       </c>
       <c r="P59" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
@@ -9594,27 +9612,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Zak Crawley</t>
+          <t>Noor Ahmad</t>
         </is>
       </c>
       <c r="B60" t="n">
+        <v>5</v>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="n">
+        <v>6</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
         <v>4</v>
       </c>
-      <c r="C60" t="n">
-        <v>95</v>
-      </c>
-      <c r="D60" t="n">
-        <v>62</v>
-      </c>
-      <c r="E60" t="n">
-        <v>10</v>
-      </c>
-      <c r="F60" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
@@ -9628,56 +9646,52 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>126</v>
+        <v>12</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P60" t="n">
-        <v>142</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>David Willey</t>
+          <t>Jordan Cox</t>
         </is>
       </c>
       <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="n">
+        <v>82</v>
+      </c>
+      <c r="D61" t="n">
+        <v>51</v>
+      </c>
+      <c r="E61" t="n">
         <v>4</v>
       </c>
-      <c r="C61" t="n">
-        <v>12</v>
-      </c>
-      <c r="D61" t="n">
-        <v>9</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2</v>
-      </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -9686,19 +9700,19 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="M61" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O61" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P61" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
@@ -9706,23 +9720,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sam Billings</t>
+          <t>Leus du Plooy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D62" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E62" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -9731,28 +9745,28 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O62" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P62" t="n">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
@@ -9760,17 +9774,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Ben Dwarshuis</t>
+          <t>Adam Milne</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -9791,101 +9805,99 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="N63" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O63" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P63" t="n">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="n">
-        <v>1</v>
-      </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Luke Wood</t>
+          <t>Dan Lawrence</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="D64" t="n">
+        <v>40</v>
+      </c>
+      <c r="E64" t="n">
+        <v>7</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>107</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="n">
         <v>8</v>
       </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>13</v>
-      </c>
-      <c r="M64" t="n">
-        <v>83</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
       <c r="O64" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P64" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="n">
-        <v>1</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dan Lawrence</t>
+          <t>Sam Billings</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C65" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D65" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E65" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65" t="n">
         <v>3</v>
@@ -9897,48 +9909,46 @@
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="M65" t="n">
         <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="O65" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P65" t="n">
-        <v>118</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Matt Henry</t>
+          <t>Ben Dwarshuis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -9947,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -9959,46 +9969,48 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="N66" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O66" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="P66" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lewis Gregory</t>
+          <t>Luke Wood</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
         <v>3</v>
@@ -10007,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -10016,52 +10028,54 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M67" t="n">
         <v>83</v>
       </c>
       <c r="N67" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="P67" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ben McKinney</t>
+          <t>Abrar Ahmed</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" t="n">
-        <v>66</v>
+        <v>7</v>
       </c>
       <c r="D68" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="E68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
         <v>3</v>
       </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -10070,45 +10084,43 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>79</v>
+        <v>9</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="N68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P68" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="n">
-        <v>3</v>
-      </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Abrar Ahmed</t>
+          <t>Matt Henry</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>3</v>
@@ -10117,7 +10129,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -10126,19 +10138,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
         <v>86</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P69" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
@@ -10146,17 +10158,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Adam Milne</t>
+          <t>Lewis Gregory</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -10180,19 +10192,19 @@
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N70" t="n">
         <v>8</v>
       </c>
       <c r="O70" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P70" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
@@ -10200,17 +10212,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Chris Woakes</t>
+          <t>Adam Zampa</t>
         </is>
       </c>
       <c r="B71" t="n">